--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,16 +148,37 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
+  </si>
+  <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>DOWN</t>
-  </si>
-  <si>
-    <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
-  </si>
-  <si>
-    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,17 +380,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -882,10 +904,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2403.9</v>
+        <v>2409</v>
       </c>
       <c r="D2">
-        <v>-1.23</v>
+        <v>0.21</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -894,97 +916,97 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-16.5</v>
+        <v>-16.32</v>
       </c>
       <c r="H2">
-        <v>10.83</v>
+        <v>11.07</v>
       </c>
       <c r="I2">
-        <v>-2.21</v>
+        <v>-0.95</v>
       </c>
       <c r="J2">
-        <v>-3.82</v>
+        <v>-3.06</v>
       </c>
       <c r="K2">
-        <v>-8.35</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L2">
-        <v>-13.08</v>
+        <v>-15.18</v>
       </c>
       <c r="M2">
-        <v>10.09</v>
+        <v>10.44</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>2431.4</v>
+        <v>2426.8</v>
       </c>
       <c r="Q2">
-        <v>2539.02</v>
+        <v>2533.32</v>
       </c>
       <c r="R2">
-        <v>2576.23</v>
+        <v>2568.94</v>
       </c>
       <c r="S2">
-        <v>2571.87</v>
+        <v>2570.8</v>
       </c>
       <c r="T2">
-        <v>-6.53</v>
+        <v>-6.29</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.87</v>
+        <v>35.69</v>
       </c>
       <c r="Z2">
-        <v>-41.19</v>
+        <v>-43.96</v>
       </c>
       <c r="AA2">
-        <v>-24.81</v>
+        <v>-28.64</v>
       </c>
       <c r="AB2">
-        <v>-16.39</v>
+        <v>-15.32</v>
       </c>
       <c r="AC2">
-        <v>2.72</v>
+        <v>2.13</v>
       </c>
       <c r="AD2">
-        <v>4.02</v>
+        <v>3.34</v>
       </c>
       <c r="AE2">
-        <v>57.62</v>
+        <v>56.28</v>
       </c>
       <c r="AF2">
-        <v>-17.73</v>
+        <v>-20.64</v>
       </c>
       <c r="AG2">
-        <v>2708.61</v>
+        <v>2712.57</v>
       </c>
       <c r="AH2">
-        <v>2369.43</v>
+        <v>2354.07</v>
       </c>
       <c r="AI2">
         <v>2568.2</v>
       </c>
       <c r="AJ2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK2">
-        <v>33.3</v>
+        <v>36.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,10 +1017,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="D3">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1007,46 +1029,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.84</v>
+        <v>-29.02</v>
       </c>
       <c r="H3">
-        <v>3.08</v>
+        <v>4.29</v>
       </c>
       <c r="I3">
-        <v>-0.54</v>
+        <v>0.85</v>
       </c>
       <c r="J3">
-        <v>-2.31</v>
+        <v>-1.44</v>
       </c>
       <c r="K3">
-        <v>-8.890000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L3">
-        <v>-26.62</v>
+        <v>-25.82</v>
       </c>
       <c r="M3">
-        <v>-0.87</v>
+        <v>-0.53</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>700.53</v>
+        <v>701.74</v>
       </c>
       <c r="Q3">
-        <v>714.1</v>
+        <v>713.48</v>
       </c>
       <c r="R3">
-        <v>746.17</v>
+        <v>743.9</v>
       </c>
       <c r="S3">
-        <v>832.1799999999999</v>
+        <v>830.75</v>
       </c>
       <c r="T3">
-        <v>-14.89</v>
+        <v>-13.75</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,43 +1083,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.95</v>
+        <v>48.55</v>
       </c>
       <c r="Z3">
-        <v>-11.76</v>
+        <v>-10.12</v>
       </c>
       <c r="AA3">
-        <v>-11.99</v>
+        <v>-11.62</v>
       </c>
       <c r="AB3">
-        <v>0.23</v>
+        <v>1.5</v>
       </c>
       <c r="AC3">
-        <v>49.64</v>
+        <v>82.97</v>
       </c>
       <c r="AD3">
-        <v>44.57</v>
+        <v>55.82</v>
       </c>
       <c r="AE3">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="AF3">
-        <v>19.26</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="AG3">
-        <v>738.48</v>
+        <v>736.87</v>
       </c>
       <c r="AH3">
-        <v>689.73</v>
+        <v>690.1</v>
       </c>
       <c r="AI3">
         <v>725.12</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>22.1</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1130,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="D4">
-        <v>0.73</v>
+        <v>-2.62</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1120,46 +1142,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.72</v>
+        <v>-34.49</v>
       </c>
       <c r="H4">
-        <v>3.11</v>
+        <v>0.41</v>
       </c>
       <c r="I4">
-        <v>-3</v>
+        <v>-3.21</v>
       </c>
       <c r="J4">
-        <v>-1.5</v>
+        <v>-3.69</v>
       </c>
       <c r="K4">
-        <v>-8.81</v>
+        <v>-10.15</v>
       </c>
       <c r="L4">
-        <v>-30.36</v>
+        <v>-33.63</v>
       </c>
       <c r="M4">
-        <v>-6.11</v>
+        <v>-6.88</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>527.4299999999999</v>
+        <v>524.01</v>
       </c>
       <c r="Q4">
-        <v>539.84</v>
+        <v>538.49</v>
       </c>
       <c r="R4">
-        <v>547.75</v>
+        <v>546.79</v>
       </c>
       <c r="S4">
-        <v>635.6900000000001</v>
+        <v>634.33</v>
       </c>
       <c r="T4">
-        <v>-16.63</v>
+        <v>-18.64</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,43 +1196,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.13</v>
+        <v>38</v>
       </c>
       <c r="Z4">
-        <v>-5.94</v>
+        <v>-6.91</v>
       </c>
       <c r="AA4">
-        <v>-4.64</v>
+        <v>-5.1</v>
       </c>
       <c r="AB4">
-        <v>-1.3</v>
+        <v>-1.81</v>
       </c>
       <c r="AC4">
-        <v>32.64</v>
+        <v>40.69</v>
       </c>
       <c r="AD4">
-        <v>22.65</v>
+        <v>31.63</v>
       </c>
       <c r="AE4">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="AF4">
-        <v>44.16</v>
+        <v>62.23</v>
       </c>
       <c r="AG4">
-        <v>560.12</v>
+        <v>561.3</v>
       </c>
       <c r="AH4">
-        <v>519.55</v>
+        <v>515.6799999999999</v>
       </c>
       <c r="AI4">
         <v>553.28</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK4">
-        <v>26.43</v>
+        <v>26.92</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1361,7 +1383,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1371,12 +1393,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1384,462 +1441,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-3.82</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.56</v>
+      <c r="D7" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.83</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-2.31</v>
       </c>
+      <c r="D8" s="6">
+        <v>-1.44</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.52</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-2.02</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-1.5</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.52</v>
+      <c r="D9" s="6">
+        <v>-3.69</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.07</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.21</v>
       </c>
+      <c r="D10" s="6">
+        <v>-0.95</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.86</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.82</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-0.54</v>
       </c>
+      <c r="D11" s="6">
+        <v>0.85</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-3</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.62</v>
+      <c r="D12" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-12.93</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-13.08</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.15</v>
+      <c r="D13" s="6">
+        <v>-15.18</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-28.18</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-26.62</v>
       </c>
+      <c r="D14" s="6">
+        <v>-25.82</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-30.2</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-30.36</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.16</v>
+      <c r="D15" s="6">
+        <v>-33.63</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-8.35</v>
       </c>
-      <c r="E16" s="6">
-        <v>-7.45</v>
+      <c r="D16" s="6">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-10.18</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-8.890000000000001</v>
       </c>
+      <c r="D17" s="6">
+        <v>-8.710000000000001</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.29</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-5.26</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-8.81</v>
       </c>
-      <c r="E18" s="6">
-        <v>-3.55</v>
+      <c r="D18" s="6">
+        <v>-10.15</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-15.46</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-16.5</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.04</v>
+      <c r="D19" s="6">
+        <v>-16.32</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.18</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-31.27</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-29.84</v>
       </c>
+      <c r="D20" s="6">
+        <v>-29.02</v>
+      </c>
       <c r="E20" s="7">
-        <v>1.43</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-33.21</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-32.72</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.49</v>
+      <c r="D21" s="6">
+        <v>-34.49</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2433.8</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2403.9</v>
       </c>
-      <c r="E22" s="6">
-        <v>-29.9</v>
+      <c r="D22" s="6">
+        <v>2409</v>
+      </c>
+      <c r="E22" s="7">
+        <v>5.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>693.8</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>708.25</v>
       </c>
+      <c r="D23" s="6">
+        <v>716.55</v>
+      </c>
       <c r="E23" s="7">
-        <v>14.45</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>526.15</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>530</v>
       </c>
-      <c r="E24" s="7">
-        <v>3.85</v>
+      <c r="D24" s="6">
+        <v>516.1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-13.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>34.87</v>
+      </c>
+      <c r="D25" s="6">
+        <v>35.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>34</v>
-      </c>
-      <c r="D25" s="5">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>43.95</v>
+      </c>
+      <c r="D26" s="6">
+        <v>48.55</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>66</v>
-      </c>
-      <c r="D26" s="5">
-        <v>34</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>44.13</v>
+      </c>
+      <c r="D27" s="6">
+        <v>38</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-6.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>37.47</v>
-      </c>
-      <c r="D27" s="5">
-        <v>34.87</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-17.73</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-20.64</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>34.49</v>
-      </c>
-      <c r="D28" s="5">
-        <v>43.95</v>
-      </c>
-      <c r="E28" s="7">
-        <v>9.460000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>19.26</v>
+      </c>
+      <c r="D29" s="6">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>41.71</v>
-      </c>
-      <c r="D29" s="5">
-        <v>44.13</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-56.36</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-17.73</v>
+      <c r="C30" s="6">
+        <v>44.16</v>
+      </c>
+      <c r="D30" s="6">
+        <v>62.23</v>
       </c>
       <c r="E30" s="7">
-        <v>38.63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="D31" s="5">
-        <v>19.26</v>
-      </c>
-      <c r="E31" s="7">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>48.22</v>
-      </c>
-      <c r="D32" s="5">
-        <v>44.16</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-4.06</v>
+        <v>18.07</v>
       </c>
     </row>
   </sheetData>
@@ -1865,60 +1888,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>41</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>40.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2020,25 +2043,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1009</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.008699999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0611</v>
+      <c r="A2" s="14">
+        <v>0.1044</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0053</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0688</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="67">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,16 +169,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.5 → 51.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>51.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +267,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +307,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,8 +766,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -904,10 +906,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2409</v>
+        <v>2373.1</v>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>-1.49</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -916,46 +918,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-16.32</v>
+        <v>-17.57</v>
       </c>
       <c r="H2">
-        <v>11.07</v>
+        <v>9.41</v>
       </c>
       <c r="I2">
-        <v>-0.95</v>
+        <v>-3.03</v>
       </c>
       <c r="J2">
-        <v>-3.06</v>
+        <v>-5.94</v>
       </c>
       <c r="K2">
-        <v>-9.390000000000001</v>
+        <v>-12.47</v>
       </c>
       <c r="L2">
-        <v>-15.18</v>
+        <v>-16.36</v>
       </c>
       <c r="M2">
-        <v>10.44</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>2426.8</v>
+        <v>2411.96</v>
       </c>
       <c r="Q2">
-        <v>2533.32</v>
+        <v>2525.72</v>
       </c>
       <c r="R2">
-        <v>2568.94</v>
+        <v>2560.73</v>
       </c>
       <c r="S2">
-        <v>2570.8</v>
+        <v>2569.55</v>
       </c>
       <c r="T2">
-        <v>-6.29</v>
+        <v>-7.65</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -970,43 +972,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.69</v>
+        <v>32.58</v>
       </c>
       <c r="Z2">
-        <v>-43.96</v>
+        <v>-48.49</v>
       </c>
       <c r="AA2">
-        <v>-28.64</v>
+        <v>-32.61</v>
       </c>
       <c r="AB2">
-        <v>-15.32</v>
+        <v>-15.88</v>
       </c>
       <c r="AC2">
-        <v>2.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD2">
-        <v>3.34</v>
+        <v>1.99</v>
       </c>
       <c r="AE2">
-        <v>56.28</v>
+        <v>55.76</v>
       </c>
       <c r="AF2">
-        <v>-20.64</v>
+        <v>-38.07</v>
       </c>
       <c r="AG2">
-        <v>2712.57</v>
+        <v>2718.8</v>
       </c>
       <c r="AH2">
-        <v>2354.07</v>
+        <v>2332.65</v>
       </c>
       <c r="AI2">
-        <v>2568.2</v>
+        <v>2551.53</v>
       </c>
       <c r="AJ2" t="s">
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>36.47</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1017,10 +1019,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>716.55</v>
+        <v>721.5</v>
       </c>
       <c r="D3">
-        <v>1.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1029,46 +1031,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.02</v>
+        <v>-28.53</v>
       </c>
       <c r="H3">
-        <v>4.29</v>
+        <v>5.01</v>
       </c>
       <c r="I3">
-        <v>0.85</v>
+        <v>2.63</v>
       </c>
       <c r="J3">
-        <v>-1.44</v>
+        <v>-1.03</v>
       </c>
       <c r="K3">
-        <v>-8.710000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="L3">
-        <v>-25.82</v>
+        <v>-25.45</v>
       </c>
       <c r="M3">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>701.74</v>
+        <v>705.4400000000001</v>
       </c>
       <c r="Q3">
-        <v>713.48</v>
+        <v>713.41</v>
       </c>
       <c r="R3">
-        <v>743.9</v>
+        <v>741.75</v>
       </c>
       <c r="S3">
-        <v>830.75</v>
+        <v>829.3099999999999</v>
       </c>
       <c r="T3">
-        <v>-13.75</v>
+        <v>-13</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1083,34 +1085,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>48.55</v>
+        <v>51.12</v>
       </c>
       <c r="Z3">
-        <v>-10.12</v>
+        <v>-8.32</v>
       </c>
       <c r="AA3">
-        <v>-11.62</v>
+        <v>-10.96</v>
       </c>
       <c r="AB3">
-        <v>1.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC3">
-        <v>82.97</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>55.82</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="AE3">
-        <v>13.4</v>
+        <v>13.48</v>
       </c>
       <c r="AF3">
-        <v>87.95999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="AG3">
-        <v>736.87</v>
+        <v>736.67</v>
       </c>
       <c r="AH3">
-        <v>690.1</v>
+        <v>690.14</v>
       </c>
       <c r="AI3">
         <v>725.12</v>
@@ -1119,7 +1121,7 @@
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>23.96</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1130,10 +1132,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="D4">
-        <v>-2.62</v>
+        <v>2.73</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1142,46 +1144,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-34.49</v>
+        <v>-32.7</v>
       </c>
       <c r="H4">
-        <v>0.41</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>-3.21</v>
+        <v>-0.67</v>
       </c>
       <c r="J4">
-        <v>-3.69</v>
+        <v>-2.36</v>
       </c>
       <c r="K4">
-        <v>-10.15</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L4">
-        <v>-33.63</v>
+        <v>-31.52</v>
       </c>
       <c r="M4">
-        <v>-6.88</v>
+        <v>-6.6</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>524.01</v>
+        <v>523.29</v>
       </c>
       <c r="Q4">
-        <v>538.49</v>
+        <v>538.09</v>
       </c>
       <c r="R4">
-        <v>546.79</v>
+        <v>545.95</v>
       </c>
       <c r="S4">
-        <v>634.33</v>
+        <v>633.09</v>
       </c>
       <c r="T4">
-        <v>-18.64</v>
+        <v>-16.25</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1196,34 +1198,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38</v>
+        <v>46.17</v>
       </c>
       <c r="Z4">
-        <v>-6.91</v>
+        <v>-6.47</v>
       </c>
       <c r="AA4">
-        <v>-5.1</v>
+        <v>-5.37</v>
       </c>
       <c r="AB4">
-        <v>-1.81</v>
+        <v>-1.1</v>
       </c>
       <c r="AC4">
-        <v>40.69</v>
+        <v>51.62</v>
       </c>
       <c r="AD4">
-        <v>31.63</v>
+        <v>41.65</v>
       </c>
       <c r="AE4">
-        <v>12.23</v>
+        <v>12.63</v>
       </c>
       <c r="AF4">
-        <v>62.23</v>
+        <v>24.94</v>
       </c>
       <c r="AG4">
-        <v>561.3</v>
+        <v>561.2</v>
       </c>
       <c r="AH4">
-        <v>515.6799999999999</v>
+        <v>514.98</v>
       </c>
       <c r="AI4">
         <v>553.28</v>
@@ -1232,7 +1234,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>26.92</v>
+        <v>25.71</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1415,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>49</v>
@@ -1428,12 +1430,12 @@
         <v>52</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1445,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1465,13 +1467,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-3.82</v>
+        <v>-3.06</v>
       </c>
       <c r="D7" s="6">
-        <v>-3.06</v>
+        <v>-5.94</v>
       </c>
       <c r="E7" s="7">
-        <v>0.76</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1482,13 +1484,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.31</v>
+        <v>-1.44</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.44</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.87</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1499,13 +1501,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.5</v>
+        <v>-3.69</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.69</v>
+        <v>-2.36</v>
       </c>
       <c r="E9" s="8">
-        <v>-2.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1516,13 +1518,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.21</v>
+        <v>-0.95</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.95</v>
+        <v>-3.03</v>
       </c>
       <c r="E10" s="7">
-        <v>1.26</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1533,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.54</v>
+        <v>0.85</v>
       </c>
       <c r="D11" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.39</v>
+        <v>2.63</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1550,13 +1552,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-3</v>
+        <v>-3.21</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.21</v>
+        <v>-0.67</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.21</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1567,13 +1569,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-13.08</v>
+        <v>-15.18</v>
       </c>
       <c r="D13" s="6">
-        <v>-15.18</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.1</v>
+        <v>-16.36</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1584,13 +1586,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.62</v>
+        <v>-25.82</v>
       </c>
       <c r="D14" s="6">
-        <v>-25.82</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.8</v>
+        <v>-25.45</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.37</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1601,13 +1603,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-30.36</v>
+        <v>-33.63</v>
       </c>
       <c r="D15" s="6">
-        <v>-33.63</v>
+        <v>-31.52</v>
       </c>
       <c r="E15" s="8">
-        <v>-3.27</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1618,13 +1620,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-8.35</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="D16" s="6">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.04</v>
+        <v>-12.47</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1635,13 +1637,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.890000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="D17" s="6">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.18</v>
+        <v>-8.33</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1652,13 +1654,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-8.81</v>
+        <v>-10.15</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.15</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1669,13 +1671,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-16.5</v>
+        <v>-16.32</v>
       </c>
       <c r="D19" s="6">
-        <v>-16.32</v>
+        <v>-17.57</v>
       </c>
       <c r="E19" s="7">
-        <v>0.18</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1686,13 +1688,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.84</v>
+        <v>-29.02</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.82</v>
+        <v>-28.53</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1703,13 +1705,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-32.72</v>
+        <v>-34.49</v>
       </c>
       <c r="D21" s="6">
-        <v>-34.49</v>
+        <v>-32.7</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.77</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1720,13 +1722,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>2403.9</v>
+        <v>2409</v>
       </c>
       <c r="D22" s="6">
-        <v>2409</v>
+        <v>2373.1</v>
       </c>
       <c r="E22" s="7">
-        <v>5.1</v>
+        <v>-35.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1737,13 +1739,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="D23" s="6">
-        <v>716.55</v>
-      </c>
-      <c r="E23" s="7">
-        <v>8.300000000000001</v>
+        <v>721.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>4.95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1754,13 +1756,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="D24" s="6">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="E24" s="8">
-        <v>-13.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1771,13 +1773,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>34.87</v>
+        <v>35.69</v>
       </c>
       <c r="D25" s="6">
-        <v>35.69</v>
+        <v>32.58</v>
       </c>
       <c r="E25" s="7">
-        <v>0.82</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1788,13 +1790,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>43.95</v>
+        <v>48.55</v>
       </c>
       <c r="D26" s="6">
-        <v>48.55</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.6</v>
+        <v>51.12</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1805,13 +1807,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>44.13</v>
+        <v>38</v>
       </c>
       <c r="D27" s="6">
-        <v>38</v>
+        <v>46.17</v>
       </c>
       <c r="E27" s="8">
-        <v>-6.13</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1822,13 +1824,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-17.73</v>
+        <v>-20.64</v>
       </c>
       <c r="D28" s="6">
-        <v>-20.64</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.91</v>
+        <v>-38.07</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-17.43</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1839,13 +1841,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>19.26</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="D29" s="6">
-        <v>87.95999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="E29" s="7">
-        <v>68.7</v>
+        <v>-90.56999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1856,13 +1858,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>44.16</v>
+        <v>62.23</v>
       </c>
       <c r="D30" s="6">
-        <v>62.23</v>
+        <v>24.94</v>
       </c>
       <c r="E30" s="7">
-        <v>18.07</v>
+        <v>-37.29</v>
       </c>
     </row>
   </sheetData>
@@ -1892,28 +1894,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1927,16 +1929,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>40.7</v>
+        <v>43.3</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.4</v>
+        <v>-9.9</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2055,13 +2057,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1044</v>
+        <v>0.0989</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0053</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0688</v>
+        <v>-0.066</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,6 +151,9 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -172,16 +175,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.5 → 51.1</t>
+    <t>46.2 → 57.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.5</t>
+    <t>46.2</t>
+  </si>
+  <si>
+    <t>57.6</t>
+  </si>
+  <si>
+    <t>51.1 → 46.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.1</t>
+  </si>
+  <si>
+    <t>46.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -383,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -391,10 +406,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -766,7 +782,10 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -906,10 +925,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2373.1</v>
+        <v>2387.7</v>
       </c>
       <c r="D2">
-        <v>-1.49</v>
+        <v>0.62</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -918,46 +937,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.57</v>
+        <v>-17.06</v>
       </c>
       <c r="H2">
-        <v>9.41</v>
+        <v>10.09</v>
       </c>
       <c r="I2">
-        <v>-3.03</v>
+        <v>-2.14</v>
       </c>
       <c r="J2">
-        <v>-5.94</v>
+        <v>-5.44</v>
       </c>
       <c r="K2">
-        <v>-12.47</v>
+        <v>-12.48</v>
       </c>
       <c r="L2">
-        <v>-16.36</v>
+        <v>-15.84</v>
       </c>
       <c r="M2">
-        <v>9.890000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>2411.96</v>
+        <v>2401.5</v>
       </c>
       <c r="Q2">
-        <v>2525.72</v>
+        <v>2517.52</v>
       </c>
       <c r="R2">
-        <v>2560.73</v>
+        <v>2555.3</v>
       </c>
       <c r="S2">
-        <v>2569.55</v>
+        <v>2568.41</v>
       </c>
       <c r="T2">
-        <v>-7.65</v>
+        <v>-7.04</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -972,34 +991,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.58</v>
+        <v>35.06</v>
       </c>
       <c r="Z2">
-        <v>-48.49</v>
+        <v>-50.32</v>
       </c>
       <c r="AA2">
-        <v>-32.61</v>
+        <v>-36.15</v>
       </c>
       <c r="AB2">
-        <v>-15.88</v>
+        <v>-14.17</v>
       </c>
       <c r="AC2">
-        <v>1.11</v>
+        <v>5.03</v>
       </c>
       <c r="AD2">
-        <v>1.99</v>
+        <v>2.76</v>
       </c>
       <c r="AE2">
-        <v>55.76</v>
+        <v>54.77</v>
       </c>
       <c r="AF2">
-        <v>-38.07</v>
+        <v>-36.32</v>
       </c>
       <c r="AG2">
-        <v>2718.8</v>
+        <v>2719.67</v>
       </c>
       <c r="AH2">
-        <v>2332.65</v>
+        <v>2315.38</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -1008,7 +1027,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>40.15</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1019,10 +1038,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>721.5</v>
+        <v>713</v>
       </c>
       <c r="D3">
-        <v>0.6899999999999999</v>
+        <v>-1.18</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1031,46 +1050,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-28.53</v>
+        <v>-29.37</v>
       </c>
       <c r="H3">
-        <v>5.01</v>
+        <v>3.77</v>
       </c>
       <c r="I3">
-        <v>2.63</v>
+        <v>3.77</v>
       </c>
       <c r="J3">
-        <v>-1.03</v>
+        <v>-1.38</v>
       </c>
       <c r="K3">
-        <v>-8.33</v>
+        <v>-10.76</v>
       </c>
       <c r="L3">
-        <v>-25.45</v>
+        <v>-26.29</v>
       </c>
       <c r="M3">
-        <v>-0.5600000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>705.4400000000001</v>
+        <v>710.62</v>
       </c>
       <c r="Q3">
-        <v>713.41</v>
+        <v>713.0599999999999</v>
       </c>
       <c r="R3">
-        <v>741.75</v>
+        <v>739.8</v>
       </c>
       <c r="S3">
-        <v>829.3099999999999</v>
+        <v>827.83</v>
       </c>
       <c r="T3">
-        <v>-13</v>
+        <v>-13.87</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1085,34 +1104,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>51.12</v>
+        <v>46.79</v>
       </c>
       <c r="Z3">
-        <v>-8.32</v>
+        <v>-7.5</v>
       </c>
       <c r="AA3">
-        <v>-10.96</v>
+        <v>-10.27</v>
       </c>
       <c r="AB3">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>93.37</v>
       </c>
       <c r="AD3">
-        <v>77.54000000000001</v>
+        <v>92.11</v>
       </c>
       <c r="AE3">
-        <v>13.48</v>
+        <v>13.12</v>
       </c>
       <c r="AF3">
-        <v>-2.61</v>
+        <v>-25.33</v>
       </c>
       <c r="AG3">
-        <v>736.67</v>
+        <v>736.11</v>
       </c>
       <c r="AH3">
-        <v>690.14</v>
+        <v>690</v>
       </c>
       <c r="AI3">
         <v>725.12</v>
@@ -1121,7 +1140,7 @@
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>24.31</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1132,10 +1151,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="D4">
-        <v>2.73</v>
+        <v>5.05</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1144,46 +1163,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.7</v>
+        <v>-29.3</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I4">
-        <v>-0.67</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J4">
-        <v>-2.36</v>
+        <v>3.48</v>
       </c>
       <c r="K4">
-        <v>-8.869999999999999</v>
+        <v>-5.8</v>
       </c>
       <c r="L4">
-        <v>-31.52</v>
+        <v>-28.56</v>
       </c>
       <c r="M4">
-        <v>-6.6</v>
+        <v>-5.49</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>523.29</v>
+        <v>531.89</v>
       </c>
       <c r="Q4">
-        <v>538.09</v>
+        <v>539.12</v>
       </c>
       <c r="R4">
-        <v>545.95</v>
+        <v>545.97</v>
       </c>
       <c r="S4">
-        <v>633.09</v>
+        <v>632.0599999999999</v>
       </c>
       <c r="T4">
-        <v>-16.25</v>
+        <v>-11.88</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1198,43 +1217,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.17</v>
+        <v>57.6</v>
       </c>
       <c r="Z4">
-        <v>-6.47</v>
+        <v>-3.91</v>
       </c>
       <c r="AA4">
-        <v>-5.37</v>
+        <v>-5.08</v>
       </c>
       <c r="AB4">
-        <v>-1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC4">
-        <v>51.62</v>
+        <v>66.52</v>
       </c>
       <c r="AD4">
-        <v>41.65</v>
+        <v>52.94</v>
       </c>
       <c r="AE4">
-        <v>12.63</v>
+        <v>13.94</v>
       </c>
       <c r="AF4">
-        <v>24.94</v>
+        <v>191.18</v>
       </c>
       <c r="AG4">
-        <v>561.2</v>
+        <v>563.7</v>
       </c>
       <c r="AH4">
-        <v>514.98</v>
+        <v>514.54</v>
       </c>
       <c r="AI4">
-        <v>553.28</v>
+        <v>503.62</v>
       </c>
       <c r="AJ4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.71</v>
+        <v>27.22</v>
       </c>
     </row>
   </sheetData>
@@ -1375,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1385,7 +1404,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1398,479 +1417,533 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-5.94</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-5.44</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-1.44</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-1.03</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-1.38</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.69</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-2.36</v>
       </c>
-      <c r="E9" s="8">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>3.48</v>
+      </c>
+      <c r="E10" s="8">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.95</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>-3.03</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-2.14</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>2.63</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>3.77</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.21</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="7">
         <v>-0.67</v>
       </c>
-      <c r="E12" s="8">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E13" s="8">
+        <v>9.039999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-15.18</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="7">
         <v>-16.36</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-15.84</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-25.82</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="7">
         <v>-25.45</v>
       </c>
-      <c r="E14" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-26.29</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-33.63</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="7">
         <v>-31.52</v>
       </c>
-      <c r="E15" s="8">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-28.56</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="7">
         <v>-12.47</v>
       </c>
-      <c r="E16" s="7">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-12.48</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="7">
         <v>-8.33</v>
       </c>
-      <c r="E17" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-10.76</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-10.15</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="7">
         <v>-8.869999999999999</v>
       </c>
-      <c r="E18" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="7">
+        <v>-5.8</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-16.32</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="7">
         <v>-17.57</v>
       </c>
-      <c r="E19" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-17.06</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-29.02</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C21" s="7">
         <v>-28.53</v>
       </c>
-      <c r="E20" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="7">
+        <v>-29.37</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-34.49</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="7">
         <v>-32.7</v>
       </c>
-      <c r="E21" s="8">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>-29.3</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2409</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="7">
         <v>2373.1</v>
       </c>
-      <c r="E22" s="7">
-        <v>-35.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>2387.7</v>
+      </c>
+      <c r="E23" s="8">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>716.55</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="7">
         <v>721.5</v>
       </c>
-      <c r="E23" s="8">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="7">
+        <v>713</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>516.1</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="7">
         <v>530.2</v>
       </c>
-      <c r="E24" s="8">
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="7">
+        <v>557</v>
+      </c>
+      <c r="E25" s="8">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="7">
+        <v>66</v>
+      </c>
+      <c r="D26" s="7">
+        <v>34</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="7">
+        <v>34</v>
+      </c>
+      <c r="D27" s="7">
+        <v>66</v>
+      </c>
+      <c r="E27" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>35.69</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C28" s="7">
         <v>32.58</v>
       </c>
-      <c r="E25" s="7">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D28" s="7">
+        <v>35.06</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>48.55</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C29" s="7">
         <v>51.12</v>
       </c>
-      <c r="E26" s="8">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D29" s="7">
+        <v>46.79</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C30" s="7">
+        <v>46.17</v>
+      </c>
+      <c r="D30" s="7">
+        <v>57.6</v>
+      </c>
+      <c r="E30" s="8">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-38.07</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-36.32</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="6">
-        <v>46.17</v>
-      </c>
-      <c r="E27" s="8">
-        <v>8.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-20.64</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-38.07</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-17.43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="C32" s="7">
+        <v>-2.61</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-25.33</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-22.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>87.95999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-90.56999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>62.23</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C33" s="7">
         <v>24.94</v>
       </c>
-      <c r="E30" s="7">
-        <v>-37.29</v>
+      <c r="D33" s="7">
+        <v>191.18</v>
+      </c>
+      <c r="E33" s="8">
+        <v>166.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1890,60 +1963,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>66</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>43.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>46.5</v>
+      </c>
+      <c r="E2" s="12">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-1.1</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="H2" s="12">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2045,25 +2118,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.0989</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.005600000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.066</v>
+      <c r="A2" s="15">
+        <v>0.1016</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0107</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0549</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,28 +175,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.2 → 57.6</t>
+    <t>46.8 → 55.4</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>46.2</t>
-  </si>
-  <si>
-    <t>57.6</t>
-  </si>
-  <si>
-    <t>51.1 → 46.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
     <t>46.8</t>
+  </si>
+  <si>
+    <t>55.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,7 +394,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -782,10 +769,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -925,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2387.7</v>
+        <v>2425</v>
       </c>
       <c r="D2">
-        <v>0.62</v>
+        <v>1.56</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -937,46 +921,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.06</v>
+        <v>-15.76</v>
       </c>
       <c r="H2">
-        <v>10.09</v>
+        <v>11.8</v>
       </c>
       <c r="I2">
-        <v>-2.14</v>
+        <v>-0.36</v>
       </c>
       <c r="J2">
-        <v>-5.44</v>
+        <v>-4.97</v>
       </c>
       <c r="K2">
-        <v>-12.48</v>
+        <v>-10.81</v>
       </c>
       <c r="L2">
-        <v>-15.84</v>
+        <v>-13.72</v>
       </c>
       <c r="M2">
-        <v>10.16</v>
+        <v>10.86</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>2401.5</v>
+        <v>2399.74</v>
       </c>
       <c r="Q2">
-        <v>2517.52</v>
+        <v>2507.57</v>
       </c>
       <c r="R2">
-        <v>2555.3</v>
+        <v>2549.06</v>
       </c>
       <c r="S2">
-        <v>2568.41</v>
+        <v>2567.58</v>
       </c>
       <c r="T2">
-        <v>-7.04</v>
+        <v>-5.55</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -991,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.06</v>
+        <v>41.02</v>
       </c>
       <c r="Z2">
-        <v>-50.32</v>
+        <v>-48.21</v>
       </c>
       <c r="AA2">
-        <v>-36.15</v>
+        <v>-38.56</v>
       </c>
       <c r="AB2">
-        <v>-14.17</v>
+        <v>-9.65</v>
       </c>
       <c r="AC2">
-        <v>5.03</v>
+        <v>17.28</v>
       </c>
       <c r="AD2">
-        <v>2.76</v>
+        <v>7.81</v>
       </c>
       <c r="AE2">
-        <v>54.77</v>
+        <v>54.52</v>
       </c>
       <c r="AF2">
-        <v>-36.32</v>
+        <v>36.07</v>
       </c>
       <c r="AG2">
-        <v>2719.67</v>
+        <v>2707.23</v>
       </c>
       <c r="AH2">
-        <v>2315.38</v>
+        <v>2307.92</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -1027,7 +1011,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>42.33</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D3">
-        <v>-1.18</v>
+        <v>2.52</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1050,46 +1034,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.37</v>
+        <v>-27.59</v>
       </c>
       <c r="H3">
-        <v>3.77</v>
+        <v>6.39</v>
       </c>
       <c r="I3">
-        <v>3.77</v>
+        <v>5.36</v>
       </c>
       <c r="J3">
-        <v>-1.38</v>
+        <v>1.53</v>
       </c>
       <c r="K3">
-        <v>-10.76</v>
+        <v>-6.26</v>
       </c>
       <c r="L3">
-        <v>-26.29</v>
+        <v>-24.41</v>
       </c>
       <c r="M3">
-        <v>-1.07</v>
+        <v>-0.3</v>
       </c>
       <c r="N3">
+        <v>66</v>
+      </c>
+      <c r="O3">
         <v>34</v>
       </c>
-      <c r="O3">
-        <v>30</v>
-      </c>
       <c r="P3">
-        <v>710.62</v>
+        <v>718.0599999999999</v>
       </c>
       <c r="Q3">
-        <v>713.0599999999999</v>
+        <v>713.35</v>
       </c>
       <c r="R3">
-        <v>739.8</v>
+        <v>738.0700000000001</v>
       </c>
       <c r="S3">
-        <v>827.83</v>
+        <v>826.48</v>
       </c>
       <c r="T3">
-        <v>-13.87</v>
+        <v>-11.55</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1104,43 +1088,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.79</v>
+        <v>55.4</v>
       </c>
       <c r="Z3">
-        <v>-7.5</v>
+        <v>-5.34</v>
       </c>
       <c r="AA3">
-        <v>-10.27</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AB3">
-        <v>2.77</v>
+        <v>3.95</v>
       </c>
       <c r="AC3">
         <v>93.37</v>
       </c>
       <c r="AD3">
-        <v>92.11</v>
+        <v>95.58</v>
       </c>
       <c r="AE3">
-        <v>13.12</v>
+        <v>13.67</v>
       </c>
       <c r="AF3">
-        <v>-25.33</v>
+        <v>35.87</v>
       </c>
       <c r="AG3">
-        <v>736.11</v>
+        <v>737.2</v>
       </c>
       <c r="AH3">
-        <v>690</v>
+        <v>689.51</v>
       </c>
       <c r="AI3">
-        <v>725.12</v>
+        <v>685.22</v>
       </c>
       <c r="AJ3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>24.62</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>557</v>
+        <v>550.95</v>
       </c>
       <c r="D4">
-        <v>5.05</v>
+        <v>-1.09</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1163,46 +1147,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-29.3</v>
+        <v>-30.06</v>
       </c>
       <c r="H4">
-        <v>8.369999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="I4">
-        <v>8.369999999999999</v>
+        <v>4.71</v>
       </c>
       <c r="J4">
-        <v>3.48</v>
+        <v>2.73</v>
       </c>
       <c r="K4">
-        <v>-5.8</v>
+        <v>-6.91</v>
       </c>
       <c r="L4">
-        <v>-28.56</v>
+        <v>-29.11</v>
       </c>
       <c r="M4">
-        <v>-5.49</v>
+        <v>-5.25</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>531.89</v>
+        <v>536.85</v>
       </c>
       <c r="Q4">
-        <v>539.12</v>
+        <v>539.5700000000001</v>
       </c>
       <c r="R4">
-        <v>545.97</v>
+        <v>545.95</v>
       </c>
       <c r="S4">
-        <v>632.0599999999999</v>
+        <v>630.98</v>
       </c>
       <c r="T4">
-        <v>-11.88</v>
+        <v>-12.68</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1217,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>57.6</v>
+        <v>54.78</v>
       </c>
       <c r="Z4">
-        <v>-3.91</v>
+        <v>-2.34</v>
       </c>
       <c r="AA4">
-        <v>-5.08</v>
+        <v>-4.53</v>
       </c>
       <c r="AB4">
-        <v>1.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC4">
-        <v>66.52</v>
+        <v>87.94</v>
       </c>
       <c r="AD4">
-        <v>52.94</v>
+        <v>68.69</v>
       </c>
       <c r="AE4">
-        <v>13.94</v>
+        <v>13.95</v>
       </c>
       <c r="AF4">
-        <v>191.18</v>
+        <v>55.33</v>
       </c>
       <c r="AG4">
-        <v>563.7</v>
+        <v>564.6900000000001</v>
       </c>
       <c r="AH4">
-        <v>514.54</v>
+        <v>514.45</v>
       </c>
       <c r="AI4">
-        <v>503.62</v>
+        <v>516.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.22</v>
+        <v>29.14</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1434,7 +1418,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -1452,498 +1436,478 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.44</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.97</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1.53</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3.48</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2.73</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-5.94</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.44</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.14</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1.03</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3.77</v>
+      </c>
+      <c r="D11" s="6">
+        <v>5.36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-2.36</v>
-      </c>
-      <c r="D10" s="7">
-        <v>3.48</v>
-      </c>
-      <c r="E10" s="8">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4.71</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-3.03</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-2.14</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-15.84</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-13.72</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2.63</v>
-      </c>
-      <c r="D12" s="7">
-        <v>3.77</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-26.29</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-24.41</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="D13" s="7">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="E13" s="8">
-        <v>9.039999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-28.56</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-29.11</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-16.36</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-15.84</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-12.48</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-10.81</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-25.45</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-26.29</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-10.76</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-31.52</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-28.56</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-5.8</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-6.91</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-12.47</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-12.48</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-17.06</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-15.76</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-8.33</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-10.76</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-29.37</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-27.59</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-5.8</v>
-      </c>
-      <c r="E19" s="8">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-29.3</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-30.06</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-17.57</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-17.06</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2387.7</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2425</v>
+      </c>
+      <c r="E22" s="7">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-28.53</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-29.37</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>713</v>
+      </c>
+      <c r="D23" s="6">
+        <v>731</v>
+      </c>
+      <c r="E23" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-32.7</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-29.3</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>557</v>
+      </c>
+      <c r="D24" s="6">
+        <v>550.95</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-6.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>34</v>
+      </c>
+      <c r="D25" s="6">
+        <v>66</v>
+      </c>
+      <c r="E25" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>34</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2373.1</v>
-      </c>
-      <c r="D23" s="7">
-        <v>2387.7</v>
-      </c>
-      <c r="E23" s="8">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>35.06</v>
+      </c>
+      <c r="D27" s="6">
+        <v>41.02</v>
+      </c>
+      <c r="E27" s="7">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7">
-        <v>721.5</v>
-      </c>
-      <c r="D24" s="7">
-        <v>713</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-8.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="D28" s="6">
+        <v>55.4</v>
+      </c>
+      <c r="E28" s="7">
+        <v>8.609999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7">
-        <v>530.2</v>
-      </c>
-      <c r="D25" s="7">
-        <v>557</v>
-      </c>
-      <c r="E25" s="8">
-        <v>26.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6">
+        <v>57.6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>54.78</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-36.32</v>
+      </c>
+      <c r="D30" s="6">
+        <v>36.07</v>
+      </c>
+      <c r="E30" s="7">
+        <v>72.39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="7">
-        <v>66</v>
-      </c>
-      <c r="D26" s="7">
-        <v>34</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-25.33</v>
+      </c>
+      <c r="D31" s="6">
+        <v>35.87</v>
+      </c>
+      <c r="E31" s="7">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="7">
-        <v>34</v>
-      </c>
-      <c r="D27" s="7">
-        <v>66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7">
-        <v>32.58</v>
-      </c>
-      <c r="D28" s="7">
-        <v>35.06</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="7">
-        <v>51.12</v>
-      </c>
-      <c r="D29" s="7">
-        <v>46.79</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="7">
-        <v>46.17</v>
-      </c>
-      <c r="D30" s="7">
-        <v>57.6</v>
-      </c>
-      <c r="E30" s="8">
-        <v>11.43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="7">
-        <v>-38.07</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-36.32</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-25.33</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-22.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="7">
-        <v>24.94</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="C32" s="6">
         <v>191.18</v>
       </c>
-      <c r="E33" s="8">
-        <v>166.24</v>
+      <c r="D32" s="6">
+        <v>55.33</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-135.85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1963,60 +1927,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="12">
-        <v>46.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>50.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="12">
-        <v>-1.1</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-0.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2118,25 +2082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.1016</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0107</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0549</v>
+      <c r="A2" s="14">
+        <v>0.1086</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.003</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0525</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.8 → 55.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>55.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2425</v>
+        <v>2440</v>
       </c>
       <c r="D2">
-        <v>1.56</v>
+        <v>0.62</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -921,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.76</v>
+        <v>-15.24</v>
       </c>
       <c r="H2">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
-        <v>-0.36</v>
+        <v>1.5</v>
       </c>
       <c r="J2">
-        <v>-4.97</v>
+        <v>-7.01</v>
       </c>
       <c r="K2">
-        <v>-10.81</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L2">
         <v>-13.72</v>
       </c>
       <c r="M2">
-        <v>10.86</v>
+        <v>11.08</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>2399.74</v>
+        <v>2406.96</v>
       </c>
       <c r="Q2">
-        <v>2507.57</v>
+        <v>2499.07</v>
       </c>
       <c r="R2">
-        <v>2549.06</v>
+        <v>2542.64</v>
       </c>
       <c r="S2">
-        <v>2567.58</v>
+        <v>2567.06</v>
       </c>
       <c r="T2">
-        <v>-5.55</v>
+        <v>-4.95</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,34 +947,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.02</v>
+        <v>43.27</v>
       </c>
       <c r="Z2">
-        <v>-48.21</v>
+        <v>-44.81</v>
       </c>
       <c r="AA2">
-        <v>-38.56</v>
+        <v>-39.81</v>
       </c>
       <c r="AB2">
-        <v>-9.65</v>
+        <v>-5</v>
       </c>
       <c r="AC2">
-        <v>17.28</v>
+        <v>43.83</v>
       </c>
       <c r="AD2">
-        <v>7.81</v>
+        <v>22.05</v>
       </c>
       <c r="AE2">
-        <v>54.52</v>
+        <v>53.76</v>
       </c>
       <c r="AF2">
-        <v>36.07</v>
+        <v>-35.2</v>
       </c>
       <c r="AG2">
-        <v>2707.23</v>
+        <v>2694.8</v>
       </c>
       <c r="AH2">
-        <v>2307.92</v>
+        <v>2303.35</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -1011,7 +983,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>40.77</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>731</v>
+        <v>739.5</v>
       </c>
       <c r="D3">
-        <v>2.52</v>
+        <v>1.16</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-27.59</v>
+        <v>-26.75</v>
       </c>
       <c r="H3">
-        <v>6.39</v>
+        <v>7.63</v>
       </c>
       <c r="I3">
-        <v>5.36</v>
+        <v>4.41</v>
       </c>
       <c r="J3">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="K3">
-        <v>-6.26</v>
+        <v>-5.96</v>
       </c>
       <c r="L3">
-        <v>-24.41</v>
+        <v>-23.51</v>
       </c>
       <c r="M3">
-        <v>-0.3</v>
+        <v>0.04</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>718.0599999999999</v>
+        <v>724.3099999999999</v>
       </c>
       <c r="Q3">
-        <v>713.35</v>
+        <v>713.98</v>
       </c>
       <c r="R3">
-        <v>738.0700000000001</v>
+        <v>736.36</v>
       </c>
       <c r="S3">
-        <v>826.48</v>
+        <v>825.23</v>
       </c>
       <c r="T3">
-        <v>-11.55</v>
+        <v>-10.39</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>55.4</v>
+        <v>58.79</v>
       </c>
       <c r="Z3">
-        <v>-5.34</v>
+        <v>-2.9</v>
       </c>
       <c r="AA3">
-        <v>-9.279999999999999</v>
+        <v>-8.01</v>
       </c>
       <c r="AB3">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AC3">
         <v>93.37</v>
       </c>
       <c r="AD3">
-        <v>95.58</v>
+        <v>93.37</v>
       </c>
       <c r="AE3">
         <v>13.67</v>
       </c>
       <c r="AF3">
-        <v>35.87</v>
+        <v>18.91</v>
       </c>
       <c r="AG3">
-        <v>737.2</v>
+        <v>739.91</v>
       </c>
       <c r="AH3">
-        <v>689.51</v>
+        <v>688.0599999999999</v>
       </c>
       <c r="AI3">
-        <v>685.22</v>
+        <v>694.85</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>27.23</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>550.95</v>
+        <v>559.4</v>
       </c>
       <c r="D4">
-        <v>-1.09</v>
+        <v>1.53</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1147,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.06</v>
+        <v>-28.99</v>
       </c>
       <c r="H4">
-        <v>7.19</v>
+        <v>8.83</v>
       </c>
       <c r="I4">
-        <v>4.71</v>
+        <v>5.55</v>
       </c>
       <c r="J4">
-        <v>2.73</v>
+        <v>3.21</v>
       </c>
       <c r="K4">
-        <v>-6.91</v>
+        <v>-6.32</v>
       </c>
       <c r="L4">
-        <v>-29.11</v>
+        <v>-27.76</v>
       </c>
       <c r="M4">
-        <v>-5.25</v>
+        <v>-5.1</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>536.85</v>
+        <v>542.73</v>
       </c>
       <c r="Q4">
-        <v>539.5700000000001</v>
+        <v>539.8</v>
       </c>
       <c r="R4">
-        <v>545.95</v>
+        <v>545.79</v>
       </c>
       <c r="S4">
-        <v>630.98</v>
+        <v>629.98</v>
       </c>
       <c r="T4">
-        <v>-12.68</v>
+        <v>-11.2</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>54.78</v>
+        <v>57.89</v>
       </c>
       <c r="Z4">
-        <v>-2.34</v>
+        <v>-0.42</v>
       </c>
       <c r="AA4">
-        <v>-4.53</v>
+        <v>-3.71</v>
       </c>
       <c r="AB4">
-        <v>2.19</v>
+        <v>3.29</v>
       </c>
       <c r="AC4">
-        <v>87.94</v>
+        <v>96.13</v>
       </c>
       <c r="AD4">
-        <v>68.69</v>
+        <v>83.53</v>
       </c>
       <c r="AE4">
-        <v>13.95</v>
+        <v>14.02</v>
       </c>
       <c r="AF4">
-        <v>55.33</v>
+        <v>-24.16</v>
       </c>
       <c r="AG4">
-        <v>564.6900000000001</v>
+        <v>565.58</v>
       </c>
       <c r="AH4">
-        <v>514.45</v>
+        <v>514.02</v>
       </c>
       <c r="AI4">
-        <v>516.11</v>
+        <v>516.72</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>29.14</v>
+        <v>30.96</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,462 +1383,411 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.97</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.47</v>
+      <c r="D7" s="5">
+        <v>-7.01</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>1.53</v>
       </c>
+      <c r="D8" s="5">
+        <v>1.99</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.91</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>3.48</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>2.73</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.75</v>
+      <c r="D9" s="5">
+        <v>3.21</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-0.36</v>
       </c>
+      <c r="D10" s="5">
+        <v>1.5</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>3.77</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>5.36</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.59</v>
+      <c r="D11" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>4.71</v>
       </c>
-      <c r="E12" s="8">
-        <v>-3.66</v>
+      <c r="D12" s="5">
+        <v>5.55</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-24.41</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-23.51</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-29.11</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-27.76</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-15.84</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-10.81</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-26.29</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-24.41</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.26</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-28.56</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-29.11</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-6.91</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-6.32</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-12.48</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-10.81</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-15.76</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-15.24</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-10.76</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.59</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.75</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-30.06</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-28.99</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-17.06</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-15.76</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2425</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2440</v>
+      </c>
+      <c r="E21" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-29.37</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-27.59</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>731</v>
+      </c>
+      <c r="D22" s="5">
+        <v>739.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.3</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-30.06</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>550.95</v>
+      </c>
+      <c r="D23" s="5">
+        <v>559.4</v>
+      </c>
+      <c r="E23" s="7">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2387.7</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2425</v>
-      </c>
-      <c r="E22" s="7">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="5">
+        <v>41.02</v>
+      </c>
+      <c r="D24" s="5">
+        <v>43.27</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>713</v>
-      </c>
-      <c r="D23" s="6">
-        <v>731</v>
-      </c>
-      <c r="E23" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>55.4</v>
+      </c>
+      <c r="D25" s="5">
+        <v>58.79</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>557</v>
-      </c>
-      <c r="D24" s="6">
-        <v>550.95</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>54.78</v>
+      </c>
+      <c r="D26" s="5">
+        <v>57.89</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="5">
+        <v>36.07</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-35.2</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-71.27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>34</v>
-      </c>
-      <c r="D25" s="6">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>35.87</v>
+      </c>
+      <c r="D28" s="5">
+        <v>18.91</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-16.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>34</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>35.06</v>
-      </c>
-      <c r="D27" s="6">
-        <v>41.02</v>
-      </c>
-      <c r="E27" s="7">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>46.79</v>
-      </c>
-      <c r="D28" s="6">
-        <v>55.4</v>
-      </c>
-      <c r="E28" s="7">
-        <v>8.609999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>57.6</v>
-      </c>
-      <c r="D29" s="6">
-        <v>54.78</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-36.32</v>
-      </c>
-      <c r="D30" s="6">
-        <v>36.07</v>
-      </c>
-      <c r="E30" s="7">
-        <v>72.39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-25.33</v>
-      </c>
-      <c r="D31" s="6">
-        <v>35.87</v>
-      </c>
-      <c r="E31" s="7">
-        <v>61.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>191.18</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C29" s="5">
         <v>55.33</v>
       </c>
-      <c r="E32" s="8">
-        <v>-135.85</v>
+      <c r="D29" s="5">
+        <v>-24.16</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-79.48999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1927,60 +1813,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>50.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>53.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-0.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2082,25 +1968,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1086</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.003</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0525</v>
+      <c r="A2" s="13">
+        <v>0.1108</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0004</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.051</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="D2">
-        <v>0.62</v>
+        <v>-0.41</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -893,25 +893,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.24</v>
+        <v>-15.59</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <v>12.04</v>
       </c>
       <c r="I2">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="J2">
-        <v>-7.01</v>
+        <v>-6.9</v>
       </c>
       <c r="K2">
-        <v>-9.289999999999999</v>
+        <v>-9.33</v>
       </c>
       <c r="L2">
-        <v>-13.72</v>
+        <v>-14.49</v>
       </c>
       <c r="M2">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -920,19 +920,19 @@
         <v>39</v>
       </c>
       <c r="P2">
-        <v>2406.96</v>
+        <v>2411.16</v>
       </c>
       <c r="Q2">
-        <v>2499.07</v>
+        <v>2489.68</v>
       </c>
       <c r="R2">
-        <v>2542.64</v>
+        <v>2536.26</v>
       </c>
       <c r="S2">
-        <v>2567.06</v>
+        <v>2566.51</v>
       </c>
       <c r="T2">
-        <v>-4.95</v>
+        <v>-5.32</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +947,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.27</v>
+        <v>42.12</v>
       </c>
       <c r="Z2">
-        <v>-44.81</v>
+        <v>-42.43</v>
       </c>
       <c r="AA2">
-        <v>-39.81</v>
+        <v>-40.34</v>
       </c>
       <c r="AB2">
-        <v>-5</v>
+        <v>-2.09</v>
       </c>
       <c r="AC2">
-        <v>43.83</v>
+        <v>67</v>
       </c>
       <c r="AD2">
-        <v>22.05</v>
+        <v>42.7</v>
       </c>
       <c r="AE2">
-        <v>53.76</v>
+        <v>52.61</v>
       </c>
       <c r="AF2">
-        <v>-35.2</v>
+        <v>-35.37</v>
       </c>
       <c r="AG2">
-        <v>2694.8</v>
+        <v>2679.32</v>
       </c>
       <c r="AH2">
-        <v>2303.35</v>
+        <v>2300.03</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -983,7 +983,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>37.32</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>739.5</v>
+        <v>738.6</v>
       </c>
       <c r="D3">
-        <v>1.16</v>
+        <v>-0.12</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-26.75</v>
+        <v>-26.84</v>
       </c>
       <c r="H3">
-        <v>7.63</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>4.41</v>
+        <v>3.08</v>
       </c>
       <c r="J3">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="K3">
-        <v>-5.96</v>
+        <v>-4.65</v>
       </c>
       <c r="L3">
-        <v>-23.51</v>
+        <v>-23.58</v>
       </c>
       <c r="M3">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>724.3099999999999</v>
+        <v>728.72</v>
       </c>
       <c r="Q3">
-        <v>713.98</v>
+        <v>714.46</v>
       </c>
       <c r="R3">
-        <v>736.36</v>
+        <v>734.78</v>
       </c>
       <c r="S3">
-        <v>825.23</v>
+        <v>823.92</v>
       </c>
       <c r="T3">
-        <v>-10.39</v>
+        <v>-10.36</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>58.79</v>
+        <v>58.29</v>
       </c>
       <c r="Z3">
-        <v>-2.9</v>
+        <v>-1.03</v>
       </c>
       <c r="AA3">
-        <v>-8.01</v>
+        <v>-6.61</v>
       </c>
       <c r="AB3">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="AC3">
-        <v>93.37</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="AD3">
-        <v>93.37</v>
+        <v>95.39</v>
       </c>
       <c r="AE3">
-        <v>13.67</v>
+        <v>13.45</v>
       </c>
       <c r="AF3">
-        <v>18.91</v>
+        <v>15.58</v>
       </c>
       <c r="AG3">
-        <v>739.91</v>
+        <v>741.87</v>
       </c>
       <c r="AH3">
-        <v>688.0599999999999</v>
+        <v>687.05</v>
       </c>
       <c r="AI3">
-        <v>694.85</v>
+        <v>703.59</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>30.56</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>559.4</v>
+        <v>559.2</v>
       </c>
       <c r="D4">
-        <v>1.53</v>
+        <v>-0.04</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1119,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-28.99</v>
+        <v>-29.02</v>
       </c>
       <c r="H4">
-        <v>8.83</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I4">
-        <v>5.55</v>
+        <v>8.35</v>
       </c>
       <c r="J4">
-        <v>3.21</v>
+        <v>0.79</v>
       </c>
       <c r="K4">
-        <v>-6.32</v>
+        <v>-6.4</v>
       </c>
       <c r="L4">
-        <v>-27.76</v>
+        <v>-27.19</v>
       </c>
       <c r="M4">
-        <v>-5.1</v>
+        <v>-5.04</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>542.73</v>
+        <v>551.35</v>
       </c>
       <c r="Q4">
-        <v>539.8</v>
+        <v>540.11</v>
       </c>
       <c r="R4">
-        <v>545.79</v>
+        <v>545.5</v>
       </c>
       <c r="S4">
-        <v>629.98</v>
+        <v>629.02</v>
       </c>
       <c r="T4">
-        <v>-11.2</v>
+        <v>-11.1</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>57.89</v>
+        <v>57.78</v>
       </c>
       <c r="Z4">
-        <v>-0.42</v>
+        <v>1.08</v>
       </c>
       <c r="AA4">
-        <v>-3.71</v>
+        <v>-2.75</v>
       </c>
       <c r="AB4">
-        <v>3.29</v>
+        <v>3.83</v>
       </c>
       <c r="AC4">
-        <v>96.13</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>83.53</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="AE4">
-        <v>14.02</v>
+        <v>13.61</v>
       </c>
       <c r="AF4">
-        <v>-24.16</v>
+        <v>-52.8</v>
       </c>
       <c r="AG4">
-        <v>565.58</v>
+        <v>566.7</v>
       </c>
       <c r="AH4">
-        <v>514.02</v>
+        <v>513.52</v>
       </c>
       <c r="AI4">
-        <v>516.72</v>
+        <v>522.38</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.96</v>
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.97</v>
+        <v>-7.01</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.01</v>
+        <v>-6.9</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="D8" s="5">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="E8" s="7">
-        <v>0.46</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>2.73</v>
+        <v>3.21</v>
       </c>
       <c r="D9" s="5">
-        <v>3.21</v>
+        <v>0.79</v>
       </c>
       <c r="E9" s="7">
-        <v>0.48</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.36</v>
+        <v>1.5</v>
       </c>
       <c r="D10" s="5">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="E10" s="7">
-        <v>1.86</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>5.36</v>
+        <v>4.41</v>
       </c>
       <c r="D11" s="5">
-        <v>4.41</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.95</v>
+        <v>3.08</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,302 +1492,319 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>4.71</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="5">
-        <v>5.55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.84</v>
+        <v>8.35</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-24.41</v>
+        <v>-13.72</v>
       </c>
       <c r="D13" s="5">
-        <v>-23.51</v>
+        <v>-14.49</v>
       </c>
       <c r="E13" s="7">
-        <v>0.9</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-29.11</v>
+        <v>-23.51</v>
       </c>
       <c r="D14" s="5">
-        <v>-27.76</v>
+        <v>-23.58</v>
       </c>
       <c r="E14" s="7">
-        <v>1.35</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-10.81</v>
+        <v>-27.76</v>
       </c>
       <c r="D15" s="5">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.52</v>
+        <v>-27.19</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.26</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.96</v>
+        <v>-9.33</v>
       </c>
       <c r="E16" s="7">
-        <v>0.3</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-6.91</v>
+        <v>-5.96</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.32</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.59</v>
+        <v>-4.65</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-15.76</v>
+        <v>-6.32</v>
       </c>
       <c r="D18" s="5">
-        <v>-15.24</v>
+        <v>-6.4</v>
       </c>
       <c r="E18" s="7">
-        <v>0.52</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.59</v>
+        <v>-15.24</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.75</v>
+        <v>-15.59</v>
       </c>
       <c r="E19" s="7">
-        <v>0.84</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-30.06</v>
+        <v>-26.75</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.99</v>
+        <v>-26.84</v>
       </c>
       <c r="E20" s="7">
-        <v>1.07</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>2425</v>
+        <v>-28.99</v>
       </c>
       <c r="D21" s="5">
-        <v>2440</v>
+        <v>-29.02</v>
       </c>
       <c r="E21" s="7">
-        <v>15</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>731</v>
+        <v>2440</v>
       </c>
       <c r="D22" s="5">
-        <v>739.5</v>
+        <v>2430</v>
       </c>
       <c r="E22" s="7">
-        <v>8.5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>550.95</v>
+        <v>739.5</v>
       </c>
       <c r="D23" s="5">
-        <v>559.4</v>
+        <v>738.6</v>
       </c>
       <c r="E23" s="7">
-        <v>8.449999999999999</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>41.02</v>
+        <v>559.4</v>
       </c>
       <c r="D24" s="5">
-        <v>43.27</v>
+        <v>559.2</v>
       </c>
       <c r="E24" s="7">
-        <v>2.25</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>55.4</v>
+        <v>43.27</v>
       </c>
       <c r="D25" s="5">
-        <v>58.79</v>
+        <v>42.12</v>
       </c>
       <c r="E25" s="7">
-        <v>3.39</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>54.78</v>
+        <v>58.79</v>
       </c>
       <c r="D26" s="5">
-        <v>57.89</v>
+        <v>58.29</v>
       </c>
       <c r="E26" s="7">
-        <v>3.11</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>36.07</v>
+        <v>57.89</v>
       </c>
       <c r="D27" s="5">
-        <v>-35.2</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-71.27</v>
+        <v>57.78</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>35.87</v>
+        <v>-35.2</v>
       </c>
       <c r="D28" s="5">
-        <v>18.91</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-16.96</v>
+        <v>-35.37</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>55.33</v>
+        <v>18.91</v>
       </c>
       <c r="D29" s="5">
+        <v>15.58</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
         <v>-24.16</v>
       </c>
-      <c r="E29" s="6">
-        <v>-79.48999999999999</v>
+      <c r="D30" s="5">
+        <v>-52.8</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-28.64</v>
       </c>
     </row>
   </sheetData>
@@ -1852,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>53.3</v>
+        <v>52.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.2</v>
+        <v>-6.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1980,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1108</v>
+        <v>0.1092</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0004</v>
+        <v>0.0025</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.051</v>
+        <v>-0.0504</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -741,7 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2430</v>
+        <v>2448.3</v>
       </c>
       <c r="D2">
-        <v>-0.41</v>
+        <v>0.75</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -893,46 +894,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.59</v>
+        <v>-14.95</v>
       </c>
       <c r="H2">
-        <v>12.04</v>
+        <v>12.88</v>
       </c>
       <c r="I2">
-        <v>0.87</v>
+        <v>3.17</v>
       </c>
       <c r="J2">
-        <v>-6.9</v>
+        <v>-6.48</v>
       </c>
       <c r="K2">
-        <v>-9.33</v>
+        <v>-6.73</v>
       </c>
       <c r="L2">
-        <v>-14.49</v>
+        <v>-14.47</v>
       </c>
       <c r="M2">
-        <v>10.92</v>
+        <v>10.9</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>2411.16</v>
+        <v>2426.2</v>
       </c>
       <c r="Q2">
-        <v>2489.68</v>
+        <v>2477.19</v>
       </c>
       <c r="R2">
-        <v>2536.26</v>
+        <v>2532.03</v>
       </c>
       <c r="S2">
-        <v>2566.51</v>
+        <v>2566.05</v>
       </c>
       <c r="T2">
-        <v>-5.32</v>
+        <v>-4.59</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +948,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.12</v>
+        <v>45.01</v>
       </c>
       <c r="Z2">
-        <v>-42.43</v>
+        <v>-38.62</v>
       </c>
       <c r="AA2">
-        <v>-40.34</v>
+        <v>-39.99</v>
       </c>
       <c r="AB2">
-        <v>-2.09</v>
+        <v>1.37</v>
       </c>
       <c r="AC2">
-        <v>67</v>
+        <v>86.97</v>
       </c>
       <c r="AD2">
-        <v>42.7</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="AE2">
-        <v>52.61</v>
+        <v>50.85</v>
       </c>
       <c r="AF2">
-        <v>-35.37</v>
+        <v>-63.69</v>
       </c>
       <c r="AG2">
-        <v>2679.32</v>
+        <v>2640.07</v>
       </c>
       <c r="AH2">
-        <v>2300.03</v>
+        <v>2314.31</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -983,7 +984,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>34.33</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>738.6</v>
+        <v>737.25</v>
       </c>
       <c r="D3">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1007,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-26.84</v>
+        <v>-26.97</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="J3">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="K3">
-        <v>-4.65</v>
+        <v>-7.05</v>
       </c>
       <c r="L3">
-        <v>-23.58</v>
+        <v>-24.53</v>
       </c>
       <c r="M3">
-        <v>0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>728.72</v>
+        <v>731.87</v>
       </c>
       <c r="Q3">
-        <v>714.46</v>
+        <v>714.95</v>
       </c>
       <c r="R3">
-        <v>734.78</v>
+        <v>733.33</v>
       </c>
       <c r="S3">
-        <v>823.92</v>
+        <v>822.62</v>
       </c>
       <c r="T3">
-        <v>-10.36</v>
+        <v>-10.38</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1061,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>58.29</v>
+        <v>57.49</v>
       </c>
       <c r="Z3">
-        <v>-1.03</v>
+        <v>0.34</v>
       </c>
       <c r="AA3">
-        <v>-6.61</v>
+        <v>-5.22</v>
       </c>
       <c r="AB3">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="AC3">
-        <v>99.43000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="AD3">
-        <v>95.39</v>
+        <v>96.92</v>
       </c>
       <c r="AE3">
-        <v>13.45</v>
+        <v>13.12</v>
       </c>
       <c r="AF3">
-        <v>15.58</v>
+        <v>-25.59</v>
       </c>
       <c r="AG3">
-        <v>741.87</v>
+        <v>743.65</v>
       </c>
       <c r="AH3">
-        <v>687.05</v>
+        <v>686.25</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1096,7 +1097,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>34.16</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>559.2</v>
+        <v>561.5</v>
       </c>
       <c r="D4">
-        <v>-0.04</v>
+        <v>0.41</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1119,46 +1120,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-29.02</v>
+        <v>-28.73</v>
       </c>
       <c r="H4">
-        <v>8.789999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="I4">
-        <v>8.35</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
-        <v>0.79</v>
+        <v>1.55</v>
       </c>
       <c r="K4">
-        <v>-6.4</v>
+        <v>-5.11</v>
       </c>
       <c r="L4">
-        <v>-27.19</v>
+        <v>-28.43</v>
       </c>
       <c r="M4">
-        <v>-5.04</v>
+        <v>-4.74</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>551.35</v>
+        <v>557.61</v>
       </c>
       <c r="Q4">
-        <v>540.11</v>
+        <v>540.85</v>
       </c>
       <c r="R4">
-        <v>545.5</v>
+        <v>545.63</v>
       </c>
       <c r="S4">
-        <v>629.02</v>
+        <v>628.02</v>
       </c>
       <c r="T4">
-        <v>-11.1</v>
+        <v>-10.59</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>57.78</v>
+        <v>58.68</v>
       </c>
       <c r="Z4">
-        <v>1.08</v>
+        <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>-2.75</v>
+        <v>-1.71</v>
       </c>
       <c r="AB4">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="AC4">
-        <v>95.98999999999999</v>
+        <v>99.86</v>
       </c>
       <c r="AD4">
-        <v>93.34999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="AE4">
-        <v>13.61</v>
+        <v>13.29</v>
       </c>
       <c r="AF4">
-        <v>-52.8</v>
+        <v>-45.66</v>
       </c>
       <c r="AG4">
-        <v>566.7</v>
+        <v>568.99</v>
       </c>
       <c r="AH4">
-        <v>513.52</v>
+        <v>512.71</v>
       </c>
       <c r="AI4">
         <v>522.38</v>
@@ -1209,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>32.8</v>
+        <v>33.12</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.01</v>
+        <v>-6.9</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.9</v>
+        <v>-6.48</v>
       </c>
       <c r="E7" s="6">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="D8" s="5">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>3.21</v>
+        <v>0.79</v>
       </c>
       <c r="D9" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.42</v>
+        <v>1.55</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.76</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="D10" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.63</v>
+        <v>3.17</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>4.41</v>
+        <v>3.08</v>
       </c>
       <c r="D11" s="5">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.33</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>5.55</v>
+        <v>8.35</v>
       </c>
       <c r="D12" s="5">
-        <v>8.35</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.8</v>
+        <v>5.9</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-13.72</v>
+        <v>-14.49</v>
       </c>
       <c r="D13" s="5">
-        <v>-14.49</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.77</v>
+        <v>-14.47</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-23.51</v>
+        <v>-23.58</v>
       </c>
       <c r="D14" s="5">
-        <v>-23.58</v>
+        <v>-24.53</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-27.76</v>
+        <v>-27.19</v>
       </c>
       <c r="D15" s="5">
-        <v>-27.19</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.57</v>
+        <v>-28.43</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-9.289999999999999</v>
+        <v>-9.33</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.33</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.04</v>
+        <v>-6.73</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.96</v>
+        <v>-4.65</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.65</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.31</v>
+        <v>-7.05</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-6.32</v>
+        <v>-6.4</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.4</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.08</v>
+        <v>-5.11</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-15.24</v>
+        <v>-15.59</v>
       </c>
       <c r="D19" s="5">
-        <v>-15.59</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.35</v>
+        <v>-14.95</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-26.75</v>
+        <v>-26.84</v>
       </c>
       <c r="D20" s="5">
-        <v>-26.84</v>
+        <v>-26.97</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-28.99</v>
+        <v>-29.02</v>
       </c>
       <c r="D21" s="5">
-        <v>-29.02</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.03</v>
+        <v>-28.73</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="D22" s="5">
-        <v>2430</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-10</v>
+        <v>2448.3</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>739.5</v>
+        <v>738.6</v>
       </c>
       <c r="D23" s="5">
-        <v>738.6</v>
+        <v>737.25</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.9</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>559.4</v>
+        <v>559.2</v>
       </c>
       <c r="D24" s="5">
-        <v>559.2</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.2</v>
+        <v>561.5</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1714,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>43.27</v>
+        <v>42.12</v>
       </c>
       <c r="D25" s="5">
-        <v>42.12</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.15</v>
+        <v>45.01</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1731,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>58.79</v>
+        <v>58.29</v>
       </c>
       <c r="D26" s="5">
-        <v>58.29</v>
+        <v>57.49</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1748,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>57.89</v>
+        <v>57.78</v>
       </c>
       <c r="D27" s="5">
-        <v>57.78</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.11</v>
+        <v>58.68</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1765,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-35.2</v>
+        <v>-35.37</v>
       </c>
       <c r="D28" s="5">
-        <v>-35.37</v>
+        <v>-63.69</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.17</v>
+        <v>-28.32</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1782,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>18.91</v>
+        <v>15.58</v>
       </c>
       <c r="D29" s="5">
-        <v>15.58</v>
+        <v>-25.59</v>
       </c>
       <c r="E29" s="7">
-        <v>-3.33</v>
+        <v>-41.17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1799,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-24.16</v>
+        <v>-52.8</v>
       </c>
       <c r="D30" s="5">
-        <v>-52.8</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-28.64</v>
+        <v>-45.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>7.14</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1870,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>52.7</v>
+        <v>53.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.8</v>
+        <v>-6.3</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1998,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1092</v>
+        <v>0.109</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0025</v>
+        <v>-0.0026</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0504</v>
+        <v>-0.0474</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>58.7 → 43.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>58.7</t>
+  </si>
+  <si>
+    <t>43.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -741,8 +769,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -882,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2448.3</v>
+        <v>2380.3</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>-2.78</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -894,46 +921,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-14.95</v>
+        <v>-17.32</v>
       </c>
       <c r="H2">
-        <v>12.88</v>
+        <v>9.74</v>
       </c>
       <c r="I2">
-        <v>3.17</v>
+        <v>-0.31</v>
       </c>
       <c r="J2">
-        <v>-6.48</v>
+        <v>-11.78</v>
       </c>
       <c r="K2">
-        <v>-6.73</v>
+        <v>-10.17</v>
       </c>
       <c r="L2">
-        <v>-14.47</v>
+        <v>-16.93</v>
       </c>
       <c r="M2">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="P2">
-        <v>2426.2</v>
+        <v>2424.72</v>
       </c>
       <c r="Q2">
-        <v>2477.19</v>
+        <v>2462.81</v>
       </c>
       <c r="R2">
-        <v>2532.03</v>
+        <v>2525.05</v>
       </c>
       <c r="S2">
-        <v>2566.05</v>
+        <v>2565.34</v>
       </c>
       <c r="T2">
-        <v>-4.59</v>
+        <v>-7.21</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.01</v>
+        <v>37.5</v>
       </c>
       <c r="Z2">
-        <v>-38.62</v>
+        <v>-40.63</v>
       </c>
       <c r="AA2">
-        <v>-39.99</v>
+        <v>-40.12</v>
       </c>
       <c r="AB2">
-        <v>1.37</v>
+        <v>-0.51</v>
       </c>
       <c r="AC2">
-        <v>86.97</v>
+        <v>73.63</v>
       </c>
       <c r="AD2">
-        <v>65.93000000000001</v>
+        <v>75.86</v>
       </c>
       <c r="AE2">
-        <v>50.85</v>
+        <v>52.08</v>
       </c>
       <c r="AF2">
-        <v>-63.69</v>
+        <v>-5.01</v>
       </c>
       <c r="AG2">
-        <v>2640.07</v>
+        <v>2604.16</v>
       </c>
       <c r="AH2">
-        <v>2314.31</v>
+        <v>2321.46</v>
       </c>
       <c r="AI2">
         <v>2551.53</v>
@@ -984,7 +1011,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>31.44</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>737.25</v>
+        <v>728.9</v>
       </c>
       <c r="D3">
-        <v>-0.18</v>
+        <v>-1.13</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1007,46 +1034,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-26.97</v>
+        <v>-27.8</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.08</v>
       </c>
       <c r="I3">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="J3">
-        <v>1.13</v>
+        <v>0.19</v>
       </c>
       <c r="K3">
-        <v>-7.05</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L3">
-        <v>-24.53</v>
+        <v>-24.61</v>
       </c>
       <c r="M3">
-        <v>-0.26</v>
+        <v>-0.88</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P3">
-        <v>731.87</v>
+        <v>735.05</v>
       </c>
       <c r="Q3">
-        <v>714.95</v>
+        <v>715.03</v>
       </c>
       <c r="R3">
-        <v>733.33</v>
+        <v>731.6</v>
       </c>
       <c r="S3">
-        <v>822.62</v>
+        <v>821.25</v>
       </c>
       <c r="T3">
-        <v>-10.38</v>
+        <v>-11.24</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,34 +1088,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>57.49</v>
+        <v>52.68</v>
       </c>
       <c r="Z3">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="AA3">
-        <v>-5.22</v>
+        <v>-4.03</v>
       </c>
       <c r="AB3">
-        <v>5.56</v>
+        <v>4.77</v>
       </c>
       <c r="AC3">
-        <v>97.95</v>
+        <v>91.03</v>
       </c>
       <c r="AD3">
-        <v>96.92</v>
+        <v>96.14</v>
       </c>
       <c r="AE3">
-        <v>13.12</v>
+        <v>13.22</v>
       </c>
       <c r="AF3">
-        <v>-25.59</v>
+        <v>-6.96</v>
       </c>
       <c r="AG3">
-        <v>743.65</v>
+        <v>743.9</v>
       </c>
       <c r="AH3">
-        <v>686.25</v>
+        <v>686.17</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1097,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>35.57</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>561.5</v>
+        <v>526.9</v>
       </c>
       <c r="D4">
-        <v>0.41</v>
+        <v>-6.16</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1120,46 +1147,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-28.73</v>
+        <v>-33.12</v>
       </c>
       <c r="H4">
-        <v>9.24</v>
+        <v>2.51</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="J4">
-        <v>1.55</v>
+        <v>-3.62</v>
       </c>
       <c r="K4">
-        <v>-5.11</v>
+        <v>-10</v>
       </c>
       <c r="L4">
-        <v>-28.43</v>
+        <v>-32.64</v>
       </c>
       <c r="M4">
-        <v>-4.74</v>
+        <v>-5.98</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>557.61</v>
+        <v>551.59</v>
       </c>
       <c r="Q4">
-        <v>540.85</v>
+        <v>539.55</v>
       </c>
       <c r="R4">
-        <v>545.63</v>
+        <v>544.79</v>
       </c>
       <c r="S4">
-        <v>628.02</v>
+        <v>626.8099999999999</v>
       </c>
       <c r="T4">
-        <v>-10.59</v>
+        <v>-15.94</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,34 +1201,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>58.68</v>
+        <v>43.67</v>
       </c>
       <c r="Z4">
-        <v>2.43</v>
+        <v>0.7</v>
       </c>
       <c r="AA4">
-        <v>-1.71</v>
+        <v>-1.23</v>
       </c>
       <c r="AB4">
-        <v>4.14</v>
+        <v>1.93</v>
       </c>
       <c r="AC4">
-        <v>99.86</v>
+        <v>80.19</v>
       </c>
       <c r="AD4">
-        <v>97.33</v>
+        <v>92.02</v>
       </c>
       <c r="AE4">
-        <v>13.29</v>
+        <v>15.74</v>
       </c>
       <c r="AF4">
-        <v>-45.66</v>
+        <v>382.7</v>
       </c>
       <c r="AG4">
-        <v>568.99</v>
+        <v>567.74</v>
       </c>
       <c r="AH4">
-        <v>512.71</v>
+        <v>511.36</v>
       </c>
       <c r="AI4">
         <v>522.38</v>
@@ -1210,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.12</v>
+        <v>33.94</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1371,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1384,428 +1446,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.9</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-6.48</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.42</v>
+      <c r="D7" s="6">
+        <v>-11.78</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>1.13</v>
       </c>
+      <c r="D8" s="6">
+        <v>0.19</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.47</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>1.55</v>
       </c>
-      <c r="E9" s="6">
-        <v>0.76</v>
+      <c r="D9" s="6">
+        <v>-3.62</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-5.17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>3.17</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.3</v>
+      <c r="D10" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>3.08</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>2.18</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.9</v>
+      <c r="D11" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>8.35</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>5.9</v>
       </c>
+      <c r="D12" s="6">
+        <v>-5.4</v>
+      </c>
       <c r="E12" s="7">
-        <v>-2.45</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-14.49</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-14.47</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.02</v>
+      <c r="D13" s="6">
+        <v>-16.93</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-23.58</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-24.53</v>
       </c>
+      <c r="D14" s="6">
+        <v>-24.61</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.95</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-27.19</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-28.43</v>
       </c>
+      <c r="D15" s="6">
+        <v>-32.64</v>
+      </c>
       <c r="E15" s="7">
-        <v>-1.24</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-9.33</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-6.73</v>
       </c>
-      <c r="E16" s="6">
-        <v>2.6</v>
+      <c r="D16" s="6">
+        <v>-10.17</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-4.65</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-7.05</v>
       </c>
+      <c r="D17" s="6">
+        <v>-8.460000000000001</v>
+      </c>
       <c r="E17" s="7">
-        <v>-2.4</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-6.4</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.11</v>
       </c>
-      <c r="E18" s="6">
-        <v>1.29</v>
+      <c r="D18" s="6">
+        <v>-10</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-4.89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-15.59</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-14.95</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.64</v>
+      <c r="D19" s="6">
+        <v>-17.32</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-26.84</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-26.97</v>
       </c>
+      <c r="D20" s="6">
+        <v>-27.8</v>
+      </c>
       <c r="E20" s="7">
-        <v>-0.13</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-29.02</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-28.73</v>
       </c>
-      <c r="E21" s="6">
-        <v>0.29</v>
+      <c r="D21" s="6">
+        <v>-33.12</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-4.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2430</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2448.3</v>
       </c>
-      <c r="E22" s="6">
-        <v>18.3</v>
+      <c r="D22" s="6">
+        <v>2380.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>738.6</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>737.25</v>
       </c>
+      <c r="D23" s="6">
+        <v>728.9</v>
+      </c>
       <c r="E23" s="7">
-        <v>-1.35</v>
+        <v>-8.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>559.2</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>561.5</v>
       </c>
-      <c r="E24" s="6">
-        <v>2.3</v>
+      <c r="D24" s="6">
+        <v>526.9</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-34.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>99</v>
+      </c>
+      <c r="D25" s="6">
+        <v>66</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>99</v>
+      </c>
+      <c r="E26" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>42.12</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C27" s="6">
         <v>45.01</v>
       </c>
-      <c r="E25" s="6">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D27" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-7.51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>58.29</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C28" s="6">
         <v>57.49</v>
       </c>
-      <c r="E26" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D28" s="6">
+        <v>52.68</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>57.78</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C29" s="6">
         <v>58.68</v>
       </c>
-      <c r="E27" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D29" s="6">
+        <v>43.67</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-15.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-35.37</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C30" s="6">
         <v>-63.69</v>
       </c>
-      <c r="E28" s="7">
-        <v>-28.32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="E30" s="8">
+        <v>58.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>15.58</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C31" s="6">
         <v>-25.59</v>
       </c>
-      <c r="E29" s="7">
-        <v>-41.17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-6.96</v>
+      </c>
+      <c r="E31" s="8">
+        <v>18.63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-52.8</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C32" s="6">
         <v>-45.66</v>
       </c>
-      <c r="E30" s="6">
-        <v>7.14</v>
+      <c r="D32" s="6">
+        <v>382.7</v>
+      </c>
+      <c r="E32" s="8">
+        <v>428.36</v>
       </c>
     </row>
   </sheetData>
@@ -1831,60 +1927,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>53.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>44.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-1.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-6.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1986,25 +2082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.109</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0026</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0474</v>
+      <c r="A2" s="14">
+        <v>0.105</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.05980000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>58.7 → 43.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>58.7</t>
-  </si>
-  <si>
-    <t>43.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2380.3</v>
+        <v>2378</v>
       </c>
       <c r="D2">
-        <v>-2.78</v>
+        <v>-0.1</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -921,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.32</v>
+        <v>-17.4</v>
       </c>
       <c r="H2">
-        <v>9.74</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I2">
-        <v>-0.31</v>
+        <v>-1.94</v>
       </c>
       <c r="J2">
-        <v>-11.78</v>
+        <v>-10.87</v>
       </c>
       <c r="K2">
-        <v>-10.17</v>
+        <v>-8.77</v>
       </c>
       <c r="L2">
-        <v>-16.93</v>
+        <v>-16.6</v>
       </c>
       <c r="M2">
-        <v>10.5</v>
+        <v>10.77</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O2">
         <v>33</v>
       </c>
       <c r="P2">
-        <v>2424.72</v>
+        <v>2415.32</v>
       </c>
       <c r="Q2">
-        <v>2462.81</v>
+        <v>2452.96</v>
       </c>
       <c r="R2">
-        <v>2525.05</v>
+        <v>2520.56</v>
       </c>
       <c r="S2">
-        <v>2565.34</v>
+        <v>2564.74</v>
       </c>
       <c r="T2">
-        <v>-7.21</v>
+        <v>-7.28</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +947,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.5</v>
+        <v>37.28</v>
       </c>
       <c r="Z2">
-        <v>-40.63</v>
+        <v>-41.91</v>
       </c>
       <c r="AA2">
-        <v>-40.12</v>
+        <v>-40.48</v>
       </c>
       <c r="AB2">
-        <v>-0.51</v>
+        <v>-1.44</v>
       </c>
       <c r="AC2">
-        <v>73.63</v>
+        <v>59.14</v>
       </c>
       <c r="AD2">
-        <v>75.86</v>
+        <v>73.25</v>
       </c>
       <c r="AE2">
-        <v>52.08</v>
+        <v>50.43</v>
       </c>
       <c r="AF2">
-        <v>-5.01</v>
+        <v>-47.62</v>
       </c>
       <c r="AG2">
-        <v>2604.16</v>
+        <v>2588.74</v>
       </c>
       <c r="AH2">
-        <v>2321.46</v>
+        <v>2317.18</v>
       </c>
       <c r="AI2">
-        <v>2551.53</v>
+        <v>2532.28</v>
       </c>
       <c r="AJ2" t="s">
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>32.71</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>728.9</v>
+        <v>735.6</v>
       </c>
       <c r="D3">
-        <v>-1.13</v>
+        <v>0.92</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-27.8</v>
+        <v>-27.13</v>
       </c>
       <c r="H3">
-        <v>6.08</v>
+        <v>7.06</v>
       </c>
       <c r="I3">
-        <v>2.23</v>
+        <v>0.63</v>
       </c>
       <c r="J3">
-        <v>0.19</v>
+        <v>1.16</v>
       </c>
       <c r="K3">
-        <v>-8.460000000000001</v>
+        <v>-7.92</v>
       </c>
       <c r="L3">
-        <v>-24.61</v>
+        <v>-23.71</v>
       </c>
       <c r="M3">
-        <v>-0.88</v>
+        <v>-0.99</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>735.05</v>
+        <v>735.97</v>
       </c>
       <c r="Q3">
-        <v>715.03</v>
+        <v>716.26</v>
       </c>
       <c r="R3">
-        <v>731.6</v>
+        <v>730.15</v>
       </c>
       <c r="S3">
-        <v>821.25</v>
+        <v>819.91</v>
       </c>
       <c r="T3">
-        <v>-11.24</v>
+        <v>-10.28</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>52.68</v>
+        <v>55.87</v>
       </c>
       <c r="Z3">
-        <v>0.74</v>
+        <v>1.58</v>
       </c>
       <c r="AA3">
-        <v>-4.03</v>
+        <v>-2.91</v>
       </c>
       <c r="AB3">
-        <v>4.77</v>
+        <v>4.49</v>
       </c>
       <c r="AC3">
-        <v>91.03</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="AD3">
-        <v>96.14</v>
+        <v>92.42</v>
       </c>
       <c r="AE3">
-        <v>13.22</v>
+        <v>13.47</v>
       </c>
       <c r="AF3">
-        <v>-6.96</v>
+        <v>-38.49</v>
       </c>
       <c r="AG3">
-        <v>743.9</v>
+        <v>746.47</v>
       </c>
       <c r="AH3">
-        <v>686.17</v>
+        <v>686.0599999999999</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1124,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>33.15</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,58 +1107,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>526.9</v>
+        <v>531</v>
       </c>
       <c r="D4">
-        <v>-6.16</v>
+        <v>0.78</v>
       </c>
       <c r="E4">
-        <v>787.8</v>
+        <v>787.55</v>
       </c>
       <c r="F4">
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-33.12</v>
+        <v>-32.58</v>
       </c>
       <c r="H4">
-        <v>2.51</v>
+        <v>3.31</v>
       </c>
       <c r="I4">
-        <v>-5.4</v>
+        <v>-3.62</v>
       </c>
       <c r="J4">
-        <v>-3.62</v>
+        <v>-3.98</v>
       </c>
       <c r="K4">
-        <v>-10</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L4">
-        <v>-32.64</v>
+        <v>-32.6</v>
       </c>
       <c r="M4">
-        <v>-5.98</v>
+        <v>-5.71</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>551.59</v>
+        <v>547.6</v>
       </c>
       <c r="Q4">
-        <v>539.55</v>
+        <v>538.7</v>
       </c>
       <c r="R4">
-        <v>544.79</v>
+        <v>544.0599999999999</v>
       </c>
       <c r="S4">
-        <v>626.8099999999999</v>
+        <v>625.65</v>
       </c>
       <c r="T4">
-        <v>-15.94</v>
+        <v>-15.13</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.67</v>
+        <v>45.45</v>
       </c>
       <c r="Z4">
-        <v>0.7</v>
+        <v>-0.34</v>
       </c>
       <c r="AA4">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AB4">
-        <v>1.93</v>
+        <v>0.71</v>
       </c>
       <c r="AC4">
-        <v>80.19</v>
+        <v>62.99</v>
       </c>
       <c r="AD4">
-        <v>92.02</v>
+        <v>81.02</v>
       </c>
       <c r="AE4">
-        <v>15.74</v>
+        <v>15.94</v>
       </c>
       <c r="AF4">
-        <v>382.7</v>
+        <v>-3.79</v>
       </c>
       <c r="AG4">
-        <v>567.74</v>
+        <v>566.84</v>
       </c>
       <c r="AH4">
-        <v>511.36</v>
+        <v>510.55</v>
       </c>
       <c r="AI4">
         <v>522.38</v>
@@ -1237,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.94</v>
+        <v>34.65</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,462 +1383,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-6.48</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-11.78</v>
       </c>
-      <c r="E7" s="7">
-        <v>-5.3</v>
+      <c r="D7" s="5">
+        <v>-10.87</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>0.19</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.9399999999999999</v>
+      <c r="D8" s="5">
+        <v>1.16</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.97</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-3.62</v>
       </c>
+      <c r="D9" s="5">
+        <v>-3.98</v>
+      </c>
       <c r="E9" s="7">
-        <v>-5.17</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-0.31</v>
       </c>
+      <c r="D10" s="5">
+        <v>-1.94</v>
+      </c>
       <c r="E10" s="7">
-        <v>-3.48</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>2.23</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.05</v>
+      <c r="D11" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-5.4</v>
       </c>
-      <c r="E12" s="7">
-        <v>-11.3</v>
+      <c r="D12" s="5">
+        <v>-3.62</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-14.47</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-16.93</v>
       </c>
-      <c r="E13" s="7">
-        <v>-2.46</v>
+      <c r="D13" s="5">
+        <v>-16.6</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-24.53</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-24.61</v>
       </c>
-      <c r="E14" s="7">
+      <c r="D14" s="5">
+        <v>-23.71</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-32.64</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-32.6</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-10.17</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-8.77</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.92</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-10</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-17.32</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-17.4</v>
+      </c>
+      <c r="E19" s="7">
         <v>-0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-27.8</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-27.13</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-28.43</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-32.64</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-33.12</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-32.58</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.73</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2380.3</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2378</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>728.9</v>
+      </c>
+      <c r="D23" s="5">
+        <v>735.6</v>
+      </c>
+      <c r="E23" s="6">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.11</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-4.89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>526.9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>531</v>
+      </c>
+      <c r="E24" s="6">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-14.95</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-17.32</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5">
+        <v>66</v>
+      </c>
+      <c r="D25" s="5">
+        <v>99</v>
+      </c>
+      <c r="E25" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-26.97</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-27.8</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5">
+        <v>99</v>
+      </c>
+      <c r="D26" s="5">
+        <v>66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>37.5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>37.28</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="5">
+        <v>52.68</v>
+      </c>
+      <c r="D28" s="5">
+        <v>55.87</v>
+      </c>
+      <c r="E28" s="6">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-28.73</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-33.12</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="5">
+        <v>43.67</v>
+      </c>
+      <c r="D29" s="5">
+        <v>45.45</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2448.3</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2380.3</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-5.01</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-47.62</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-42.61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>737.25</v>
-      </c>
-      <c r="D23" s="6">
-        <v>728.9</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-8.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-6.96</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-38.49</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-31.53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>561.5</v>
-      </c>
-      <c r="D24" s="6">
-        <v>526.9</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-34.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>99</v>
-      </c>
-      <c r="D25" s="6">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>99</v>
-      </c>
-      <c r="E26" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>45.01</v>
-      </c>
-      <c r="D27" s="6">
-        <v>37.5</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-7.51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>57.49</v>
-      </c>
-      <c r="D28" s="6">
-        <v>52.68</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>58.68</v>
-      </c>
-      <c r="D29" s="6">
-        <v>43.67</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-15.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-63.69</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="E30" s="8">
-        <v>58.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-25.59</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="E31" s="8">
-        <v>18.63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-45.66</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>382.7</v>
       </c>
-      <c r="E32" s="8">
-        <v>428.36</v>
+      <c r="D32" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-386.49</v>
       </c>
     </row>
   </sheetData>
@@ -1927,60 +1864,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>46.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2082,25 +2019,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.105</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.008800000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.05980000000000001</v>
+      <c r="A2" s="13">
+        <v>0.1077</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0571</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>55.9 → 47.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>55.9</t>
+  </si>
+  <si>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,17 +386,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,58 +909,58 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2378</v>
+        <v>2302.3</v>
       </c>
       <c r="D2">
-        <v>-0.1</v>
+        <v>-3.18</v>
       </c>
       <c r="E2">
-        <v>2878.78</v>
+        <v>2839.64</v>
       </c>
       <c r="F2">
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.4</v>
+        <v>-18.92</v>
       </c>
       <c r="H2">
-        <v>9.640000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="I2">
-        <v>-1.94</v>
+        <v>-5.64</v>
       </c>
       <c r="J2">
-        <v>-10.87</v>
+        <v>-10.59</v>
       </c>
       <c r="K2">
-        <v>-8.77</v>
+        <v>-13.23</v>
       </c>
       <c r="L2">
-        <v>-16.6</v>
+        <v>-20.03</v>
       </c>
       <c r="M2">
-        <v>10.77</v>
+        <v>10.71</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P2">
-        <v>2415.32</v>
+        <v>2387.78</v>
       </c>
       <c r="Q2">
-        <v>2452.96</v>
+        <v>2439.63</v>
       </c>
       <c r="R2">
-        <v>2520.56</v>
+        <v>2513.59</v>
       </c>
       <c r="S2">
-        <v>2564.74</v>
+        <v>2563.73</v>
       </c>
       <c r="T2">
-        <v>-7.28</v>
+        <v>-10.2</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +975,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.28</v>
+        <v>30.71</v>
       </c>
       <c r="Z2">
-        <v>-41.91</v>
+        <v>-48.49</v>
       </c>
       <c r="AA2">
-        <v>-40.48</v>
+        <v>-42.08</v>
       </c>
       <c r="AB2">
-        <v>-1.44</v>
+        <v>-6.41</v>
       </c>
       <c r="AC2">
-        <v>59.14</v>
+        <v>25.81</v>
       </c>
       <c r="AD2">
-        <v>73.25</v>
+        <v>52.86</v>
       </c>
       <c r="AE2">
-        <v>50.43</v>
+        <v>52.35</v>
       </c>
       <c r="AF2">
-        <v>-47.62</v>
+        <v>28.6</v>
       </c>
       <c r="AG2">
-        <v>2588.74</v>
+        <v>2579.74</v>
       </c>
       <c r="AH2">
-        <v>2317.18</v>
+        <v>2299.51</v>
       </c>
       <c r="AI2">
-        <v>2532.28</v>
+        <v>2490.49</v>
       </c>
       <c r="AJ2" t="s">
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>34.61</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>735.6</v>
+        <v>719.05</v>
       </c>
       <c r="D3">
-        <v>0.92</v>
+        <v>-2.25</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1034,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-27.13</v>
+        <v>-28.77</v>
       </c>
       <c r="H3">
-        <v>7.06</v>
+        <v>4.65</v>
       </c>
       <c r="I3">
-        <v>0.63</v>
+        <v>-2.77</v>
       </c>
       <c r="J3">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="K3">
-        <v>-7.92</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L3">
-        <v>-23.71</v>
+        <v>-24.88</v>
       </c>
       <c r="M3">
-        <v>-0.99</v>
+        <v>-1.31</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>34</v>
       </c>
       <c r="P3">
-        <v>735.97</v>
+        <v>731.88</v>
       </c>
       <c r="Q3">
-        <v>716.26</v>
+        <v>716.2</v>
       </c>
       <c r="R3">
-        <v>730.15</v>
+        <v>728.14</v>
       </c>
       <c r="S3">
-        <v>819.91</v>
+        <v>818.52</v>
       </c>
       <c r="T3">
-        <v>-10.28</v>
+        <v>-12.15</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1088,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>55.87</v>
+        <v>47.38</v>
       </c>
       <c r="Z3">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="AA3">
-        <v>-2.91</v>
+        <v>-2.14</v>
       </c>
       <c r="AB3">
-        <v>4.49</v>
+        <v>3.05</v>
       </c>
       <c r="AC3">
-        <v>88.29000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="AD3">
-        <v>92.42</v>
+        <v>85.39</v>
       </c>
       <c r="AE3">
-        <v>13.47</v>
+        <v>13.76</v>
       </c>
       <c r="AF3">
-        <v>-38.49</v>
+        <v>-32.72</v>
       </c>
       <c r="AG3">
-        <v>746.47</v>
+        <v>746.38</v>
       </c>
       <c r="AH3">
-        <v>686.0599999999999</v>
+        <v>686.03</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1096,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>31.99</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>531</v>
+        <v>531.6</v>
       </c>
       <c r="D4">
-        <v>0.78</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1119,46 +1147,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.58</v>
+        <v>-32.5</v>
       </c>
       <c r="H4">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="I4">
-        <v>-3.62</v>
+        <v>-4.97</v>
       </c>
       <c r="J4">
-        <v>-3.98</v>
+        <v>-2.99</v>
       </c>
       <c r="K4">
-        <v>-8.960000000000001</v>
+        <v>-7.68</v>
       </c>
       <c r="L4">
-        <v>-32.6</v>
+        <v>-31.41</v>
       </c>
       <c r="M4">
-        <v>-5.71</v>
+        <v>-5.81</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>547.6</v>
+        <v>542.04</v>
       </c>
       <c r="Q4">
-        <v>538.7</v>
+        <v>537.88</v>
       </c>
       <c r="R4">
-        <v>544.0599999999999</v>
+        <v>543.42</v>
       </c>
       <c r="S4">
-        <v>625.65</v>
+        <v>624.49</v>
       </c>
       <c r="T4">
-        <v>-15.13</v>
+        <v>-14.87</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1201,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.45</v>
+        <v>45.72</v>
       </c>
       <c r="Z4">
-        <v>-0.34</v>
+        <v>-1.11</v>
       </c>
       <c r="AA4">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="AB4">
-        <v>0.71</v>
+        <v>-0.04</v>
       </c>
       <c r="AC4">
-        <v>62.99</v>
+        <v>46.01</v>
       </c>
       <c r="AD4">
-        <v>81.02</v>
+        <v>63.06</v>
       </c>
       <c r="AE4">
-        <v>15.94</v>
+        <v>15.41</v>
       </c>
       <c r="AF4">
-        <v>-3.79</v>
+        <v>-48.48</v>
       </c>
       <c r="AG4">
-        <v>566.84</v>
+        <v>565.83</v>
       </c>
       <c r="AH4">
-        <v>510.55</v>
+        <v>509.92</v>
       </c>
       <c r="AI4">
         <v>522.38</v>
@@ -1209,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>34.65</v>
+        <v>35.26</v>
       </c>
     </row>
   </sheetData>
@@ -1370,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,462 +1446,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.78</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-10.87</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.91</v>
+      <c r="D7" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>1.16</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.97</v>
+      <c r="D8" s="6">
+        <v>1.13</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
+        <v>-3.98</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.94</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.64</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
         <v>-3.62</v>
       </c>
-      <c r="D9" s="5">
-        <v>-3.98</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-4.97</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.31</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-16.6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-20.03</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2.23</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-23.71</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-24.88</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-5.4</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-32.6</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-31.41</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-16.93</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-16.6</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-8.77</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-13.23</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-4.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-24.61</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-23.71</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-7.92</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-32.64</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-32.6</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-7.68</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-10.17</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-17.4</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-18.92</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-7.92</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-27.13</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-28.77</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-10</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-32.58</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-32.5</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-17.32</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-17.4</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2378</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2302.3</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-75.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-27.8</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-27.13</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>735.6</v>
+      </c>
+      <c r="D23" s="6">
+        <v>719.05</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-16.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-33.12</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-32.58</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>531</v>
+      </c>
+      <c r="D24" s="6">
+        <v>531.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2380.3</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2378</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>99</v>
+      </c>
+      <c r="D25" s="6">
+        <v>66</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>728.9</v>
-      </c>
-      <c r="D23" s="5">
-        <v>735.6</v>
-      </c>
-      <c r="E23" s="6">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>37.28</v>
+      </c>
+      <c r="D27" s="6">
+        <v>30.71</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>55.87</v>
+      </c>
+      <c r="D28" s="6">
+        <v>47.38</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-8.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>526.9</v>
-      </c>
-      <c r="D24" s="5">
-        <v>531</v>
-      </c>
-      <c r="E24" s="6">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6">
+        <v>45.45</v>
+      </c>
+      <c r="D29" s="6">
+        <v>45.72</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>66</v>
-      </c>
-      <c r="D25" s="5">
-        <v>99</v>
-      </c>
-      <c r="E25" s="6">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-47.62</v>
+      </c>
+      <c r="D30" s="6">
+        <v>28.6</v>
+      </c>
+      <c r="E30" s="7">
+        <v>76.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>99</v>
-      </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>37.5</v>
-      </c>
-      <c r="D27" s="5">
-        <v>37.28</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>52.68</v>
-      </c>
-      <c r="D28" s="5">
-        <v>55.87</v>
-      </c>
-      <c r="E28" s="6">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-38.49</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-32.72</v>
+      </c>
+      <c r="E31" s="7">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>43.67</v>
-      </c>
-      <c r="D29" s="5">
-        <v>45.45</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-5.01</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-47.62</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-42.61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-38.49</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-31.53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>382.7</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>-3.79</v>
       </c>
-      <c r="E32" s="7">
-        <v>-386.49</v>
+      <c r="D32" s="6">
+        <v>-48.48</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-44.69</v>
       </c>
     </row>
   </sheetData>
@@ -1864,60 +1927,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-4.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2019,25 +2082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1077</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.009899999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0571</v>
+      <c r="A2" s="14">
+        <v>0.1071</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0131</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0581</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>55.9 → 47.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.9</t>
-  </si>
-  <si>
-    <t>47.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,18 +359,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2302.3</v>
+        <v>2223.3</v>
       </c>
       <c r="D2">
-        <v>-3.18</v>
+        <v>-3.43</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -921,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-18.92</v>
+        <v>-21.7</v>
       </c>
       <c r="H2">
-        <v>6.15</v>
+        <v>2.51</v>
       </c>
       <c r="I2">
-        <v>-5.64</v>
+        <v>-8.51</v>
       </c>
       <c r="J2">
-        <v>-10.59</v>
+        <v>-13.46</v>
       </c>
       <c r="K2">
-        <v>-13.23</v>
+        <v>-19.03</v>
       </c>
       <c r="L2">
-        <v>-20.03</v>
+        <v>-21.52</v>
       </c>
       <c r="M2">
-        <v>10.71</v>
+        <v>11.19</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>2387.78</v>
+        <v>2346.44</v>
       </c>
       <c r="Q2">
-        <v>2439.63</v>
+        <v>2419.69</v>
       </c>
       <c r="R2">
-        <v>2513.59</v>
+        <v>2505.15</v>
       </c>
       <c r="S2">
-        <v>2563.73</v>
+        <v>2562.08</v>
       </c>
       <c r="T2">
-        <v>-10.2</v>
+        <v>-13.22</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +947,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>30.71</v>
+        <v>25.63</v>
       </c>
       <c r="Z2">
-        <v>-48.49</v>
+        <v>-59.38</v>
       </c>
       <c r="AA2">
-        <v>-42.08</v>
+        <v>-45.54</v>
       </c>
       <c r="AB2">
-        <v>-6.41</v>
+        <v>-13.84</v>
       </c>
       <c r="AC2">
-        <v>25.81</v>
+        <v>12.6</v>
       </c>
       <c r="AD2">
-        <v>52.86</v>
+        <v>32.52</v>
       </c>
       <c r="AE2">
-        <v>52.35</v>
+        <v>54.3</v>
       </c>
       <c r="AF2">
-        <v>28.6</v>
+        <v>109.68</v>
       </c>
       <c r="AG2">
-        <v>2579.74</v>
+        <v>2563.9</v>
       </c>
       <c r="AH2">
-        <v>2299.51</v>
+        <v>2275.47</v>
       </c>
       <c r="AI2">
-        <v>2490.49</v>
+        <v>2426.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>38.8</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>719.05</v>
+        <v>722.7</v>
       </c>
       <c r="D3">
-        <v>-2.25</v>
+        <v>0.51</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-28.77</v>
+        <v>-28.41</v>
       </c>
       <c r="H3">
-        <v>4.65</v>
+        <v>5.18</v>
       </c>
       <c r="I3">
-        <v>-2.77</v>
+        <v>-2.15</v>
       </c>
       <c r="J3">
-        <v>1.13</v>
+        <v>0.33</v>
       </c>
       <c r="K3">
-        <v>-9.890000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="L3">
-        <v>-24.88</v>
+        <v>-24.01</v>
       </c>
       <c r="M3">
-        <v>-1.31</v>
+        <v>-0.95</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P3">
-        <v>731.88</v>
+        <v>728.7</v>
       </c>
       <c r="Q3">
-        <v>716.2</v>
+        <v>716.89</v>
       </c>
       <c r="R3">
-        <v>728.14</v>
+        <v>727.04</v>
       </c>
       <c r="S3">
-        <v>818.52</v>
+        <v>817.1799999999999</v>
       </c>
       <c r="T3">
-        <v>-12.15</v>
+        <v>-11.56</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.38</v>
+        <v>49.21</v>
       </c>
       <c r="Z3">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="AA3">
-        <v>-2.14</v>
+        <v>-1.59</v>
       </c>
       <c r="AB3">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="AC3">
-        <v>76.84</v>
+        <v>72.91</v>
       </c>
       <c r="AD3">
-        <v>85.39</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="AE3">
-        <v>13.76</v>
+        <v>13.95</v>
       </c>
       <c r="AF3">
-        <v>-32.72</v>
+        <v>36.47</v>
       </c>
       <c r="AG3">
-        <v>746.38</v>
+        <v>747</v>
       </c>
       <c r="AH3">
-        <v>686.03</v>
+        <v>686.78</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1124,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>29.48</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>531.6</v>
+        <v>523.55</v>
       </c>
       <c r="D4">
-        <v>0.11</v>
+        <v>-1.51</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1147,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.5</v>
+        <v>-33.52</v>
       </c>
       <c r="H4">
-        <v>3.42</v>
+        <v>1.86</v>
       </c>
       <c r="I4">
-        <v>-4.97</v>
+        <v>-6.38</v>
       </c>
       <c r="J4">
-        <v>-2.99</v>
+        <v>-4.46</v>
       </c>
       <c r="K4">
-        <v>-7.68</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L4">
-        <v>-31.41</v>
+        <v>-32.03</v>
       </c>
       <c r="M4">
-        <v>-5.81</v>
+        <v>-6.33</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>27</v>
       </c>
       <c r="P4">
-        <v>542.04</v>
+        <v>534.91</v>
       </c>
       <c r="Q4">
-        <v>537.88</v>
+        <v>536.89</v>
       </c>
       <c r="R4">
-        <v>543.42</v>
+        <v>542.6</v>
       </c>
       <c r="S4">
-        <v>624.49</v>
+        <v>623.25</v>
       </c>
       <c r="T4">
-        <v>-14.87</v>
+        <v>-16</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.72</v>
+        <v>42.67</v>
       </c>
       <c r="Z4">
-        <v>-1.11</v>
+        <v>-2.33</v>
       </c>
       <c r="AA4">
-        <v>-1.06</v>
+        <v>-1.32</v>
       </c>
       <c r="AB4">
-        <v>-0.04</v>
+        <v>-1.01</v>
       </c>
       <c r="AC4">
-        <v>46.01</v>
+        <v>44.69</v>
       </c>
       <c r="AD4">
-        <v>63.06</v>
+        <v>51.23</v>
       </c>
       <c r="AE4">
-        <v>15.41</v>
+        <v>15.24</v>
       </c>
       <c r="AF4">
-        <v>-48.48</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="AG4">
-        <v>565.83</v>
+        <v>565.42</v>
       </c>
       <c r="AH4">
-        <v>509.92</v>
+        <v>508.35</v>
       </c>
       <c r="AI4">
         <v>522.38</v>
@@ -1237,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>35.26</v>
+        <v>36.82</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,462 +1383,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.87</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-10.59</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.28</v>
+      <c r="D7" s="5">
+        <v>-13.46</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>1.13</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.03</v>
+      <c r="D8" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.98</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-2.99</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.99</v>
+      <c r="D9" s="5">
+        <v>-4.46</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-5.64</v>
       </c>
-      <c r="E10" s="8">
-        <v>-3.7</v>
+      <c r="D10" s="5">
+        <v>-8.51</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>0.63</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-2.77</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.4</v>
+      <c r="D11" s="5">
+        <v>-2.15</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.62</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-4.97</v>
       </c>
-      <c r="E12" s="8">
-        <v>-1.35</v>
+      <c r="D12" s="5">
+        <v>-6.38</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-16.6</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-20.03</v>
       </c>
-      <c r="E13" s="8">
-        <v>-3.43</v>
+      <c r="D13" s="5">
+        <v>-21.52</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-23.71</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-24.88</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.17</v>
+      <c r="D14" s="5">
+        <v>-24.01</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-32.6</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-31.41</v>
       </c>
-      <c r="E15" s="7">
-        <v>1.19</v>
+      <c r="D15" s="5">
+        <v>-32.03</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-13.23</v>
       </c>
-      <c r="E16" s="8">
-        <v>-4.46</v>
+      <c r="D16" s="5">
+        <v>-19.03</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-5.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-7.92</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-9.890000000000001</v>
       </c>
-      <c r="E17" s="8">
-        <v>-1.97</v>
+      <c r="D17" s="5">
+        <v>-9.23</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-7.68</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.28</v>
+      <c r="D18" s="5">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-17.4</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-18.92</v>
       </c>
-      <c r="E19" s="8">
-        <v>-1.52</v>
+      <c r="D19" s="5">
+        <v>-21.7</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-27.13</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-28.77</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.64</v>
+      <c r="D20" s="5">
+        <v>-28.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-32.58</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-32.5</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.08</v>
+      <c r="D21" s="5">
+        <v>-33.52</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2378</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2302.3</v>
       </c>
-      <c r="E22" s="8">
-        <v>-75.7</v>
+      <c r="D22" s="5">
+        <v>2223.3</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>735.6</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>719.05</v>
       </c>
-      <c r="E23" s="8">
-        <v>-16.55</v>
+      <c r="D23" s="5">
+        <v>722.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>531</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>531.6</v>
       </c>
-      <c r="E24" s="7">
-        <v>0.6</v>
+      <c r="D24" s="5">
+        <v>523.55</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="6">
-        <v>99</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>66</v>
       </c>
-      <c r="E25" s="8">
-        <v>-33</v>
+      <c r="D25" s="5">
+        <v>34</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5">
+        <v>34</v>
+      </c>
+      <c r="D26" s="5">
+        <v>66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>30.71</v>
+      </c>
+      <c r="D27" s="5">
+        <v>25.63</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-5.08</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>99</v>
-      </c>
-      <c r="E26" s="7">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="5">
+        <v>47.38</v>
+      </c>
+      <c r="D28" s="5">
+        <v>49.21</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="5">
+        <v>45.72</v>
+      </c>
+      <c r="D29" s="5">
+        <v>42.67</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>37.28</v>
-      </c>
-      <c r="D27" s="6">
-        <v>30.71</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
+        <v>28.6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>109.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>81.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>55.87</v>
-      </c>
-      <c r="D28" s="6">
-        <v>47.38</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-8.49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-32.72</v>
+      </c>
+      <c r="D31" s="5">
+        <v>36.47</v>
+      </c>
+      <c r="E31" s="7">
+        <v>69.19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>45.45</v>
-      </c>
-      <c r="D29" s="6">
-        <v>45.72</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-47.62</v>
-      </c>
-      <c r="D30" s="6">
-        <v>28.6</v>
-      </c>
-      <c r="E30" s="7">
-        <v>76.22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-38.49</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-32.72</v>
-      </c>
-      <c r="E31" s="7">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>-48.48</v>
       </c>
-      <c r="E32" s="8">
-        <v>-44.69</v>
+      <c r="D32" s="5">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="E32" s="7">
+        <v>120.24</v>
       </c>
     </row>
   </sheetData>
@@ -1927,60 +1864,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-10.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2082,25 +2019,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1071</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0131</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0581</v>
+      <c r="A2" s="13">
+        <v>0.1119</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0095</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0633</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.6 → 34.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.6</t>
+  </si>
+  <si>
+    <t>34.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2223.3</v>
+        <v>2280.7</v>
       </c>
       <c r="D2">
-        <v>-3.43</v>
+        <v>2.58</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -893,46 +921,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-21.7</v>
+        <v>-19.68</v>
       </c>
       <c r="H2">
-        <v>2.51</v>
+        <v>5.15</v>
       </c>
       <c r="I2">
-        <v>-8.51</v>
+        <v>-6.85</v>
       </c>
       <c r="J2">
-        <v>-13.46</v>
+        <v>-13.02</v>
       </c>
       <c r="K2">
-        <v>-19.03</v>
+        <v>-17.35</v>
       </c>
       <c r="L2">
-        <v>-21.52</v>
+        <v>-18.95</v>
       </c>
       <c r="M2">
-        <v>11.19</v>
+        <v>11.73</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P2">
-        <v>2346.44</v>
+        <v>2312.92</v>
       </c>
       <c r="Q2">
-        <v>2419.69</v>
+        <v>2406.48</v>
       </c>
       <c r="R2">
-        <v>2505.15</v>
+        <v>2499.15</v>
       </c>
       <c r="S2">
-        <v>2562.08</v>
+        <v>2560.45</v>
       </c>
       <c r="T2">
-        <v>-13.22</v>
+        <v>-10.93</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.63</v>
+        <v>34.15</v>
       </c>
       <c r="Z2">
-        <v>-59.38</v>
+        <v>-62.67</v>
       </c>
       <c r="AA2">
-        <v>-45.54</v>
+        <v>-48.97</v>
       </c>
       <c r="AB2">
-        <v>-13.84</v>
+        <v>-13.7</v>
       </c>
       <c r="AC2">
-        <v>12.6</v>
+        <v>14.65</v>
       </c>
       <c r="AD2">
-        <v>32.52</v>
+        <v>17.69</v>
       </c>
       <c r="AE2">
-        <v>54.3</v>
+        <v>56.9</v>
       </c>
       <c r="AF2">
-        <v>109.68</v>
+        <v>38.09</v>
       </c>
       <c r="AG2">
-        <v>2563.9</v>
+        <v>2550.8</v>
       </c>
       <c r="AH2">
-        <v>2275.47</v>
+        <v>2262.15</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -983,7 +1011,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>43.91</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>722.7</v>
+        <v>708.7</v>
       </c>
       <c r="D3">
-        <v>0.51</v>
+        <v>-1.94</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1034,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-28.41</v>
+        <v>-29.8</v>
       </c>
       <c r="H3">
-        <v>5.18</v>
+        <v>3.14</v>
       </c>
       <c r="I3">
-        <v>-2.15</v>
+        <v>-3.87</v>
       </c>
       <c r="J3">
-        <v>0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="K3">
-        <v>-9.23</v>
+        <v>-10.96</v>
       </c>
       <c r="L3">
-        <v>-24.01</v>
+        <v>-25.39</v>
       </c>
       <c r="M3">
-        <v>-0.95</v>
+        <v>-1.35</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P3">
-        <v>728.7</v>
+        <v>722.99</v>
       </c>
       <c r="Q3">
-        <v>716.89</v>
+        <v>716.73</v>
       </c>
       <c r="R3">
-        <v>727.04</v>
+        <v>725.98</v>
       </c>
       <c r="S3">
-        <v>817.1799999999999</v>
+        <v>815.72</v>
       </c>
       <c r="T3">
-        <v>-11.56</v>
+        <v>-13.12</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1088,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>49.21</v>
+        <v>43.02</v>
       </c>
       <c r="Z3">
-        <v>0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AA3">
-        <v>-1.59</v>
+        <v>-1.4</v>
       </c>
       <c r="AB3">
-        <v>2.24</v>
+        <v>0.73</v>
       </c>
       <c r="AC3">
-        <v>72.91</v>
+        <v>54.59</v>
       </c>
       <c r="AD3">
-        <v>79.34999999999999</v>
+        <v>68.11</v>
       </c>
       <c r="AE3">
         <v>13.95</v>
       </c>
       <c r="AF3">
-        <v>36.47</v>
+        <v>21.83</v>
       </c>
       <c r="AG3">
-        <v>747</v>
+        <v>746.98</v>
       </c>
       <c r="AH3">
-        <v>686.78</v>
+        <v>686.47</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1096,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>26.84</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>523.55</v>
+        <v>521.2</v>
       </c>
       <c r="D4">
-        <v>-1.51</v>
+        <v>-0.45</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1119,46 +1147,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-33.52</v>
+        <v>-33.82</v>
       </c>
       <c r="H4">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>-6.38</v>
+        <v>-7.18</v>
       </c>
       <c r="J4">
-        <v>-4.46</v>
+        <v>-4.08</v>
       </c>
       <c r="K4">
-        <v>-8.140000000000001</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L4">
-        <v>-32.03</v>
+        <v>-31.87</v>
       </c>
       <c r="M4">
-        <v>-6.33</v>
+        <v>-6.09</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>534.91</v>
+        <v>526.85</v>
       </c>
       <c r="Q4">
-        <v>536.89</v>
+        <v>535.9299999999999</v>
       </c>
       <c r="R4">
-        <v>542.6</v>
+        <v>541.8</v>
       </c>
       <c r="S4">
-        <v>623.25</v>
+        <v>621.98</v>
       </c>
       <c r="T4">
-        <v>-16</v>
+        <v>-16.2</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.67</v>
+        <v>41.79</v>
       </c>
       <c r="Z4">
-        <v>-2.33</v>
+        <v>-3.45</v>
       </c>
       <c r="AA4">
-        <v>-1.32</v>
+        <v>-1.75</v>
       </c>
       <c r="AB4">
-        <v>-1.01</v>
+        <v>-1.71</v>
       </c>
       <c r="AC4">
-        <v>44.69</v>
+        <v>34.8</v>
       </c>
       <c r="AD4">
-        <v>51.23</v>
+        <v>41.83</v>
       </c>
       <c r="AE4">
-        <v>15.24</v>
+        <v>14.88</v>
       </c>
       <c r="AF4">
-        <v>71.76000000000001</v>
+        <v>6.91</v>
       </c>
       <c r="AG4">
-        <v>565.42</v>
+        <v>565.26</v>
       </c>
       <c r="AH4">
-        <v>508.35</v>
+        <v>506.61</v>
       </c>
       <c r="AI4">
-        <v>522.38</v>
+        <v>561.9299999999999</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK4">
-        <v>36.82</v>
+        <v>38.84</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,462 +1446,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-10.59</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-13.46</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.87</v>
+      <c r="D7" s="6">
+        <v>-13.02</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.13</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>0.33</v>
       </c>
-      <c r="E8" s="6">
+      <c r="D8" s="6">
+        <v>-0.04</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-4.46</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-4.08</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.85</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.87</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.38</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7.18</v>
+      </c>
+      <c r="E12" s="8">
         <v>-0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-21.52</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-18.95</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-24.01</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-25.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-4.46</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-32.03</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-31.87</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-5.64</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-19.03</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-17.35</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.15</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-10.96</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-4.97</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-20.03</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-21.52</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-21.7</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-19.68</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-24.88</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-24.01</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-28.41</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-29.8</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-31.41</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-32.03</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-33.52</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-33.82</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-13.23</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-19.03</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2223.3</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2280.7</v>
+      </c>
+      <c r="E22" s="7">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-9.23</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>722.7</v>
+      </c>
+      <c r="D23" s="6">
+        <v>708.7</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-7.68</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>523.55</v>
+      </c>
+      <c r="D24" s="6">
+        <v>521.2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-18.92</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-21.7</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>25.63</v>
+      </c>
+      <c r="D25" s="6">
+        <v>34.15</v>
+      </c>
+      <c r="E25" s="7">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-28.77</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-28.41</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>49.21</v>
+      </c>
+      <c r="D26" s="6">
+        <v>43.02</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-6.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-32.5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-33.52</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>42.67</v>
+      </c>
+      <c r="D27" s="6">
+        <v>41.79</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2302.3</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2223.3</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>109.68</v>
+      </c>
+      <c r="D28" s="6">
+        <v>38.09</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-71.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>719.05</v>
-      </c>
-      <c r="D23" s="5">
-        <v>722.7</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>36.47</v>
+      </c>
+      <c r="D29" s="6">
+        <v>21.83</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-14.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>531.6</v>
-      </c>
-      <c r="D24" s="5">
-        <v>523.55</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>66</v>
-      </c>
-      <c r="D25" s="5">
-        <v>34</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>34</v>
-      </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="D27" s="5">
-        <v>25.63</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-5.08</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>47.38</v>
-      </c>
-      <c r="D28" s="5">
-        <v>49.21</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>45.72</v>
-      </c>
-      <c r="D29" s="5">
-        <v>42.67</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>28.6</v>
-      </c>
-      <c r="D30" s="5">
-        <v>109.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>81.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-32.72</v>
-      </c>
-      <c r="D31" s="5">
-        <v>36.47</v>
-      </c>
-      <c r="E31" s="7">
-        <v>69.19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-48.48</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C30" s="6">
         <v>71.76000000000001</v>
       </c>
-      <c r="E32" s="7">
-        <v>120.24</v>
+      <c r="D30" s="6">
+        <v>6.91</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-64.84999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1864,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>39.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-5.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-12.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-12.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2019,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1119</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0095</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0633</v>
+      <c r="A2" s="14">
+        <v>0.1173</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0135</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0609</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.6 → 34.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.6</t>
-  </si>
-  <si>
-    <t>34.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,7 +741,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -909,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2280.7</v>
+        <v>2308.1</v>
       </c>
       <c r="D2">
-        <v>2.58</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -921,46 +895,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.68</v>
+        <v>-18.72</v>
       </c>
       <c r="H2">
-        <v>5.15</v>
+        <v>6.42</v>
       </c>
       <c r="I2">
-        <v>-6.85</v>
+        <v>-3.03</v>
       </c>
       <c r="J2">
-        <v>-13.02</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="K2">
-        <v>-17.35</v>
+        <v>-17.57</v>
       </c>
       <c r="L2">
-        <v>-18.95</v>
+        <v>-16.08</v>
       </c>
       <c r="M2">
-        <v>11.73</v>
+        <v>11.82</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P2">
-        <v>2312.92</v>
+        <v>2298.48</v>
       </c>
       <c r="Q2">
-        <v>2406.48</v>
+        <v>2395.6</v>
       </c>
       <c r="R2">
-        <v>2499.15</v>
+        <v>2494.39</v>
       </c>
       <c r="S2">
-        <v>2560.45</v>
+        <v>2558.9</v>
       </c>
       <c r="T2">
-        <v>-10.93</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,34 +949,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.15</v>
+        <v>37.81</v>
       </c>
       <c r="Z2">
-        <v>-62.67</v>
+        <v>-62.34</v>
       </c>
       <c r="AA2">
-        <v>-48.97</v>
+        <v>-51.64</v>
       </c>
       <c r="AB2">
-        <v>-13.7</v>
+        <v>-10.7</v>
       </c>
       <c r="AC2">
-        <v>14.65</v>
+        <v>35.61</v>
       </c>
       <c r="AD2">
-        <v>17.69</v>
+        <v>20.95</v>
       </c>
       <c r="AE2">
-        <v>56.9</v>
+        <v>56.51</v>
       </c>
       <c r="AF2">
-        <v>38.09</v>
+        <v>71.33</v>
       </c>
       <c r="AG2">
-        <v>2550.8</v>
+        <v>2534.79</v>
       </c>
       <c r="AH2">
-        <v>2262.15</v>
+        <v>2256.4</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1011,7 +985,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>47.13</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>708.7</v>
+        <v>721.2</v>
       </c>
       <c r="D3">
-        <v>-1.94</v>
+        <v>1.76</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1008,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.8</v>
+        <v>-28.56</v>
       </c>
       <c r="H3">
-        <v>3.14</v>
+        <v>4.96</v>
       </c>
       <c r="I3">
-        <v>-3.87</v>
+        <v>-1.06</v>
       </c>
       <c r="J3">
-        <v>-0.04</v>
+        <v>1.31</v>
       </c>
       <c r="K3">
-        <v>-10.96</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L3">
-        <v>-25.39</v>
+        <v>-23.69</v>
       </c>
       <c r="M3">
-        <v>-1.35</v>
+        <v>-0.85</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P3">
-        <v>722.99</v>
+        <v>721.45</v>
       </c>
       <c r="Q3">
-        <v>716.73</v>
+        <v>717.75</v>
       </c>
       <c r="R3">
-        <v>725.98</v>
+        <v>725.34</v>
       </c>
       <c r="S3">
-        <v>815.72</v>
+        <v>814.3200000000001</v>
       </c>
       <c r="T3">
-        <v>-13.12</v>
+        <v>-11.44</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1062,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.02</v>
+        <v>49.17</v>
       </c>
       <c r="Z3">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="AA3">
-        <v>-1.4</v>
+        <v>-1.26</v>
       </c>
       <c r="AB3">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC3">
-        <v>54.59</v>
+        <v>47.17</v>
       </c>
       <c r="AD3">
-        <v>68.11</v>
+        <v>58.22</v>
       </c>
       <c r="AE3">
-        <v>13.95</v>
+        <v>13.97</v>
       </c>
       <c r="AF3">
-        <v>21.83</v>
+        <v>22.14</v>
       </c>
       <c r="AG3">
-        <v>746.98</v>
+        <v>747.1</v>
       </c>
       <c r="AH3">
-        <v>686.47</v>
+        <v>688.39</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1124,7 +1098,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>24.54</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>521.2</v>
+        <v>534.2</v>
       </c>
       <c r="D4">
-        <v>-0.45</v>
+        <v>2.49</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1147,46 +1121,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-33.82</v>
+        <v>-32.17</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
       <c r="I4">
-        <v>-7.18</v>
+        <v>1.39</v>
       </c>
       <c r="J4">
-        <v>-4.08</v>
+        <v>-1.13</v>
       </c>
       <c r="K4">
-        <v>-8.779999999999999</v>
+        <v>-5.9</v>
       </c>
       <c r="L4">
-        <v>-31.87</v>
+        <v>-30.12</v>
       </c>
       <c r="M4">
-        <v>-6.09</v>
+        <v>-5.81</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>526.85</v>
+        <v>528.3099999999999</v>
       </c>
       <c r="Q4">
-        <v>535.9299999999999</v>
+        <v>535.99</v>
       </c>
       <c r="R4">
-        <v>541.8</v>
+        <v>541.42</v>
       </c>
       <c r="S4">
-        <v>621.98</v>
+        <v>620.77</v>
       </c>
       <c r="T4">
-        <v>-16.2</v>
+        <v>-13.95</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1175,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.79</v>
+        <v>48.15</v>
       </c>
       <c r="Z4">
-        <v>-3.45</v>
+        <v>-3.26</v>
       </c>
       <c r="AA4">
-        <v>-1.75</v>
+        <v>-2.05</v>
       </c>
       <c r="AB4">
-        <v>-1.71</v>
+        <v>-1.21</v>
       </c>
       <c r="AC4">
         <v>34.8</v>
       </c>
       <c r="AD4">
-        <v>41.83</v>
+        <v>38.1</v>
       </c>
       <c r="AE4">
-        <v>14.88</v>
+        <v>15.35</v>
       </c>
       <c r="AF4">
-        <v>6.91</v>
+        <v>-16.5</v>
       </c>
       <c r="AG4">
-        <v>565.26</v>
+        <v>565.3</v>
       </c>
       <c r="AH4">
-        <v>506.61</v>
+        <v>506.69</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1237,7 +1211,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>38.84</v>
+        <v>35.11</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,428 +1385,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-13.46</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-13.02</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.44</v>
+      <c r="D7" s="5">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.72</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-0.04</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.37</v>
+      <c r="D8" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.46</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-4.08</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.38</v>
+      <c r="D9" s="5">
+        <v>-1.13</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-6.85</v>
       </c>
-      <c r="E10" s="7">
-        <v>1.66</v>
+      <c r="D10" s="5">
+        <v>-3.03</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-3.87</v>
       </c>
-      <c r="E11" s="8">
-        <v>-1.72</v>
+      <c r="D11" s="5">
+        <v>-1.06</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2.81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-7.18</v>
       </c>
-      <c r="E12" s="8">
-        <v>-0.8</v>
+      <c r="D12" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="E12" s="6">
+        <v>8.57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-21.52</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-18.95</v>
       </c>
-      <c r="E13" s="7">
-        <v>2.57</v>
+      <c r="D13" s="5">
+        <v>-16.08</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-24.01</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-25.39</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.38</v>
+      <c r="D14" s="5">
+        <v>-23.69</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-32.03</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-31.87</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.16</v>
+      <c r="D15" s="5">
+        <v>-30.12</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-19.03</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-17.35</v>
       </c>
+      <c r="D16" s="5">
+        <v>-17.57</v>
+      </c>
       <c r="E16" s="7">
-        <v>1.68</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-10.96</v>
       </c>
-      <c r="E17" s="8">
-        <v>-1.73</v>
+      <c r="D17" s="5">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-8.779999999999999</v>
       </c>
-      <c r="E18" s="8">
-        <v>-0.64</v>
+      <c r="D18" s="5">
+        <v>-5.9</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.88</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-21.7</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-19.68</v>
       </c>
-      <c r="E19" s="7">
-        <v>2.02</v>
+      <c r="D19" s="5">
+        <v>-18.72</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-28.41</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-29.8</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.39</v>
+      <c r="D20" s="5">
+        <v>-28.56</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.24</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-33.52</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-33.82</v>
       </c>
-      <c r="E21" s="8">
-        <v>-0.3</v>
+      <c r="D21" s="5">
+        <v>-32.17</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2223.3</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2280.7</v>
       </c>
-      <c r="E22" s="7">
-        <v>57.4</v>
+      <c r="D22" s="5">
+        <v>2308.1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>27.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>722.7</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>708.7</v>
       </c>
-      <c r="E23" s="8">
-        <v>-14</v>
+      <c r="D23" s="5">
+        <v>721.2</v>
+      </c>
+      <c r="E23" s="6">
+        <v>12.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>523.55</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>521.2</v>
       </c>
-      <c r="E24" s="8">
-        <v>-2.35</v>
+      <c r="D24" s="5">
+        <v>534.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>25.63</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>34.15</v>
       </c>
-      <c r="E25" s="7">
-        <v>8.52</v>
+      <c r="D25" s="5">
+        <v>37.81</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>49.21</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>43.02</v>
       </c>
-      <c r="E26" s="8">
-        <v>-6.19</v>
+      <c r="D26" s="5">
+        <v>49.17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>6.15</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>42.67</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>41.79</v>
       </c>
-      <c r="E27" s="8">
-        <v>-0.88</v>
+      <c r="D27" s="5">
+        <v>48.15</v>
+      </c>
+      <c r="E27" s="6">
+        <v>6.36</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>109.68</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>38.09</v>
       </c>
-      <c r="E28" s="8">
-        <v>-71.59</v>
+      <c r="D28" s="5">
+        <v>71.33</v>
+      </c>
+      <c r="E28" s="6">
+        <v>33.24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>36.47</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>21.83</v>
       </c>
-      <c r="E29" s="8">
-        <v>-14.64</v>
+      <c r="D29" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.31</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>71.76000000000001</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>6.91</v>
       </c>
-      <c r="E30" s="8">
-        <v>-64.84999999999999</v>
+      <c r="D30" s="5">
+        <v>-16.5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-23.41</v>
       </c>
     </row>
   </sheetData>
@@ -1893,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-12.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-11.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2048,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1173</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0135</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0609</v>
+      <c r="A2" s="13">
+        <v>0.1182</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0581</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -741,9 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -883,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2308.1</v>
+        <v>2346</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -895,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-18.72</v>
+        <v>-17.38</v>
       </c>
       <c r="H2">
-        <v>6.42</v>
+        <v>8.16</v>
       </c>
       <c r="I2">
-        <v>-3.03</v>
+        <v>-1.35</v>
       </c>
       <c r="J2">
-        <v>-9.300000000000001</v>
+        <v>-7.11</v>
       </c>
       <c r="K2">
-        <v>-17.57</v>
+        <v>-15.41</v>
       </c>
       <c r="L2">
-        <v>-16.08</v>
+        <v>-14.73</v>
       </c>
       <c r="M2">
-        <v>11.82</v>
+        <v>12.38</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>2298.48</v>
+        <v>2292.08</v>
       </c>
       <c r="Q2">
-        <v>2395.6</v>
+        <v>2387.36</v>
       </c>
       <c r="R2">
-        <v>2494.39</v>
+        <v>2491.13</v>
       </c>
       <c r="S2">
-        <v>2558.9</v>
+        <v>2557.88</v>
       </c>
       <c r="T2">
-        <v>-9.800000000000001</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +947,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.81</v>
+        <v>42.57</v>
       </c>
       <c r="Z2">
-        <v>-62.34</v>
+        <v>-58.35</v>
       </c>
       <c r="AA2">
-        <v>-51.64</v>
+        <v>-52.98</v>
       </c>
       <c r="AB2">
-        <v>-10.7</v>
+        <v>-5.37</v>
       </c>
       <c r="AC2">
-        <v>35.61</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="AD2">
-        <v>20.95</v>
+        <v>38.33</v>
       </c>
       <c r="AE2">
-        <v>56.51</v>
+        <v>56.86</v>
       </c>
       <c r="AF2">
-        <v>71.33</v>
+        <v>85.37</v>
       </c>
       <c r="AG2">
-        <v>2534.79</v>
+        <v>2517.03</v>
       </c>
       <c r="AH2">
-        <v>2256.4</v>
+        <v>2257.68</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -985,7 +983,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>49.11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>721.2</v>
+        <v>704.8</v>
       </c>
       <c r="D3">
-        <v>1.76</v>
+        <v>-2.27</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1008,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-28.56</v>
+        <v>-30.18</v>
       </c>
       <c r="H3">
-        <v>4.96</v>
+        <v>2.58</v>
       </c>
       <c r="I3">
-        <v>-1.06</v>
+        <v>-4.19</v>
       </c>
       <c r="J3">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="K3">
-        <v>-9.970000000000001</v>
+        <v>-15.07</v>
       </c>
       <c r="L3">
-        <v>-23.69</v>
+        <v>-25.83</v>
       </c>
       <c r="M3">
-        <v>-0.85</v>
+        <v>-1.47</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>721.45</v>
+        <v>715.29</v>
       </c>
       <c r="Q3">
-        <v>717.75</v>
+        <v>717.65</v>
       </c>
       <c r="R3">
-        <v>725.34</v>
+        <v>724.5</v>
       </c>
       <c r="S3">
-        <v>814.3200000000001</v>
+        <v>812.87</v>
       </c>
       <c r="T3">
-        <v>-11.44</v>
+        <v>-13.29</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>49.17</v>
+        <v>42.67</v>
       </c>
       <c r="Z3">
-        <v>-0.7</v>
+        <v>-2.02</v>
       </c>
       <c r="AA3">
-        <v>-1.26</v>
+        <v>-1.41</v>
       </c>
       <c r="AB3">
-        <v>0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="AC3">
-        <v>47.17</v>
+        <v>24.69</v>
       </c>
       <c r="AD3">
-        <v>58.22</v>
+        <v>42.15</v>
       </c>
       <c r="AE3">
-        <v>13.97</v>
+        <v>15.33</v>
       </c>
       <c r="AF3">
-        <v>22.14</v>
+        <v>119.62</v>
       </c>
       <c r="AG3">
-        <v>747.1</v>
+        <v>747.17</v>
       </c>
       <c r="AH3">
-        <v>688.39</v>
+        <v>688.14</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1098,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>22.97</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>534.2</v>
+        <v>531</v>
       </c>
       <c r="D4">
-        <v>2.49</v>
+        <v>-0.6</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1121,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.17</v>
+        <v>-32.58</v>
       </c>
       <c r="H4">
-        <v>3.93</v>
+        <v>3.31</v>
       </c>
       <c r="I4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-1.13</v>
+        <v>-0.38</v>
       </c>
       <c r="K4">
-        <v>-5.9</v>
+        <v>-5.88</v>
       </c>
       <c r="L4">
-        <v>-30.12</v>
+        <v>-29.82</v>
       </c>
       <c r="M4">
-        <v>-5.81</v>
+        <v>-6.02</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P4">
         <v>528.3099999999999</v>
       </c>
       <c r="Q4">
-        <v>535.99</v>
+        <v>535.87</v>
       </c>
       <c r="R4">
-        <v>541.42</v>
+        <v>541.02</v>
       </c>
       <c r="S4">
-        <v>620.77</v>
+        <v>619.5599999999999</v>
       </c>
       <c r="T4">
-        <v>-13.95</v>
+        <v>-14.29</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>48.15</v>
+        <v>46.79</v>
       </c>
       <c r="Z4">
-        <v>-3.26</v>
+        <v>-3.32</v>
       </c>
       <c r="AA4">
-        <v>-2.05</v>
+        <v>-2.3</v>
       </c>
       <c r="AB4">
-        <v>-1.21</v>
+        <v>-1.02</v>
       </c>
       <c r="AC4">
-        <v>34.8</v>
+        <v>36.62</v>
       </c>
       <c r="AD4">
-        <v>38.1</v>
+        <v>35.41</v>
       </c>
       <c r="AE4">
-        <v>15.35</v>
+        <v>15.29</v>
       </c>
       <c r="AF4">
-        <v>-16.5</v>
+        <v>-30.22</v>
       </c>
       <c r="AG4">
-        <v>565.3</v>
+        <v>565.24</v>
       </c>
       <c r="AH4">
-        <v>506.69</v>
+        <v>506.5</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1211,7 +1209,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>35.11</v>
+        <v>31.83</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-13.02</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.300000000000001</v>
+        <v>-7.11</v>
       </c>
       <c r="E7" s="6">
-        <v>3.72</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.04</v>
+        <v>1.31</v>
       </c>
       <c r="D8" s="5">
-        <v>1.31</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.35</v>
+        <v>0.57</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-4.08</v>
+        <v>-1.13</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.13</v>
+        <v>-0.38</v>
       </c>
       <c r="E9" s="6">
-        <v>2.95</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.85</v>
+        <v>-3.03</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.03</v>
+        <v>-1.35</v>
       </c>
       <c r="E10" s="6">
-        <v>3.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.87</v>
+        <v>-1.06</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2.81</v>
+        <v>-4.19</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-7.18</v>
+        <v>1.39</v>
       </c>
       <c r="D12" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="E12" s="6">
-        <v>8.57</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-18.95</v>
+        <v>-16.08</v>
       </c>
       <c r="D13" s="5">
-        <v>-16.08</v>
+        <v>-14.73</v>
       </c>
       <c r="E13" s="6">
-        <v>2.87</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.39</v>
+        <v>-23.69</v>
       </c>
       <c r="D14" s="5">
-        <v>-23.69</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.7</v>
+        <v>-25.83</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-31.87</v>
+        <v>-30.12</v>
       </c>
       <c r="D15" s="5">
-        <v>-30.12</v>
+        <v>-29.82</v>
       </c>
       <c r="E15" s="6">
-        <v>1.75</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-17.35</v>
+        <v>-17.57</v>
       </c>
       <c r="D16" s="5">
-        <v>-17.57</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.22</v>
+        <v>-15.41</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-10.96</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D17" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.99</v>
+        <v>-15.07</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-5.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-8.779999999999999</v>
+        <v>-5.9</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.9</v>
+        <v>-5.88</v>
       </c>
       <c r="E18" s="6">
-        <v>2.88</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-19.68</v>
+        <v>-18.72</v>
       </c>
       <c r="D19" s="5">
-        <v>-18.72</v>
+        <v>-17.38</v>
       </c>
       <c r="E19" s="6">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-29.8</v>
+        <v>-28.56</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.56</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.24</v>
+        <v>-30.18</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.82</v>
+        <v>-32.17</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.17</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.65</v>
+        <v>-32.58</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2280.7</v>
+        <v>2308.1</v>
       </c>
       <c r="D22" s="5">
-        <v>2308.1</v>
+        <v>2346</v>
       </c>
       <c r="E22" s="6">
-        <v>27.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>708.7</v>
+        <v>721.2</v>
       </c>
       <c r="D23" s="5">
-        <v>721.2</v>
-      </c>
-      <c r="E23" s="6">
-        <v>12.5</v>
+        <v>704.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-16.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>521.2</v>
+        <v>534.2</v>
       </c>
       <c r="D24" s="5">
-        <v>534.2</v>
-      </c>
-      <c r="E24" s="6">
-        <v>13</v>
+        <v>531</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1712,16 +1710,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>34.15</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5">
-        <v>37.81</v>
+        <v>99</v>
       </c>
       <c r="E25" s="6">
-        <v>3.66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1729,84 +1727,118 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>43.02</v>
+        <v>99</v>
       </c>
       <c r="D26" s="5">
-        <v>49.17</v>
-      </c>
-      <c r="E26" s="6">
-        <v>6.15</v>
+        <v>34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>41.79</v>
+        <v>37.81</v>
       </c>
       <c r="D27" s="5">
-        <v>48.15</v>
+        <v>42.57</v>
       </c>
       <c r="E27" s="6">
-        <v>6.36</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>38.09</v>
+        <v>49.17</v>
       </c>
       <c r="D28" s="5">
-        <v>71.33</v>
-      </c>
-      <c r="E28" s="6">
-        <v>33.24</v>
+        <v>42.67</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>21.83</v>
+        <v>48.15</v>
       </c>
       <c r="D29" s="5">
-        <v>22.14</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.31</v>
+        <v>46.79</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>6.91</v>
+        <v>71.33</v>
       </c>
       <c r="D30" s="5">
+        <v>85.37</v>
+      </c>
+      <c r="E30" s="6">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="D31" s="5">
+        <v>119.62</v>
+      </c>
+      <c r="E31" s="6">
+        <v>97.48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
         <v>-16.5</v>
       </c>
-      <c r="E30" s="7">
-        <v>-23.41</v>
+      <c r="D32" s="5">
+        <v>-30.22</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-13.72</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1903,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3</v>
+        <v>-2.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-11.1</v>
+        <v>-12.1</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +2031,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1182</v>
+        <v>0.1238</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.008500000000000001</v>
+        <v>-0.0147</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0581</v>
+        <v>-0.0602</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.8 → 52.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.8</t>
+  </si>
+  <si>
+    <t>52.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -741,7 +769,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +910,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2346</v>
+        <v>2352.4</v>
       </c>
       <c r="D2">
-        <v>1.64</v>
+        <v>0.27</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -893,46 +922,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.38</v>
+        <v>-17.16</v>
       </c>
       <c r="H2">
-        <v>8.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I2">
-        <v>-1.35</v>
+        <v>2.18</v>
       </c>
       <c r="J2">
-        <v>-7.11</v>
+        <v>-6.31</v>
       </c>
       <c r="K2">
-        <v>-15.41</v>
+        <v>-15.48</v>
       </c>
       <c r="L2">
-        <v>-14.73</v>
+        <v>-13.1</v>
       </c>
       <c r="M2">
-        <v>12.38</v>
+        <v>12.53</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>2292.08</v>
+        <v>2302.1</v>
       </c>
       <c r="Q2">
-        <v>2387.36</v>
+        <v>2382.06</v>
       </c>
       <c r="R2">
-        <v>2491.13</v>
+        <v>2488.07</v>
       </c>
       <c r="S2">
-        <v>2557.88</v>
+        <v>2557</v>
       </c>
       <c r="T2">
-        <v>-8.279999999999999</v>
+        <v>-8</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +976,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.57</v>
+        <v>43.36</v>
       </c>
       <c r="Z2">
-        <v>-58.35</v>
+        <v>-54.04</v>
       </c>
       <c r="AA2">
-        <v>-52.98</v>
+        <v>-53.19</v>
       </c>
       <c r="AB2">
-        <v>-5.37</v>
+        <v>-0.85</v>
       </c>
       <c r="AC2">
-        <v>64.73999999999999</v>
+        <v>80.58</v>
       </c>
       <c r="AD2">
-        <v>38.33</v>
+        <v>60.31</v>
       </c>
       <c r="AE2">
-        <v>56.86</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>85.37</v>
+        <v>29.3</v>
       </c>
       <c r="AG2">
-        <v>2517.03</v>
+        <v>2508.13</v>
       </c>
       <c r="AH2">
-        <v>2257.68</v>
+        <v>2255.99</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -983,7 +1012,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>46</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1023,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>704.8</v>
+        <v>711.45</v>
       </c>
       <c r="D3">
-        <v>-2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1035,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-30.18</v>
+        <v>-29.52</v>
       </c>
       <c r="H3">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="I3">
-        <v>-4.19</v>
+        <v>-1.06</v>
       </c>
       <c r="J3">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="K3">
-        <v>-15.07</v>
+        <v>-14.21</v>
       </c>
       <c r="L3">
-        <v>-25.83</v>
+        <v>-25.19</v>
       </c>
       <c r="M3">
-        <v>-1.47</v>
+        <v>-1.52</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>715.29</v>
+        <v>713.77</v>
       </c>
       <c r="Q3">
-        <v>717.65</v>
+        <v>717.62</v>
       </c>
       <c r="R3">
-        <v>724.5</v>
+        <v>723.87</v>
       </c>
       <c r="S3">
-        <v>812.87</v>
+        <v>811.45</v>
       </c>
       <c r="T3">
-        <v>-13.29</v>
+        <v>-12.32</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1089,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.67</v>
+        <v>45.8</v>
       </c>
       <c r="Z3">
-        <v>-2.02</v>
+        <v>-2.51</v>
       </c>
       <c r="AA3">
-        <v>-1.41</v>
+        <v>-1.63</v>
       </c>
       <c r="AB3">
-        <v>-0.61</v>
+        <v>-0.87</v>
       </c>
       <c r="AC3">
-        <v>24.69</v>
+        <v>19.47</v>
       </c>
       <c r="AD3">
-        <v>42.15</v>
+        <v>30.44</v>
       </c>
       <c r="AE3">
-        <v>15.33</v>
+        <v>15.21</v>
       </c>
       <c r="AF3">
-        <v>119.62</v>
+        <v>-15.59</v>
       </c>
       <c r="AG3">
-        <v>747.17</v>
+        <v>747.16</v>
       </c>
       <c r="AH3">
-        <v>688.14</v>
+        <v>688.08</v>
       </c>
       <c r="AI3">
         <v>703.59</v>
@@ -1096,7 +1125,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>21.9</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1136,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>531</v>
+        <v>543.95</v>
       </c>
       <c r="D4">
-        <v>-0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1119,46 +1148,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.58</v>
+        <v>-30.93</v>
       </c>
       <c r="H4">
-        <v>3.31</v>
+        <v>5.83</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="J4">
-        <v>-0.38</v>
+        <v>1.96</v>
       </c>
       <c r="K4">
-        <v>-5.88</v>
+        <v>-4.98</v>
       </c>
       <c r="L4">
-        <v>-29.82</v>
+        <v>-28.09</v>
       </c>
       <c r="M4">
-        <v>-6.02</v>
+        <v>-5.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>528.3099999999999</v>
+        <v>530.78</v>
       </c>
       <c r="Q4">
-        <v>535.87</v>
+        <v>535.75</v>
       </c>
       <c r="R4">
-        <v>541.02</v>
+        <v>540.8</v>
       </c>
       <c r="S4">
-        <v>619.5599999999999</v>
+        <v>618.46</v>
       </c>
       <c r="T4">
-        <v>-14.29</v>
+        <v>-12.05</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1202,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.79</v>
+        <v>52.6</v>
       </c>
       <c r="Z4">
-        <v>-3.32</v>
+        <v>-2.3</v>
       </c>
       <c r="AA4">
         <v>-2.3</v>
       </c>
       <c r="AB4">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>36.62</v>
+        <v>51.86</v>
       </c>
       <c r="AD4">
-        <v>35.41</v>
+        <v>41.1</v>
       </c>
       <c r="AE4">
-        <v>15.29</v>
+        <v>15.86</v>
       </c>
       <c r="AF4">
-        <v>-30.22</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="AG4">
-        <v>565.24</v>
+        <v>564.95</v>
       </c>
       <c r="AH4">
-        <v>506.5</v>
+        <v>506.54</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1209,7 +1238,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>31.83</v>
+        <v>29.14</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,12 +1399,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,462 +1447,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.11</v>
       </c>
-      <c r="E7" s="6">
-        <v>2.19</v>
+      <c r="D7" s="6">
+        <v>-6.31</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.31</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>0.57</v>
       </c>
+      <c r="D8" s="6">
+        <v>0.68</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.74</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.13</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-0.38</v>
       </c>
-      <c r="E9" s="6">
-        <v>0.75</v>
+      <c r="D9" s="6">
+        <v>1.96</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.35</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.68</v>
+      <c r="D10" s="6">
+        <v>2.18</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
+        <v>-4.19</v>
+      </c>
+      <c r="D11" s="6">
         <v>-1.06</v>
       </c>
-      <c r="D11" s="5">
-        <v>-4.19</v>
-      </c>
       <c r="E11" s="7">
-        <v>-3.13</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>0</v>
       </c>
+      <c r="D12" s="6">
+        <v>2.32</v>
+      </c>
       <c r="E12" s="7">
-        <v>-1.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-16.08</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-14.73</v>
       </c>
-      <c r="E13" s="6">
-        <v>1.35</v>
+      <c r="D13" s="6">
+        <v>-13.1</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.63</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-23.69</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-25.83</v>
       </c>
+      <c r="D14" s="6">
+        <v>-25.19</v>
+      </c>
       <c r="E14" s="7">
-        <v>-2.14</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-30.12</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-29.82</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.3</v>
+      <c r="D15" s="6">
+        <v>-28.09</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-17.57</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-15.41</v>
       </c>
-      <c r="E16" s="6">
-        <v>2.16</v>
+      <c r="D16" s="6">
+        <v>-15.48</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-15.07</v>
       </c>
+      <c r="D17" s="6">
+        <v>-14.21</v>
+      </c>
       <c r="E17" s="7">
-        <v>-5.1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-5.9</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.88</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.02</v>
+      <c r="D18" s="6">
+        <v>-4.98</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-18.72</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-17.38</v>
       </c>
-      <c r="E19" s="6">
-        <v>1.34</v>
+      <c r="D19" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-28.56</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-30.18</v>
       </c>
+      <c r="D20" s="6">
+        <v>-29.52</v>
+      </c>
       <c r="E20" s="7">
-        <v>-1.62</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-32.17</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-32.58</v>
       </c>
+      <c r="D21" s="6">
+        <v>-30.93</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.41</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2308.1</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2346</v>
       </c>
-      <c r="E22" s="6">
-        <v>37.9</v>
+      <c r="D22" s="6">
+        <v>2352.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>6.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>721.2</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>704.8</v>
       </c>
+      <c r="D23" s="6">
+        <v>711.45</v>
+      </c>
       <c r="E23" s="7">
-        <v>-16.4</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>534.2</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>531</v>
       </c>
+      <c r="D24" s="6">
+        <v>543.95</v>
+      </c>
       <c r="E24" s="7">
-        <v>-3.2</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>34</v>
-      </c>
-      <c r="D25" s="5">
-        <v>99</v>
-      </c>
-      <c r="E25" s="6">
-        <v>65</v>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>42.57</v>
+      </c>
+      <c r="D25" s="6">
+        <v>43.36</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>99</v>
-      </c>
-      <c r="D26" s="5">
-        <v>34</v>
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>42.67</v>
+      </c>
+      <c r="D26" s="6">
+        <v>45.8</v>
       </c>
       <c r="E26" s="7">
-        <v>-65</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="D27" s="6">
+        <v>52.6</v>
+      </c>
+      <c r="E27" s="7">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>37.81</v>
-      </c>
-      <c r="D27" s="5">
-        <v>42.57</v>
-      </c>
-      <c r="E27" s="6">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>85.37</v>
+      </c>
+      <c r="D28" s="6">
+        <v>29.3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-56.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>49.17</v>
-      </c>
-      <c r="D28" s="5">
-        <v>42.67</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>119.62</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-15.59</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-135.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>48.15</v>
-      </c>
-      <c r="D29" s="5">
-        <v>46.79</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>71.33</v>
-      </c>
-      <c r="D30" s="5">
-        <v>85.37</v>
-      </c>
-      <c r="E30" s="6">
-        <v>14.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>22.14</v>
-      </c>
-      <c r="D31" s="5">
-        <v>119.62</v>
-      </c>
-      <c r="E31" s="6">
-        <v>97.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-16.5</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C30" s="6">
         <v>-30.22</v>
       </c>
-      <c r="E32" s="7">
-        <v>-13.72</v>
+      <c r="D30" s="6">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>98.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1864,60 +1894,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>44</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>47.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-12.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-1.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-11.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2019,25 +2049,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1238</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0147</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0602</v>
+      <c r="A2" s="14">
+        <v>0.1253</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0152</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0537</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="58">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,40 +151,10 @@
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.8 → 52.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>52.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,15 +356,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,8 +738,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -910,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2352.4</v>
+        <v>2314.8</v>
       </c>
       <c r="D2">
-        <v>0.27</v>
+        <v>-1.6</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -922,46 +891,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.16</v>
+        <v>-18.48</v>
       </c>
       <c r="H2">
-        <v>8.460000000000001</v>
+        <v>6.72</v>
       </c>
       <c r="I2">
-        <v>2.18</v>
+        <v>4.12</v>
       </c>
       <c r="J2">
-        <v>-6.31</v>
+        <v>-5.84</v>
       </c>
       <c r="K2">
-        <v>-15.48</v>
+        <v>-12.95</v>
       </c>
       <c r="L2">
-        <v>-13.1</v>
+        <v>-14.84</v>
       </c>
       <c r="M2">
-        <v>12.53</v>
+        <v>12.06</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="P2">
-        <v>2302.1</v>
+        <v>2320.4</v>
       </c>
       <c r="Q2">
-        <v>2382.06</v>
+        <v>2376.2</v>
       </c>
       <c r="R2">
-        <v>2488.07</v>
+        <v>2483.32</v>
       </c>
       <c r="S2">
-        <v>2557</v>
+        <v>2556.14</v>
       </c>
       <c r="T2">
-        <v>-8</v>
+        <v>-9.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -976,34 +945,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.36</v>
+        <v>39.89</v>
       </c>
       <c r="Z2">
-        <v>-54.04</v>
+        <v>-53.06</v>
       </c>
       <c r="AA2">
-        <v>-53.19</v>
+        <v>-53.17</v>
       </c>
       <c r="AB2">
-        <v>-0.85</v>
+        <v>0.11</v>
       </c>
       <c r="AC2">
-        <v>80.58</v>
+        <v>84.16</v>
       </c>
       <c r="AD2">
-        <v>60.31</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>54.81</v>
       </c>
       <c r="AF2">
-        <v>29.3</v>
+        <v>5.16</v>
       </c>
       <c r="AG2">
-        <v>2508.13</v>
+        <v>2503.39</v>
       </c>
       <c r="AH2">
-        <v>2255.99</v>
+        <v>2249.01</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1012,7 +981,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>43.3</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1023,10 +992,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>711.45</v>
+        <v>702.75</v>
       </c>
       <c r="D3">
-        <v>0.9399999999999999</v>
+        <v>-1.22</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1035,46 +1004,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.52</v>
+        <v>-30.39</v>
       </c>
       <c r="H3">
-        <v>3.54</v>
+        <v>2.28</v>
       </c>
       <c r="I3">
-        <v>-1.06</v>
+        <v>-2.76</v>
       </c>
       <c r="J3">
-        <v>0.68</v>
+        <v>-1.31</v>
       </c>
       <c r="K3">
-        <v>-14.21</v>
+        <v>-13.27</v>
       </c>
       <c r="L3">
-        <v>-25.19</v>
+        <v>-27.2</v>
       </c>
       <c r="M3">
-        <v>-1.52</v>
+        <v>-1.71</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>713.77</v>
+        <v>709.78</v>
       </c>
       <c r="Q3">
-        <v>717.62</v>
+        <v>717.23</v>
       </c>
       <c r="R3">
-        <v>723.87</v>
+        <v>723.13</v>
       </c>
       <c r="S3">
-        <v>811.45</v>
+        <v>810.05</v>
       </c>
       <c r="T3">
-        <v>-12.32</v>
+        <v>-13.25</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1089,43 +1058,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.8</v>
+        <v>42.52</v>
       </c>
       <c r="Z3">
-        <v>-2.51</v>
+        <v>-3.55</v>
       </c>
       <c r="AA3">
-        <v>-1.63</v>
+        <v>-2.02</v>
       </c>
       <c r="AB3">
-        <v>-0.87</v>
+        <v>-1.54</v>
       </c>
       <c r="AC3">
-        <v>19.47</v>
+        <v>6.47</v>
       </c>
       <c r="AD3">
-        <v>30.44</v>
+        <v>16.88</v>
       </c>
       <c r="AE3">
-        <v>15.21</v>
+        <v>14.82</v>
       </c>
       <c r="AF3">
-        <v>-15.59</v>
+        <v>-4.66</v>
       </c>
       <c r="AG3">
-        <v>747.16</v>
+        <v>747.37</v>
       </c>
       <c r="AH3">
-        <v>688.08</v>
+        <v>687.1</v>
       </c>
       <c r="AI3">
-        <v>703.59</v>
+        <v>750.8099999999999</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>20.88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1136,10 +1105,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>543.95</v>
+        <v>546.05</v>
       </c>
       <c r="D4">
-        <v>2.44</v>
+        <v>0.39</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1148,46 +1117,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.93</v>
+        <v>-30.66</v>
       </c>
       <c r="H4">
-        <v>5.83</v>
+        <v>6.24</v>
       </c>
       <c r="I4">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
-        <v>1.96</v>
+        <v>-0.06</v>
       </c>
       <c r="K4">
-        <v>-4.98</v>
+        <v>-1.74</v>
       </c>
       <c r="L4">
-        <v>-28.09</v>
+        <v>-28.53</v>
       </c>
       <c r="M4">
-        <v>-5.37</v>
+        <v>-5.29</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>530.78</v>
+        <v>535.28</v>
       </c>
       <c r="Q4">
-        <v>535.75</v>
+        <v>536.39</v>
       </c>
       <c r="R4">
-        <v>540.8</v>
+        <v>540.67</v>
       </c>
       <c r="S4">
-        <v>618.46</v>
+        <v>617.42</v>
       </c>
       <c r="T4">
-        <v>-12.05</v>
+        <v>-11.56</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1202,34 +1171,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>52.6</v>
+        <v>53.49</v>
       </c>
       <c r="Z4">
-        <v>-2.3</v>
+        <v>-1.31</v>
       </c>
       <c r="AA4">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AC4">
-        <v>51.86</v>
+        <v>58.6</v>
       </c>
       <c r="AD4">
-        <v>41.1</v>
+        <v>49.03</v>
       </c>
       <c r="AE4">
-        <v>15.86</v>
+        <v>15.45</v>
       </c>
       <c r="AF4">
-        <v>68.23999999999999</v>
+        <v>-51.85</v>
       </c>
       <c r="AG4">
-        <v>564.95</v>
+        <v>565.92</v>
       </c>
       <c r="AH4">
-        <v>506.54</v>
+        <v>506.86</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1238,7 +1207,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>29.14</v>
+        <v>26.81</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1389,7 +1358,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1399,47 +1368,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1447,428 +1381,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.11</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.31</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.8</v>
+      <c r="D7" s="5">
+        <v>-5.84</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>0.68</v>
       </c>
+      <c r="D8" s="5">
+        <v>-1.31</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.11</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-0.38</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>1.96</v>
       </c>
+      <c r="D9" s="5">
+        <v>-0.06</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.34</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.35</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>2.18</v>
       </c>
-      <c r="E10" s="7">
-        <v>3.53</v>
+      <c r="D10" s="5">
+        <v>4.12</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.19</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-1.06</v>
       </c>
+      <c r="D11" s="5">
+        <v>-2.76</v>
+      </c>
       <c r="E11" s="7">
-        <v>3.13</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>2.32</v>
       </c>
-      <c r="E12" s="7">
-        <v>2.32</v>
+      <c r="D12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.98</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-14.73</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-13.1</v>
       </c>
+      <c r="D13" s="5">
+        <v>-14.84</v>
+      </c>
       <c r="E13" s="7">
-        <v>1.63</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-25.83</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-25.19</v>
       </c>
+      <c r="D14" s="5">
+        <v>-27.2</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.64</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-29.82</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-28.09</v>
       </c>
+      <c r="D15" s="5">
+        <v>-28.53</v>
+      </c>
       <c r="E15" s="7">
-        <v>1.73</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-15.41</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-15.48</v>
       </c>
-      <c r="E16" s="8">
-        <v>-0.07000000000000001</v>
+      <c r="D16" s="5">
+        <v>-12.95</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-15.07</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-14.21</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.86</v>
+      <c r="D17" s="5">
+        <v>-13.27</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-4.98</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.9</v>
+      <c r="D18" s="5">
+        <v>-1.74</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-17.38</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-17.16</v>
       </c>
+      <c r="D19" s="5">
+        <v>-18.48</v>
+      </c>
       <c r="E19" s="7">
-        <v>0.22</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-30.18</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-29.52</v>
       </c>
+      <c r="D20" s="5">
+        <v>-30.39</v>
+      </c>
       <c r="E20" s="7">
-        <v>0.66</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-32.58</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-30.93</v>
       </c>
-      <c r="E21" s="7">
-        <v>1.65</v>
+      <c r="D21" s="5">
+        <v>-30.66</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.27</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2346</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2352.4</v>
       </c>
+      <c r="D22" s="5">
+        <v>2314.8</v>
+      </c>
       <c r="E22" s="7">
-        <v>6.4</v>
+        <v>-37.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>704.8</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>711.45</v>
       </c>
+      <c r="D23" s="5">
+        <v>702.75</v>
+      </c>
       <c r="E23" s="7">
-        <v>6.65</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>531</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>543.95</v>
       </c>
-      <c r="E24" s="7">
-        <v>12.95</v>
+      <c r="D24" s="5">
+        <v>546.05</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5">
+        <v>99</v>
+      </c>
+      <c r="D25" s="5">
+        <v>66</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5">
+        <v>99</v>
+      </c>
+      <c r="E26" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>42.57</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C27" s="5">
         <v>43.36</v>
       </c>
-      <c r="E25" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D27" s="5">
+        <v>39.89</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>42.67</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C28" s="5">
         <v>45.8</v>
       </c>
-      <c r="E26" s="7">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D28" s="5">
+        <v>42.52</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>46.79</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C29" s="5">
         <v>52.6</v>
       </c>
-      <c r="E27" s="7">
-        <v>5.81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D29" s="5">
+        <v>53.49</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>85.37</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C30" s="5">
         <v>29.3</v>
       </c>
-      <c r="E28" s="8">
-        <v>-56.07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D30" s="5">
+        <v>5.16</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-24.14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>119.62</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C31" s="5">
         <v>-15.59</v>
       </c>
-      <c r="E29" s="8">
-        <v>-135.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D31" s="5">
+        <v>-4.66</v>
+      </c>
+      <c r="E31" s="6">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-30.22</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C32" s="5">
         <v>68.23999999999999</v>
       </c>
-      <c r="E30" s="7">
-        <v>98.45999999999999</v>
+      <c r="D32" s="5">
+        <v>-51.85</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-120.09</v>
       </c>
     </row>
   </sheetData>
@@ -1894,60 +1862,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-11.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2049,25 +2017,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1253</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0152</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0537</v>
+      <c r="A2" s="13">
+        <v>0.1206</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0171</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0529</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
   <si>
     <t>Symbol</t>
   </si>
@@ -240,14 +240,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -280,13 +280,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,8 +738,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -879,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2314.8</v>
+        <v>2245</v>
       </c>
       <c r="D2">
-        <v>-1.6</v>
+        <v>-3.02</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -891,46 +890,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-18.48</v>
+        <v>-20.94</v>
       </c>
       <c r="H2">
-        <v>6.72</v>
+        <v>3.51</v>
       </c>
       <c r="I2">
-        <v>4.12</v>
+        <v>-1.57</v>
       </c>
       <c r="J2">
-        <v>-5.84</v>
+        <v>-7.69</v>
       </c>
       <c r="K2">
-        <v>-12.95</v>
+        <v>-17.98</v>
       </c>
       <c r="L2">
-        <v>-14.84</v>
+        <v>-17.94</v>
       </c>
       <c r="M2">
-        <v>12.06</v>
+        <v>11.49</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>2320.4</v>
+        <v>2313.26</v>
       </c>
       <c r="Q2">
-        <v>2376.2</v>
+        <v>2366.09</v>
       </c>
       <c r="R2">
-        <v>2483.32</v>
+        <v>2477.59</v>
       </c>
       <c r="S2">
-        <v>2556.14</v>
+        <v>2554.04</v>
       </c>
       <c r="T2">
-        <v>-9.44</v>
+        <v>-12.1</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -945,34 +944,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.89</v>
+        <v>34.4</v>
       </c>
       <c r="Z2">
-        <v>-53.06</v>
+        <v>-57.25</v>
       </c>
       <c r="AA2">
-        <v>-53.17</v>
+        <v>-53.98</v>
       </c>
       <c r="AB2">
-        <v>0.11</v>
+        <v>-3.26</v>
       </c>
       <c r="AC2">
-        <v>84.16</v>
+        <v>70.11</v>
       </c>
       <c r="AD2">
-        <v>76.48999999999999</v>
+        <v>78.28</v>
       </c>
       <c r="AE2">
-        <v>54.81</v>
+        <v>56.7</v>
       </c>
       <c r="AF2">
-        <v>5.16</v>
+        <v>41.46</v>
       </c>
       <c r="AG2">
-        <v>2503.39</v>
+        <v>2501.38</v>
       </c>
       <c r="AH2">
-        <v>2249.01</v>
+        <v>2230.79</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -981,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>42.77</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -992,10 +991,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>702.75</v>
+        <v>692.25</v>
       </c>
       <c r="D3">
-        <v>-1.22</v>
+        <v>-1.49</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1004,46 +1003,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-30.39</v>
+        <v>-31.43</v>
       </c>
       <c r="H3">
-        <v>2.28</v>
+        <v>0.75</v>
       </c>
       <c r="I3">
-        <v>-2.76</v>
+        <v>-2.32</v>
       </c>
       <c r="J3">
-        <v>-1.31</v>
+        <v>-2.57</v>
       </c>
       <c r="K3">
-        <v>-13.27</v>
+        <v>-15.33</v>
       </c>
       <c r="L3">
-        <v>-27.2</v>
+        <v>-28.28</v>
       </c>
       <c r="M3">
-        <v>-1.71</v>
+        <v>-1.91</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>709.78</v>
+        <v>706.49</v>
       </c>
       <c r="Q3">
-        <v>717.23</v>
+        <v>716.7</v>
       </c>
       <c r="R3">
-        <v>723.13</v>
+        <v>722.27</v>
       </c>
       <c r="S3">
-        <v>810.05</v>
+        <v>808.61</v>
       </c>
       <c r="T3">
-        <v>-13.25</v>
+        <v>-14.39</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1058,43 +1057,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.52</v>
+        <v>38.91</v>
       </c>
       <c r="Z3">
-        <v>-3.55</v>
+        <v>-5.17</v>
       </c>
       <c r="AA3">
-        <v>-2.02</v>
+        <v>-2.65</v>
       </c>
       <c r="AB3">
-        <v>-1.54</v>
+        <v>-2.52</v>
       </c>
       <c r="AC3">
         <v>6.47</v>
       </c>
       <c r="AD3">
-        <v>16.88</v>
+        <v>10.8</v>
       </c>
       <c r="AE3">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
       <c r="AF3">
-        <v>-4.66</v>
+        <v>-16.62</v>
       </c>
       <c r="AG3">
-        <v>747.37</v>
+        <v>748.25</v>
       </c>
       <c r="AH3">
-        <v>687.1</v>
+        <v>685.15</v>
       </c>
       <c r="AI3">
-        <v>750.8099999999999</v>
+        <v>742.71</v>
       </c>
       <c r="AJ3" t="s">
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1105,10 +1104,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>546.05</v>
+        <v>544.5</v>
       </c>
       <c r="D4">
-        <v>0.39</v>
+        <v>-0.28</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1117,46 +1116,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.66</v>
+        <v>-30.86</v>
       </c>
       <c r="H4">
-        <v>6.24</v>
+        <v>5.93</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="J4">
-        <v>-0.06</v>
+        <v>2.12</v>
       </c>
       <c r="K4">
-        <v>-1.74</v>
+        <v>-1.33</v>
       </c>
       <c r="L4">
-        <v>-28.53</v>
+        <v>-28.28</v>
       </c>
       <c r="M4">
-        <v>-5.29</v>
+        <v>-5.26</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>535.28</v>
+        <v>539.9400000000001</v>
       </c>
       <c r="Q4">
-        <v>536.39</v>
+        <v>536.92</v>
       </c>
       <c r="R4">
-        <v>540.67</v>
+        <v>540.38</v>
       </c>
       <c r="S4">
-        <v>617.42</v>
+        <v>616.36</v>
       </c>
       <c r="T4">
-        <v>-11.56</v>
+        <v>-11.66</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1171,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>53.49</v>
+        <v>52.71</v>
       </c>
       <c r="Z4">
-        <v>-1.31</v>
+        <v>-0.64</v>
       </c>
       <c r="AA4">
-        <v>-2.1</v>
+        <v>-1.81</v>
       </c>
       <c r="AB4">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AC4">
-        <v>58.6</v>
+        <v>65.97</v>
       </c>
       <c r="AD4">
-        <v>49.03</v>
+        <v>58.81</v>
       </c>
       <c r="AE4">
-        <v>15.45</v>
+        <v>14.87</v>
       </c>
       <c r="AF4">
-        <v>-51.85</v>
+        <v>-51.57</v>
       </c>
       <c r="AG4">
-        <v>565.92</v>
+        <v>566.64</v>
       </c>
       <c r="AH4">
-        <v>506.86</v>
+        <v>507.2</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1207,7 +1206,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>26.81</v>
+        <v>25.05</v>
       </c>
     </row>
   </sheetData>
@@ -1348,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1405,13 +1404,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.31</v>
+        <v>-5.84</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.84</v>
+        <v>-7.69</v>
       </c>
       <c r="E7" s="6">
-        <v>0.47</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1422,13 +1421,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>0.68</v>
+        <v>-1.31</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.99</v>
+        <v>-2.57</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1439,13 +1438,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>1.96</v>
+        <v>-0.06</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.06</v>
+        <v>2.12</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.02</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1456,13 +1455,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>2.18</v>
+        <v>4.12</v>
       </c>
       <c r="D10" s="5">
-        <v>4.12</v>
+        <v>-1.57</v>
       </c>
       <c r="E10" s="6">
-        <v>1.94</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1473,13 +1472,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.06</v>
+        <v>-2.76</v>
       </c>
       <c r="D11" s="5">
-        <v>-2.76</v>
+        <v>-2.32</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.7</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1490,13 +1489,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="D12" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.98</v>
+        <v>4.47</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1507,13 +1506,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-13.1</v>
+        <v>-14.84</v>
       </c>
       <c r="D13" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.74</v>
+        <v>-17.94</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1524,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.19</v>
+        <v>-27.2</v>
       </c>
       <c r="D14" s="5">
-        <v>-27.2</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.01</v>
+        <v>-28.28</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1541,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-28.09</v>
+        <v>-28.53</v>
       </c>
       <c r="D15" s="5">
-        <v>-28.53</v>
+        <v>-28.28</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1558,13 +1557,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-15.48</v>
+        <v>-12.95</v>
       </c>
       <c r="D16" s="5">
-        <v>-12.95</v>
+        <v>-17.98</v>
       </c>
       <c r="E16" s="6">
-        <v>2.53</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1575,13 +1574,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-14.21</v>
+        <v>-13.27</v>
       </c>
       <c r="D17" s="5">
-        <v>-13.27</v>
+        <v>-15.33</v>
       </c>
       <c r="E17" s="6">
-        <v>0.9399999999999999</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1592,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.98</v>
+        <v>-1.74</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="E18" s="6">
-        <v>3.24</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1609,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-17.16</v>
+        <v>-18.48</v>
       </c>
       <c r="D19" s="5">
-        <v>-18.48</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.32</v>
+        <v>-20.94</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1626,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-29.52</v>
+        <v>-30.39</v>
       </c>
       <c r="D20" s="5">
-        <v>-30.39</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.87</v>
+        <v>-31.43</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1643,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.93</v>
+        <v>-30.66</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.66</v>
+        <v>-30.86</v>
       </c>
       <c r="E21" s="6">
-        <v>0.27</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1660,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2352.4</v>
+        <v>2314.8</v>
       </c>
       <c r="D22" s="5">
-        <v>2314.8</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-37.6</v>
+        <v>2245</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-69.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1677,13 +1676,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>711.45</v>
+        <v>702.75</v>
       </c>
       <c r="D23" s="5">
-        <v>702.75</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-8.699999999999999</v>
+        <v>692.25</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1694,13 +1693,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>543.95</v>
+        <v>546.05</v>
       </c>
       <c r="D24" s="5">
-        <v>546.05</v>
+        <v>544.5</v>
       </c>
       <c r="E24" s="6">
-        <v>2.1</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1708,135 +1707,101 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>99</v>
+        <v>39.89</v>
       </c>
       <c r="D25" s="5">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-33</v>
+        <v>34.4</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>66</v>
+        <v>42.52</v>
       </c>
       <c r="D26" s="5">
-        <v>99</v>
+        <v>38.91</v>
       </c>
       <c r="E26" s="6">
-        <v>33</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>43.36</v>
+        <v>53.49</v>
       </c>
       <c r="D27" s="5">
-        <v>39.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.47</v>
+        <v>52.71</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>45.8</v>
+        <v>5.16</v>
       </c>
       <c r="D28" s="5">
-        <v>42.52</v>
+        <v>41.46</v>
       </c>
       <c r="E28" s="7">
-        <v>-3.28</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>52.6</v>
+        <v>-4.66</v>
       </c>
       <c r="D29" s="5">
-        <v>53.49</v>
+        <v>-16.62</v>
       </c>
       <c r="E29" s="6">
-        <v>0.89</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>29.3</v>
+        <v>-51.85</v>
       </c>
       <c r="D30" s="5">
-        <v>5.16</v>
+        <v>-51.57</v>
       </c>
       <c r="E30" s="7">
-        <v>-24.14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-15.59</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-4.66</v>
-      </c>
-      <c r="E31" s="6">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>68.23999999999999</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-51.85</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-120.09</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -1901,16 +1866,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>45.3</v>
+        <v>42</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-9.300000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2029,13 +1994,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1206</v>
+        <v>0.1149</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0171</v>
+        <v>-0.0191</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0529</v>
+        <v>-0.0526</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,16 +160,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -200,13 +191,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,22 +227,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,24 +244,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,33 +313,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1347,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1380,428 +1331,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-5.84</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-7.69</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-2.57</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-0.06</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2.12</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4.12</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-5.69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="D12" s="5">
-        <v>4.47</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-17.94</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-27.2</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-28.28</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-28.53</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-28.28</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-12.95</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-17.98</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-5.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-13.27</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.33</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-18.48</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-20.94</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-30.39</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-31.43</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-30.66</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-30.86</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2314.8</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2245</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-69.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>702.75</v>
-      </c>
-      <c r="D23" s="5">
-        <v>692.25</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>546.05</v>
-      </c>
-      <c r="D24" s="5">
-        <v>544.5</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>39.89</v>
-      </c>
-      <c r="D25" s="5">
-        <v>34.4</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-5.49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>42.52</v>
-      </c>
-      <c r="D26" s="5">
-        <v>38.91</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>53.49</v>
-      </c>
-      <c r="D27" s="5">
-        <v>52.71</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5">
-        <v>5.16</v>
-      </c>
-      <c r="D28" s="5">
-        <v>41.46</v>
-      </c>
-      <c r="E28" s="7">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-4.66</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-16.62</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-11.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-51.85</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-51.57</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -1827,60 +1358,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>42</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>-2.7</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <v>-11.5</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1982,24 +1513,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>0.1149</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>-0.0191</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="9">
         <v>-0.0526</v>
       </c>
     </row>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,16 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -191,11 +200,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,8 +238,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,6 +269,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,27 +356,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -689,7 +738,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -829,10 +880,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2245</v>
+        <v>2262.5</v>
       </c>
       <c r="D2">
-        <v>-3.02</v>
+        <v>0.78</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -841,46 +892,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-20.94</v>
+        <v>-20.32</v>
       </c>
       <c r="H2">
-        <v>3.51</v>
+        <v>4.31</v>
       </c>
       <c r="I2">
-        <v>-1.57</v>
+        <v>-1.98</v>
       </c>
       <c r="J2">
-        <v>-7.69</v>
+        <v>-7.55</v>
       </c>
       <c r="K2">
-        <v>-17.98</v>
+        <v>-18.06</v>
       </c>
       <c r="L2">
-        <v>-17.94</v>
+        <v>-18.32</v>
       </c>
       <c r="M2">
-        <v>11.49</v>
+        <v>11.52</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>2313.26</v>
+        <v>2304.14</v>
       </c>
       <c r="Q2">
-        <v>2366.09</v>
+        <v>2357.21</v>
       </c>
       <c r="R2">
-        <v>2477.59</v>
+        <v>2472</v>
       </c>
       <c r="S2">
-        <v>2554.04</v>
+        <v>2552.27</v>
       </c>
       <c r="T2">
-        <v>-12.1</v>
+        <v>-11.35</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -895,34 +946,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.4</v>
+        <v>36.75</v>
       </c>
       <c r="Z2">
-        <v>-57.25</v>
+        <v>-58.48</v>
       </c>
       <c r="AA2">
-        <v>-53.98</v>
+        <v>-54.88</v>
       </c>
       <c r="AB2">
-        <v>-3.26</v>
+        <v>-3.6</v>
       </c>
       <c r="AC2">
-        <v>70.11</v>
+        <v>58.75</v>
       </c>
       <c r="AD2">
-        <v>78.28</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="AE2">
-        <v>56.7</v>
+        <v>56.89</v>
       </c>
       <c r="AF2">
-        <v>41.46</v>
+        <v>30.17</v>
       </c>
       <c r="AG2">
-        <v>2501.38</v>
+        <v>2495.35</v>
       </c>
       <c r="AH2">
-        <v>2230.79</v>
+        <v>2219.07</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -931,7 +982,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>44.52</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -942,10 +993,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>692.25</v>
+        <v>707.25</v>
       </c>
       <c r="D3">
-        <v>-1.49</v>
+        <v>2.17</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -954,46 +1005,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-31.43</v>
+        <v>-29.94</v>
       </c>
       <c r="H3">
-        <v>0.75</v>
+        <v>2.93</v>
       </c>
       <c r="I3">
-        <v>-2.32</v>
+        <v>-1.93</v>
       </c>
       <c r="J3">
-        <v>-2.57</v>
+        <v>0.6</v>
       </c>
       <c r="K3">
-        <v>-15.33</v>
+        <v>-14.27</v>
       </c>
       <c r="L3">
-        <v>-28.28</v>
+        <v>-27.35</v>
       </c>
       <c r="M3">
-        <v>-1.91</v>
+        <v>-1.87</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P3">
-        <v>706.49</v>
+        <v>703.7</v>
       </c>
       <c r="Q3">
-        <v>716.7</v>
+        <v>717.7</v>
       </c>
       <c r="R3">
-        <v>722.27</v>
+        <v>721.45</v>
       </c>
       <c r="S3">
-        <v>808.61</v>
+        <v>807.22</v>
       </c>
       <c r="T3">
-        <v>-14.39</v>
+        <v>-12.38</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1008,34 +1059,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.91</v>
+        <v>45.97</v>
       </c>
       <c r="Z3">
-        <v>-5.17</v>
+        <v>-5.18</v>
       </c>
       <c r="AA3">
-        <v>-2.65</v>
+        <v>-3.15</v>
       </c>
       <c r="AB3">
-        <v>-2.52</v>
+        <v>-2.02</v>
       </c>
       <c r="AC3">
-        <v>6.47</v>
+        <v>11.84</v>
       </c>
       <c r="AD3">
-        <v>10.8</v>
+        <v>8.26</v>
       </c>
       <c r="AE3">
-        <v>14.85</v>
+        <v>15.07</v>
       </c>
       <c r="AF3">
-        <v>-16.62</v>
+        <v>-43.98</v>
       </c>
       <c r="AG3">
-        <v>748.25</v>
+        <v>746.4400000000001</v>
       </c>
       <c r="AH3">
-        <v>685.15</v>
+        <v>688.97</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1044,7 +1095,7 @@
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>19.17</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1055,10 +1106,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>544.5</v>
+        <v>556.65</v>
       </c>
       <c r="D4">
-        <v>-0.28</v>
+        <v>2.23</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1067,46 +1118,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.86</v>
+        <v>-29.32</v>
       </c>
       <c r="H4">
-        <v>5.93</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.12</v>
+        <v>4.28</v>
       </c>
       <c r="K4">
-        <v>-1.33</v>
+        <v>-1.95</v>
       </c>
       <c r="L4">
-        <v>-28.28</v>
+        <v>-27.05</v>
       </c>
       <c r="M4">
-        <v>-5.26</v>
+        <v>-4.72</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P4">
-        <v>539.9400000000001</v>
+        <v>544.4299999999999</v>
       </c>
       <c r="Q4">
-        <v>536.92</v>
+        <v>539.0599999999999</v>
       </c>
       <c r="R4">
         <v>540.38</v>
       </c>
       <c r="S4">
-        <v>616.36</v>
+        <v>615.3099999999999</v>
       </c>
       <c r="T4">
-        <v>-11.66</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1121,34 +1172,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>52.71</v>
+        <v>57.91</v>
       </c>
       <c r="Z4">
-        <v>-0.64</v>
+        <v>0.87</v>
       </c>
       <c r="AA4">
-        <v>-1.81</v>
+        <v>-1.27</v>
       </c>
       <c r="AB4">
-        <v>1.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC4">
-        <v>65.97</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="AD4">
-        <v>58.81</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="AE4">
-        <v>14.87</v>
+        <v>15.08</v>
       </c>
       <c r="AF4">
-        <v>-51.57</v>
+        <v>-47.66</v>
       </c>
       <c r="AG4">
-        <v>566.64</v>
+        <v>567.96</v>
       </c>
       <c r="AH4">
-        <v>507.2</v>
+        <v>510.15</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1157,7 +1208,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>25.05</v>
+        <v>26.29</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1331,8 +1382,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>46</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.69</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.55</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-2.57</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2.12</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4.28</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-1.57</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.98</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-2.32</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-1.93</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4.47</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-17.94</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-18.32</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-28.28</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-27.35</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-28.28</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-27.05</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-17.98</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-18.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-15.33</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-14.27</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.33</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-20.94</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-20.32</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-31.43</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-29.94</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-30.86</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-29.32</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2245</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2262.5</v>
+      </c>
+      <c r="E22" s="6">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>692.25</v>
+      </c>
+      <c r="D23" s="5">
+        <v>707.25</v>
+      </c>
+      <c r="E23" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>544.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>556.65</v>
+      </c>
+      <c r="E24" s="6">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>34.4</v>
+      </c>
+      <c r="D25" s="5">
+        <v>36.75</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>38.91</v>
+      </c>
+      <c r="D26" s="5">
+        <v>45.97</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>52.71</v>
+      </c>
+      <c r="D27" s="5">
+        <v>57.91</v>
+      </c>
+      <c r="E27" s="6">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>41.46</v>
+      </c>
+      <c r="D28" s="5">
+        <v>30.17</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-11.29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-43.98</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-27.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-51.57</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-47.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3.91</v>
       </c>
     </row>
   </sheetData>
@@ -1358,60 +1829,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>54</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="6">
-        <v>42</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="10">
+        <v>46.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-11.5</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="10">
+        <v>-0.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-11.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1513,25 +1984,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9">
-        <v>0.1149</v>
-      </c>
-      <c r="B2" s="9">
-        <v>-0.0191</v>
-      </c>
-      <c r="C2" s="9">
-        <v>-0.0526</v>
+      <c r="A2" s="13">
+        <v>0.1152</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0187</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0472</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,13 +148,37 @@
     <t>No</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -356,14 +380,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -738,9 +763,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -880,10 +903,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2262.5</v>
+        <v>2289.7</v>
       </c>
       <c r="D2">
-        <v>0.78</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -892,46 +915,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-20.32</v>
+        <v>-19.37</v>
       </c>
       <c r="H2">
-        <v>4.31</v>
+        <v>5.57</v>
       </c>
       <c r="I2">
-        <v>-1.98</v>
+        <v>-2.4</v>
       </c>
       <c r="J2">
-        <v>-7.55</v>
+        <v>-6.16</v>
       </c>
       <c r="K2">
-        <v>-18.06</v>
+        <v>-16.71</v>
       </c>
       <c r="L2">
-        <v>-18.32</v>
+        <v>-15.78</v>
       </c>
       <c r="M2">
-        <v>11.52</v>
+        <v>11.83</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>2304.14</v>
+        <v>2292.88</v>
       </c>
       <c r="Q2">
-        <v>2357.21</v>
+        <v>2350.01</v>
       </c>
       <c r="R2">
-        <v>2472</v>
+        <v>2466.87</v>
       </c>
       <c r="S2">
-        <v>2552.27</v>
+        <v>2550.69</v>
       </c>
       <c r="T2">
-        <v>-11.35</v>
+        <v>-10.23</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -946,43 +969,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.75</v>
+        <v>40.33</v>
       </c>
       <c r="Z2">
-        <v>-58.48</v>
+        <v>-56.61</v>
       </c>
       <c r="AA2">
-        <v>-54.88</v>
+        <v>-55.23</v>
       </c>
       <c r="AB2">
-        <v>-3.6</v>
+        <v>-1.38</v>
       </c>
       <c r="AC2">
-        <v>58.75</v>
+        <v>59.5</v>
       </c>
       <c r="AD2">
-        <v>71.01000000000001</v>
+        <v>62.79</v>
       </c>
       <c r="AE2">
-        <v>56.89</v>
+        <v>56.08</v>
       </c>
       <c r="AF2">
-        <v>30.17</v>
+        <v>2.61</v>
       </c>
       <c r="AG2">
-        <v>2495.35</v>
+        <v>2486.34</v>
       </c>
       <c r="AH2">
-        <v>2219.07</v>
+        <v>2213.67</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
       </c>
       <c r="AJ2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.11</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -993,10 +1016,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>707.25</v>
+        <v>704.9</v>
       </c>
       <c r="D3">
-        <v>2.17</v>
+        <v>-0.33</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1005,46 +1028,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.94</v>
+        <v>-30.17</v>
       </c>
       <c r="H3">
-        <v>2.93</v>
+        <v>2.59</v>
       </c>
       <c r="I3">
-        <v>-1.93</v>
+        <v>0.01</v>
       </c>
       <c r="J3">
-        <v>0.6</v>
+        <v>2.59</v>
       </c>
       <c r="K3">
-        <v>-14.27</v>
+        <v>-13.82</v>
       </c>
       <c r="L3">
-        <v>-27.35</v>
+        <v>-28.25</v>
       </c>
       <c r="M3">
-        <v>-1.87</v>
+        <v>-1.88</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P3">
-        <v>703.7</v>
+        <v>703.72</v>
       </c>
       <c r="Q3">
-        <v>717.7</v>
+        <v>718.26</v>
       </c>
       <c r="R3">
-        <v>721.45</v>
+        <v>720.47</v>
       </c>
       <c r="S3">
-        <v>807.22</v>
+        <v>805.8</v>
       </c>
       <c r="T3">
-        <v>-12.38</v>
+        <v>-12.52</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1059,43 +1082,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.97</v>
+        <v>45.09</v>
       </c>
       <c r="Z3">
-        <v>-5.18</v>
+        <v>-5.31</v>
       </c>
       <c r="AA3">
-        <v>-3.15</v>
+        <v>-3.58</v>
       </c>
       <c r="AB3">
-        <v>-2.02</v>
+        <v>-1.73</v>
       </c>
       <c r="AC3">
-        <v>11.84</v>
+        <v>22.48</v>
       </c>
       <c r="AD3">
-        <v>8.26</v>
+        <v>13.6</v>
       </c>
       <c r="AE3">
-        <v>15.07</v>
+        <v>14.82</v>
       </c>
       <c r="AF3">
-        <v>-43.98</v>
+        <v>-44.49</v>
       </c>
       <c r="AG3">
-        <v>746.4400000000001</v>
+        <v>745.4299999999999</v>
       </c>
       <c r="AH3">
-        <v>688.97</v>
+        <v>691.09</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>16.95</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1106,10 +1129,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>556.65</v>
+        <v>559.25</v>
       </c>
       <c r="D4">
-        <v>2.23</v>
+        <v>0.47</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1118,49 +1141,49 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-29.32</v>
+        <v>-28.99</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>5.32</v>
       </c>
       <c r="J4">
-        <v>4.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K4">
-        <v>-1.95</v>
+        <v>-2.47</v>
       </c>
       <c r="L4">
-        <v>-27.05</v>
+        <v>-25.99</v>
       </c>
       <c r="M4">
-        <v>-4.72</v>
+        <v>-4.25</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P4">
-        <v>544.4299999999999</v>
+        <v>550.08</v>
       </c>
       <c r="Q4">
-        <v>539.0599999999999</v>
+        <v>540.71</v>
       </c>
       <c r="R4">
-        <v>540.38</v>
+        <v>540.66</v>
       </c>
       <c r="S4">
-        <v>615.3099999999999</v>
+        <v>614.3</v>
       </c>
       <c r="T4">
-        <v>-9.529999999999999</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="U4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V4" t="s">
         <v>41</v>
@@ -1169,46 +1192,46 @@
         <v>41</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>57.91</v>
+        <v>58.96</v>
       </c>
       <c r="Z4">
-        <v>0.87</v>
+        <v>2.24</v>
       </c>
       <c r="AA4">
-        <v>-1.27</v>
+        <v>-0.57</v>
       </c>
       <c r="AB4">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="AC4">
-        <v>76.45999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="AD4">
-        <v>67.01000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="AE4">
-        <v>15.08</v>
+        <v>14.7</v>
       </c>
       <c r="AF4">
-        <v>-47.66</v>
+        <v>-66.98999999999999</v>
       </c>
       <c r="AG4">
-        <v>567.96</v>
+        <v>570.29</v>
       </c>
       <c r="AH4">
-        <v>510.15</v>
+        <v>511.13</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
       </c>
       <c r="AJ4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>26.29</v>
+        <v>27.65</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1382,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1369,12 +1392,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1382,428 +1440,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>49</v>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.69</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.55</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.14</v>
+      <c r="D7" s="6">
+        <v>-6.16</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.57</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>0.6</v>
       </c>
-      <c r="E8" s="6">
-        <v>3.17</v>
+      <c r="D8" s="6">
+        <v>2.59</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>2.12</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>4.28</v>
       </c>
-      <c r="E9" s="6">
-        <v>2.16</v>
+      <c r="D9" s="6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.98</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.41</v>
+      <c r="D10" s="6">
+        <v>-2.4</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-1.93</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.39</v>
+      <c r="D11" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>4.47</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>4.2</v>
       </c>
+      <c r="D12" s="6">
+        <v>5.32</v>
+      </c>
       <c r="E12" s="7">
-        <v>-0.27</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-17.94</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-18.32</v>
       </c>
+      <c r="D13" s="6">
+        <v>-15.78</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.38</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-28.28</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-27.35</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.93</v>
+      <c r="D14" s="6">
+        <v>-28.25</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-28.28</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-27.05</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.23</v>
+      <c r="D15" s="6">
+        <v>-25.99</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-17.98</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-18.06</v>
       </c>
+      <c r="D16" s="6">
+        <v>-16.71</v>
+      </c>
       <c r="E16" s="7">
-        <v>-0.08</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-14.27</v>
       </c>
-      <c r="E17" s="6">
-        <v>1.06</v>
+      <c r="D17" s="6">
+        <v>-13.82</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-1.33</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-1.95</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.62</v>
+      <c r="D18" s="6">
+        <v>-2.47</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-20.94</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-20.32</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.62</v>
+      <c r="D19" s="6">
+        <v>-19.37</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-31.43</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-29.94</v>
       </c>
-      <c r="E20" s="6">
-        <v>1.49</v>
+      <c r="D20" s="6">
+        <v>-30.17</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-30.86</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-29.32</v>
       </c>
-      <c r="E21" s="6">
-        <v>1.54</v>
+      <c r="D21" s="6">
+        <v>-28.99</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2245</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2262.5</v>
       </c>
-      <c r="E22" s="6">
-        <v>17.5</v>
+      <c r="D22" s="6">
+        <v>2289.7</v>
+      </c>
+      <c r="E22" s="7">
+        <v>27.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>692.25</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>707.25</v>
       </c>
-      <c r="E23" s="6">
-        <v>15</v>
+      <c r="D23" s="6">
+        <v>704.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>544.5</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>556.65</v>
       </c>
-      <c r="E24" s="6">
-        <v>12.15</v>
+      <c r="D24" s="6">
+        <v>559.25</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>34.4</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>36.75</v>
       </c>
-      <c r="E25" s="6">
-        <v>2.35</v>
+      <c r="D25" s="6">
+        <v>40.33</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>38.91</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>45.97</v>
       </c>
-      <c r="E26" s="6">
-        <v>7.06</v>
+      <c r="D26" s="6">
+        <v>45.09</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>52.71</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>57.91</v>
       </c>
-      <c r="E27" s="6">
-        <v>5.2</v>
+      <c r="D27" s="6">
+        <v>58.96</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>41.46</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>30.17</v>
       </c>
-      <c r="E28" s="7">
-        <v>-11.29</v>
+      <c r="D28" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-27.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-16.62</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-43.98</v>
       </c>
-      <c r="E29" s="7">
-        <v>-27.36</v>
+      <c r="D29" s="6">
+        <v>-44.49</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-51.57</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-47.66</v>
       </c>
-      <c r="E30" s="6">
-        <v>3.91</v>
+      <c r="D30" s="6">
+        <v>-66.98999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-19.33</v>
       </c>
     </row>
   </sheetData>
@@ -1829,60 +1887,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>57</v>
+      <c r="B1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>48.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-0.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-11.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-11</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1984,25 +2042,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1152</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0187</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0472</v>
+      <c r="A2" s="14">
+        <v>0.1183</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0188</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0425</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,28 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -763,7 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -903,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2289.7</v>
+        <v>2330</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -915,25 +894,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.37</v>
+        <v>-17.95</v>
       </c>
       <c r="H2">
-        <v>5.57</v>
+        <v>7.42</v>
       </c>
       <c r="I2">
-        <v>-2.4</v>
+        <v>-0.95</v>
       </c>
       <c r="J2">
-        <v>-6.16</v>
+        <v>-4.26</v>
       </c>
       <c r="K2">
-        <v>-16.71</v>
+        <v>-12.4</v>
       </c>
       <c r="L2">
-        <v>-15.78</v>
+        <v>-13.03</v>
       </c>
       <c r="M2">
-        <v>11.83</v>
+        <v>12.27</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -942,19 +921,19 @@
         <v>41</v>
       </c>
       <c r="P2">
-        <v>2292.88</v>
+        <v>2288.4</v>
       </c>
       <c r="Q2">
-        <v>2350.01</v>
+        <v>2346.31</v>
       </c>
       <c r="R2">
-        <v>2466.87</v>
+        <v>2461.16</v>
       </c>
       <c r="S2">
-        <v>2550.69</v>
+        <v>2549.09</v>
       </c>
       <c r="T2">
-        <v>-10.23</v>
+        <v>-8.59</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -969,34 +948,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.33</v>
+        <v>45.28</v>
       </c>
       <c r="Z2">
-        <v>-56.61</v>
+        <v>-51.29</v>
       </c>
       <c r="AA2">
-        <v>-55.23</v>
+        <v>-54.44</v>
       </c>
       <c r="AB2">
-        <v>-1.38</v>
+        <v>3.15</v>
       </c>
       <c r="AC2">
-        <v>59.5</v>
+        <v>77.75</v>
       </c>
       <c r="AD2">
-        <v>62.79</v>
+        <v>65.33</v>
       </c>
       <c r="AE2">
-        <v>56.08</v>
+        <v>56.94</v>
       </c>
       <c r="AF2">
-        <v>2.61</v>
+        <v>-4.53</v>
       </c>
       <c r="AG2">
-        <v>2486.34</v>
+        <v>2480.49</v>
       </c>
       <c r="AH2">
-        <v>2213.67</v>
+        <v>2212.13</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1005,7 +984,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>45.76</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1016,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>704.9</v>
+        <v>714</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>1.29</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1028,46 +1007,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-30.17</v>
+        <v>-29.27</v>
       </c>
       <c r="H3">
-        <v>2.59</v>
+        <v>3.92</v>
       </c>
       <c r="I3">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="J3">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="K3">
-        <v>-13.82</v>
+        <v>-11.79</v>
       </c>
       <c r="L3">
-        <v>-28.25</v>
+        <v>-27.05</v>
       </c>
       <c r="M3">
-        <v>-1.88</v>
+        <v>-1.75</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>703.72</v>
+        <v>704.23</v>
       </c>
       <c r="Q3">
-        <v>718.26</v>
+        <v>718.55</v>
       </c>
       <c r="R3">
-        <v>720.47</v>
+        <v>719.79</v>
       </c>
       <c r="S3">
-        <v>805.8</v>
+        <v>804.39</v>
       </c>
       <c r="T3">
-        <v>-12.52</v>
+        <v>-11.24</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1082,34 +1061,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.09</v>
+        <v>49.15</v>
       </c>
       <c r="Z3">
-        <v>-5.31</v>
+        <v>-4.63</v>
       </c>
       <c r="AA3">
-        <v>-3.58</v>
+        <v>-3.79</v>
       </c>
       <c r="AB3">
-        <v>-1.73</v>
+        <v>-0.84</v>
       </c>
       <c r="AC3">
-        <v>22.48</v>
+        <v>40.85</v>
       </c>
       <c r="AD3">
-        <v>13.6</v>
+        <v>25.06</v>
       </c>
       <c r="AE3">
-        <v>14.82</v>
+        <v>14.59</v>
       </c>
       <c r="AF3">
-        <v>-44.49</v>
+        <v>-40.7</v>
       </c>
       <c r="AG3">
-        <v>745.4299999999999</v>
+        <v>745.4</v>
       </c>
       <c r="AH3">
-        <v>691.09</v>
+        <v>691.7</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1118,7 +1097,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>14.94</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1129,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>559.25</v>
+        <v>560</v>
       </c>
       <c r="D4">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1141,46 +1120,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-28.99</v>
+        <v>-28.89</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I4">
-        <v>5.32</v>
+        <v>2.95</v>
       </c>
       <c r="J4">
-        <v>8.800000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="K4">
-        <v>-2.47</v>
+        <v>0.86</v>
       </c>
       <c r="L4">
-        <v>-25.99</v>
+        <v>-25.06</v>
       </c>
       <c r="M4">
-        <v>-4.25</v>
+        <v>-4.16</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P4">
-        <v>550.08</v>
+        <v>553.29</v>
       </c>
       <c r="Q4">
-        <v>540.71</v>
+        <v>542.21</v>
       </c>
       <c r="R4">
-        <v>540.66</v>
+        <v>540.89</v>
       </c>
       <c r="S4">
-        <v>614.3</v>
+        <v>613.28</v>
       </c>
       <c r="T4">
-        <v>-8.960000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1195,34 +1174,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>58.96</v>
+        <v>59.27</v>
       </c>
       <c r="Z4">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA4">
-        <v>-0.57</v>
+        <v>0.21</v>
       </c>
       <c r="AB4">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AC4">
-        <v>86.7</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="AD4">
-        <v>76.38</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="AE4">
-        <v>14.7</v>
+        <v>14.52</v>
       </c>
       <c r="AF4">
-        <v>-66.98999999999999</v>
+        <v>-65.84</v>
       </c>
       <c r="AG4">
-        <v>570.29</v>
+        <v>572.53</v>
       </c>
       <c r="AH4">
-        <v>511.13</v>
+        <v>511.89</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1231,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.65</v>
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
@@ -1392,47 +1371,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1440,428 +1384,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>57</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.16</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.39</v>
+      <c r="D7" s="5">
+        <v>-4.26</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>2.59</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.99</v>
+      <c r="D8" s="5">
+        <v>2.91</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.32</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>4.28</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>8.800000000000001</v>
       </c>
+      <c r="D9" s="5">
+        <v>6.43</v>
+      </c>
       <c r="E9" s="7">
-        <v>4.52</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-2.4</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.42</v>
+      <c r="D10" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>0.01</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.94</v>
+      <c r="D11" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>4.2</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>5.32</v>
       </c>
+      <c r="D12" s="5">
+        <v>2.95</v>
+      </c>
       <c r="E12" s="7">
-        <v>1.12</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-18.32</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-15.78</v>
       </c>
-      <c r="E13" s="7">
-        <v>2.54</v>
+      <c r="D13" s="5">
+        <v>-13.03</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.75</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-27.35</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-28.25</v>
       </c>
-      <c r="E14" s="8">
-        <v>-0.9</v>
+      <c r="D14" s="5">
+        <v>-27.05</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-27.05</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-25.99</v>
       </c>
-      <c r="E15" s="7">
-        <v>1.06</v>
+      <c r="D15" s="5">
+        <v>-25.06</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-18.06</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-16.71</v>
       </c>
-      <c r="E16" s="7">
-        <v>1.35</v>
+      <c r="D16" s="5">
+        <v>-12.4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-14.27</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-13.82</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.45</v>
+      <c r="D17" s="5">
+        <v>-11.79</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-2.47</v>
       </c>
-      <c r="E18" s="8">
-        <v>-0.52</v>
+      <c r="D18" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.33</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-20.32</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-19.37</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.95</v>
+      <c r="D19" s="5">
+        <v>-17.95</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-29.94</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-30.17</v>
       </c>
-      <c r="E20" s="8">
-        <v>-0.23</v>
+      <c r="D20" s="5">
+        <v>-29.27</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-29.32</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-28.99</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.33</v>
+      <c r="D21" s="5">
+        <v>-28.89</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2262.5</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2289.7</v>
       </c>
-      <c r="E22" s="7">
-        <v>27.2</v>
+      <c r="D22" s="5">
+        <v>2330</v>
+      </c>
+      <c r="E22" s="6">
+        <v>40.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>707.25</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>704.9</v>
       </c>
-      <c r="E23" s="8">
-        <v>-2.35</v>
+      <c r="D23" s="5">
+        <v>714</v>
+      </c>
+      <c r="E23" s="6">
+        <v>9.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>556.65</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>559.25</v>
       </c>
-      <c r="E24" s="7">
-        <v>2.6</v>
+      <c r="D24" s="5">
+        <v>560</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>36.75</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>40.33</v>
       </c>
-      <c r="E25" s="7">
-        <v>3.58</v>
+      <c r="D25" s="5">
+        <v>45.28</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.95</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>45.97</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>45.09</v>
       </c>
-      <c r="E26" s="8">
-        <v>-0.88</v>
+      <c r="D26" s="5">
+        <v>49.15</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>57.91</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>58.96</v>
       </c>
-      <c r="E27" s="7">
-        <v>1.05</v>
+      <c r="D27" s="5">
+        <v>59.27</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>30.17</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>2.61</v>
       </c>
-      <c r="E28" s="8">
-        <v>-27.56</v>
+      <c r="D28" s="5">
+        <v>-4.53</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.14</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-43.98</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-44.49</v>
       </c>
-      <c r="E29" s="8">
-        <v>-0.51</v>
+      <c r="D29" s="5">
+        <v>-40.7</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-47.66</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-66.98999999999999</v>
       </c>
-      <c r="E30" s="8">
-        <v>-19.33</v>
+      <c r="D30" s="5">
+        <v>-65.84</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -1887,60 +1831,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>51.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>1.7</v>
       </c>
-      <c r="G2" s="11">
-        <v>-11</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2042,25 +1986,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1183</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0188</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0425</v>
+      <c r="A2" s="13">
+        <v>0.1227</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0175</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0416</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,8 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -882,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2330</v>
+        <v>2296.9</v>
       </c>
       <c r="D2">
-        <v>1.76</v>
+        <v>-1.42</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -894,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.95</v>
+        <v>-19.11</v>
       </c>
       <c r="H2">
-        <v>7.42</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="J2">
-        <v>-4.26</v>
+        <v>-4.45</v>
       </c>
       <c r="K2">
-        <v>-12.4</v>
+        <v>-15.84</v>
       </c>
       <c r="L2">
-        <v>-13.03</v>
+        <v>-14.32</v>
       </c>
       <c r="M2">
-        <v>12.27</v>
+        <v>11.57</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>2288.4</v>
+        <v>2284.82</v>
       </c>
       <c r="Q2">
-        <v>2346.31</v>
+        <v>2340.71</v>
       </c>
       <c r="R2">
-        <v>2461.16</v>
+        <v>2455.08</v>
       </c>
       <c r="S2">
-        <v>2549.09</v>
+        <v>2547.58</v>
       </c>
       <c r="T2">
-        <v>-8.59</v>
+        <v>-9.84</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +947,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.28</v>
+        <v>42.18</v>
       </c>
       <c r="Z2">
-        <v>-51.29</v>
+        <v>-49.17</v>
       </c>
       <c r="AA2">
-        <v>-54.44</v>
+        <v>-53.39</v>
       </c>
       <c r="AB2">
-        <v>3.15</v>
+        <v>4.21</v>
       </c>
       <c r="AC2">
-        <v>77.75</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AD2">
-        <v>65.33</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AE2">
-        <v>56.94</v>
+        <v>57.1</v>
       </c>
       <c r="AF2">
-        <v>-4.53</v>
+        <v>-14.32</v>
       </c>
       <c r="AG2">
-        <v>2480.49</v>
+        <v>2473.21</v>
       </c>
       <c r="AH2">
-        <v>2212.13</v>
+        <v>2208.2</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -984,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>42.87</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>714</v>
+        <v>710.7</v>
       </c>
       <c r="D3">
-        <v>1.29</v>
+        <v>-0.46</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1007,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.27</v>
+        <v>-29.6</v>
       </c>
       <c r="H3">
-        <v>3.92</v>
+        <v>3.43</v>
       </c>
       <c r="I3">
-        <v>0.36</v>
+        <v>1.13</v>
       </c>
       <c r="J3">
-        <v>2.91</v>
+        <v>0.35</v>
       </c>
       <c r="K3">
-        <v>-11.79</v>
+        <v>-12.85</v>
       </c>
       <c r="L3">
-        <v>-27.05</v>
+        <v>-27.26</v>
       </c>
       <c r="M3">
-        <v>-1.75</v>
+        <v>-2.4</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>704.23</v>
+        <v>705.8200000000001</v>
       </c>
       <c r="Q3">
-        <v>718.55</v>
+        <v>718.26</v>
       </c>
       <c r="R3">
-        <v>719.79</v>
+        <v>718.9400000000001</v>
       </c>
       <c r="S3">
-        <v>804.39</v>
+        <v>802.96</v>
       </c>
       <c r="T3">
-        <v>-11.24</v>
+        <v>-11.49</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>49.15</v>
+        <v>47.77</v>
       </c>
       <c r="Z3">
-        <v>-4.63</v>
+        <v>-4.31</v>
       </c>
       <c r="AA3">
-        <v>-3.79</v>
+        <v>-3.9</v>
       </c>
       <c r="AB3">
-        <v>-0.84</v>
+        <v>-0.41</v>
       </c>
       <c r="AC3">
-        <v>40.85</v>
+        <v>46.43</v>
       </c>
       <c r="AD3">
-        <v>25.06</v>
+        <v>36.59</v>
       </c>
       <c r="AE3">
-        <v>14.59</v>
+        <v>14.3</v>
       </c>
       <c r="AF3">
-        <v>-40.7</v>
+        <v>-23.68</v>
       </c>
       <c r="AG3">
-        <v>745.4</v>
+        <v>745.3200000000001</v>
       </c>
       <c r="AH3">
-        <v>691.7</v>
+        <v>691.1900000000001</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1097,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>560</v>
+        <v>544.05</v>
       </c>
       <c r="D4">
-        <v>0.13</v>
+        <v>-2.85</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1120,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-28.89</v>
+        <v>-30.92</v>
       </c>
       <c r="H4">
-        <v>8.949999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I4">
-        <v>2.95</v>
+        <v>-0.37</v>
       </c>
       <c r="J4">
-        <v>6.43</v>
+        <v>2.65</v>
       </c>
       <c r="K4">
-        <v>0.86</v>
+        <v>-4.34</v>
       </c>
       <c r="L4">
-        <v>-25.06</v>
+        <v>-27.88</v>
       </c>
       <c r="M4">
-        <v>-4.16</v>
+        <v>-4.51</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>553.29</v>
+        <v>552.89</v>
       </c>
       <c r="Q4">
-        <v>542.21</v>
+        <v>543.61</v>
       </c>
       <c r="R4">
-        <v>540.89</v>
+        <v>540.71</v>
       </c>
       <c r="S4">
-        <v>613.28</v>
+        <v>612.22</v>
       </c>
       <c r="T4">
-        <v>-8.69</v>
+        <v>-11.13</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1174,34 +1173,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>59.27</v>
+        <v>50.45</v>
       </c>
       <c r="Z4">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="AA4">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="AB4">
-        <v>3.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC4">
-        <v>98.48999999999999</v>
+        <v>83.19</v>
       </c>
       <c r="AD4">
-        <v>87.20999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="AE4">
-        <v>14.52</v>
+        <v>14.89</v>
       </c>
       <c r="AF4">
-        <v>-65.84</v>
+        <v>-53.41</v>
       </c>
       <c r="AG4">
-        <v>572.53</v>
+        <v>571.33</v>
       </c>
       <c r="AH4">
-        <v>511.89</v>
+        <v>515.89</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1210,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>29.2</v>
+        <v>25.73</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.16</v>
+        <v>-4.26</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.26</v>
+        <v>-4.45</v>
       </c>
       <c r="E7" s="6">
-        <v>1.9</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1425,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="D8" s="5">
-        <v>2.91</v>
+        <v>0.35</v>
       </c>
       <c r="E8" s="6">
-        <v>0.32</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1442,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>8.800000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="D9" s="5">
-        <v>6.43</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.37</v>
+        <v>2.65</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1459,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.4</v>
+        <v>-0.95</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.45</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1476,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="D11" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.35</v>
+        <v>1.13</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1493,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>5.32</v>
+        <v>2.95</v>
       </c>
       <c r="D12" s="5">
-        <v>2.95</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.37</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1510,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-15.78</v>
+        <v>-13.03</v>
       </c>
       <c r="D13" s="5">
-        <v>-13.03</v>
+        <v>-14.32</v>
       </c>
       <c r="E13" s="6">
-        <v>2.75</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1527,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-28.25</v>
+        <v>-27.05</v>
       </c>
       <c r="D14" s="5">
-        <v>-27.05</v>
+        <v>-27.26</v>
       </c>
       <c r="E14" s="6">
-        <v>1.2</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1544,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-25.99</v>
+        <v>-25.06</v>
       </c>
       <c r="D15" s="5">
-        <v>-25.06</v>
+        <v>-27.88</v>
       </c>
       <c r="E15" s="6">
-        <v>0.93</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1561,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-16.71</v>
+        <v>-12.4</v>
       </c>
       <c r="D16" s="5">
-        <v>-12.4</v>
+        <v>-15.84</v>
       </c>
       <c r="E16" s="6">
-        <v>4.31</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1578,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-13.82</v>
+        <v>-11.79</v>
       </c>
       <c r="D17" s="5">
-        <v>-11.79</v>
+        <v>-12.85</v>
       </c>
       <c r="E17" s="6">
-        <v>2.03</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1595,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-2.47</v>
+        <v>0.86</v>
       </c>
       <c r="D18" s="5">
-        <v>0.86</v>
+        <v>-4.34</v>
       </c>
       <c r="E18" s="6">
-        <v>3.33</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1612,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-19.37</v>
+        <v>-17.95</v>
       </c>
       <c r="D19" s="5">
-        <v>-17.95</v>
+        <v>-19.11</v>
       </c>
       <c r="E19" s="6">
-        <v>1.42</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1629,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-30.17</v>
+        <v>-29.27</v>
       </c>
       <c r="D20" s="5">
-        <v>-29.27</v>
+        <v>-29.6</v>
       </c>
       <c r="E20" s="6">
-        <v>0.9</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1646,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-28.99</v>
+        <v>-28.89</v>
       </c>
       <c r="D21" s="5">
-        <v>-28.89</v>
+        <v>-30.92</v>
       </c>
       <c r="E21" s="6">
-        <v>0.1</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1663,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2289.7</v>
+        <v>2330</v>
       </c>
       <c r="D22" s="5">
-        <v>2330</v>
+        <v>2296.9</v>
       </c>
       <c r="E22" s="6">
-        <v>40.3</v>
+        <v>-33.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1680,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>704.9</v>
+        <v>714</v>
       </c>
       <c r="D23" s="5">
-        <v>714</v>
+        <v>710.7</v>
       </c>
       <c r="E23" s="6">
-        <v>9.1</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1697,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>559.25</v>
+        <v>560</v>
       </c>
       <c r="D24" s="5">
-        <v>560</v>
+        <v>544.05</v>
       </c>
       <c r="E24" s="6">
-        <v>0.75</v>
+        <v>-15.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1714,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>40.33</v>
+        <v>45.28</v>
       </c>
       <c r="D25" s="5">
-        <v>45.28</v>
+        <v>42.18</v>
       </c>
       <c r="E25" s="6">
-        <v>4.95</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1731,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>45.09</v>
+        <v>49.15</v>
       </c>
       <c r="D26" s="5">
-        <v>49.15</v>
+        <v>47.77</v>
       </c>
       <c r="E26" s="6">
-        <v>4.06</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1748,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>58.96</v>
+        <v>59.27</v>
       </c>
       <c r="D27" s="5">
-        <v>59.27</v>
+        <v>50.45</v>
       </c>
       <c r="E27" s="6">
-        <v>0.31</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1765,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>2.61</v>
+        <v>-4.53</v>
       </c>
       <c r="D28" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-7.14</v>
+        <v>-14.32</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-9.789999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1782,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-44.49</v>
+        <v>-40.7</v>
       </c>
       <c r="D29" s="5">
-        <v>-40.7</v>
-      </c>
-      <c r="E29" s="6">
-        <v>3.79</v>
+        <v>-23.68</v>
+      </c>
+      <c r="E29" s="7">
+        <v>17.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1799,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-66.98999999999999</v>
+        <v>-65.84</v>
       </c>
       <c r="D30" s="5">
-        <v>-65.84</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.15</v>
+        <v>-53.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>12.43</v>
       </c>
     </row>
   </sheetData>
@@ -1870,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>51.2</v>
+        <v>46.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>1.7</v>
+        <v>-0.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.8</v>
+        <v>-11</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1998,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1227</v>
+        <v>0.1157</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0175</v>
+        <v>-0.024</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0416</v>
+        <v>-0.0451</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>42.2 → 54.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>42.2</t>
+  </si>
+  <si>
+    <t>54.2</t>
+  </si>
+  <si>
+    <t>47.8 → 54.5</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>54.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -741,7 +778,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +920,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2296.9</v>
+        <v>2415</v>
       </c>
       <c r="D2">
-        <v>-1.42</v>
+        <v>5.14</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -893,46 +932,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.11</v>
+        <v>-14.95</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>11.34</v>
       </c>
       <c r="I2">
-        <v>-0.77</v>
+        <v>7.57</v>
       </c>
       <c r="J2">
-        <v>-4.45</v>
+        <v>0.25</v>
       </c>
       <c r="K2">
-        <v>-15.84</v>
+        <v>-7.19</v>
       </c>
       <c r="L2">
-        <v>-14.32</v>
+        <v>-10.59</v>
       </c>
       <c r="M2">
-        <v>11.57</v>
+        <v>12.85</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="P2">
-        <v>2284.82</v>
+        <v>2318.82</v>
       </c>
       <c r="Q2">
-        <v>2340.71</v>
+        <v>2342.8</v>
       </c>
       <c r="R2">
-        <v>2455.08</v>
+        <v>2452.26</v>
       </c>
       <c r="S2">
-        <v>2547.58</v>
+        <v>2546.7</v>
       </c>
       <c r="T2">
-        <v>-9.84</v>
+        <v>-5.17</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +986,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.18</v>
+        <v>54.2</v>
       </c>
       <c r="Z2">
-        <v>-49.17</v>
+        <v>-37.53</v>
       </c>
       <c r="AA2">
-        <v>-53.39</v>
+        <v>-50.22</v>
       </c>
       <c r="AB2">
-        <v>4.21</v>
+        <v>12.68</v>
       </c>
       <c r="AC2">
-        <v>86.70999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>74.65000000000001</v>
+        <v>86.41</v>
       </c>
       <c r="AE2">
-        <v>57.1</v>
+        <v>63.54</v>
       </c>
       <c r="AF2">
-        <v>-14.32</v>
+        <v>95.8</v>
       </c>
       <c r="AG2">
-        <v>2473.21</v>
+        <v>2478.74</v>
       </c>
       <c r="AH2">
-        <v>2208.2</v>
+        <v>2206.86</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -983,7 +1022,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.3</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1033,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>710.7</v>
+        <v>726.85</v>
       </c>
       <c r="D3">
-        <v>-0.46</v>
+        <v>2.27</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1045,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.6</v>
+        <v>-28</v>
       </c>
       <c r="H3">
-        <v>3.43</v>
+        <v>5.79</v>
       </c>
       <c r="I3">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>0.35</v>
+        <v>1.44</v>
       </c>
       <c r="K3">
-        <v>-12.85</v>
+        <v>-10.08</v>
       </c>
       <c r="L3">
-        <v>-27.26</v>
+        <v>-25.9</v>
       </c>
       <c r="M3">
-        <v>-2.4</v>
+        <v>-1.77</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>705.8200000000001</v>
+        <v>712.74</v>
       </c>
       <c r="Q3">
-        <v>718.26</v>
+        <v>718.52</v>
       </c>
       <c r="R3">
-        <v>718.9400000000001</v>
+        <v>718.64</v>
       </c>
       <c r="S3">
-        <v>802.96</v>
+        <v>801.63</v>
       </c>
       <c r="T3">
-        <v>-11.49</v>
+        <v>-9.33</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1099,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.77</v>
+        <v>54.5</v>
       </c>
       <c r="Z3">
-        <v>-4.31</v>
+        <v>-2.72</v>
       </c>
       <c r="AA3">
-        <v>-3.9</v>
+        <v>-3.66</v>
       </c>
       <c r="AB3">
-        <v>-0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC3">
-        <v>46.43</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="AD3">
-        <v>36.59</v>
+        <v>51.23</v>
       </c>
       <c r="AE3">
-        <v>14.3</v>
+        <v>14.52</v>
       </c>
       <c r="AF3">
-        <v>-23.68</v>
+        <v>19.51</v>
       </c>
       <c r="AG3">
-        <v>745.3200000000001</v>
+        <v>745.83</v>
       </c>
       <c r="AH3">
-        <v>691.1900000000001</v>
+        <v>691.22</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1096,7 +1135,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>15.25</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1146,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>544.05</v>
+        <v>550.55</v>
       </c>
       <c r="D4">
-        <v>-2.85</v>
+        <v>1.19</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1119,46 +1158,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.92</v>
+        <v>-30.09</v>
       </c>
       <c r="H4">
-        <v>5.85</v>
+        <v>7.11</v>
       </c>
       <c r="I4">
-        <v>-0.37</v>
+        <v>1.11</v>
       </c>
       <c r="J4">
-        <v>2.65</v>
+        <v>6.68</v>
       </c>
       <c r="K4">
-        <v>-4.34</v>
+        <v>-3</v>
       </c>
       <c r="L4">
-        <v>-27.88</v>
+        <v>-26.33</v>
       </c>
       <c r="M4">
-        <v>-4.51</v>
+        <v>-4.56</v>
       </c>
       <c r="N4">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>552.89</v>
+        <v>554.1</v>
       </c>
       <c r="Q4">
-        <v>543.61</v>
+        <v>544.63</v>
       </c>
       <c r="R4">
-        <v>540.71</v>
+        <v>541</v>
       </c>
       <c r="S4">
-        <v>612.22</v>
+        <v>611.23</v>
       </c>
       <c r="T4">
-        <v>-11.13</v>
+        <v>-9.93</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1173,34 +1212,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.45</v>
+        <v>53.49</v>
       </c>
       <c r="Z4">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="AA4">
-        <v>0.75</v>
+        <v>1.21</v>
       </c>
       <c r="AB4">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AC4">
-        <v>83.19</v>
+        <v>72.17</v>
       </c>
       <c r="AD4">
-        <v>89.45999999999999</v>
+        <v>84.61</v>
       </c>
       <c r="AE4">
-        <v>14.89</v>
+        <v>14.79</v>
       </c>
       <c r="AF4">
-        <v>-53.41</v>
+        <v>-63.43</v>
       </c>
       <c r="AG4">
-        <v>571.33</v>
+        <v>571.76</v>
       </c>
       <c r="AH4">
-        <v>515.89</v>
+        <v>517.49</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1209,7 +1248,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.73</v>
+        <v>22.72</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,447 +1409,536 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-4.45</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>2.91</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>0.35</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>6.43</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>2.65</v>
       </c>
-      <c r="E9" s="6">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>6.68</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-0.77</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>7.57</v>
+      </c>
+      <c r="E11" s="7">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>1.13</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.95</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-0.37</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>1.11</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-13.03</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-14.32</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-27.05</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-27.26</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-25.9</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-25.06</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-27.88</v>
       </c>
-      <c r="E15" s="6">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-26.33</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-12.4</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-15.84</v>
       </c>
-      <c r="E16" s="6">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-7.19</v>
+      </c>
+      <c r="E17" s="7">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-11.79</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-12.85</v>
       </c>
-      <c r="E17" s="6">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.86</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-4.34</v>
       </c>
-      <c r="E18" s="6">
-        <v>-5.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-17.95</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-19.11</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-14.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-29.27</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-29.6</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-28</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-28.89</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-30.92</v>
       </c>
-      <c r="E21" s="6">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-30.09</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2330</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>2296.9</v>
       </c>
-      <c r="E22" s="6">
-        <v>-33.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>2415</v>
+      </c>
+      <c r="E23" s="7">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>714</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>710.7</v>
       </c>
-      <c r="E23" s="6">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>726.85</v>
+      </c>
+      <c r="E24" s="7">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>560</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>544.05</v>
       </c>
-      <c r="E24" s="6">
-        <v>-15.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>550.55</v>
+      </c>
+      <c r="E25" s="7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="6">
+        <v>99</v>
+      </c>
+      <c r="D27" s="6">
+        <v>66</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>45.28</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C28" s="6">
         <v>42.18</v>
       </c>
-      <c r="E25" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D28" s="6">
+        <v>54.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>49.15</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C29" s="6">
         <v>47.77</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D29" s="6">
+        <v>54.5</v>
+      </c>
+      <c r="E29" s="7">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>59.27</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C30" s="6">
         <v>50.45</v>
       </c>
-      <c r="E27" s="6">
-        <v>-8.82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D30" s="6">
+        <v>53.49</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C31" s="6">
         <v>-14.32</v>
       </c>
-      <c r="E28" s="6">
-        <v>-9.789999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D31" s="6">
+        <v>95.8</v>
+      </c>
+      <c r="E31" s="7">
+        <v>110.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-40.7</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C32" s="6">
         <v>-23.68</v>
       </c>
-      <c r="E29" s="7">
-        <v>17.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D32" s="6">
+        <v>19.51</v>
+      </c>
+      <c r="E32" s="7">
+        <v>43.19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-65.84</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C33" s="6">
         <v>-53.41</v>
       </c>
-      <c r="E30" s="7">
-        <v>12.43</v>
+      <c r="D33" s="6">
+        <v>-63.43</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-10.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1830,60 +1958,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>54.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-11</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2113,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1157</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.024</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0451</v>
+      <c r="A2" s="14">
+        <v>0.1285</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0177</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.04559999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,28 +172,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>42.2 → 54.2</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>42.2</t>
-  </si>
-  <si>
-    <t>54.2</t>
-  </si>
-  <si>
-    <t>47.8 → 54.5</t>
-  </si>
-  <si>
-    <t>47.8</t>
-  </si>
-  <si>
-    <t>54.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -778,16 +763,13 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -920,10 +902,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2415</v>
+        <v>2398.6</v>
       </c>
       <c r="D2">
-        <v>5.14</v>
+        <v>-0.68</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -932,46 +914,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-14.95</v>
+        <v>-15.53</v>
       </c>
       <c r="H2">
-        <v>11.34</v>
+        <v>10.59</v>
       </c>
       <c r="I2">
-        <v>7.57</v>
+        <v>6.02</v>
       </c>
       <c r="J2">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="K2">
-        <v>-7.19</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L2">
-        <v>-10.59</v>
+        <v>-13.53</v>
       </c>
       <c r="M2">
-        <v>12.85</v>
+        <v>12.69</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>2318.82</v>
+        <v>2346.04</v>
       </c>
       <c r="Q2">
-        <v>2342.8</v>
+        <v>2343.35</v>
       </c>
       <c r="R2">
-        <v>2452.26</v>
+        <v>2448.99</v>
       </c>
       <c r="S2">
-        <v>2546.7</v>
+        <v>2545.74</v>
       </c>
       <c r="T2">
-        <v>-5.17</v>
+        <v>-5.78</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -986,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>54.2</v>
+        <v>52.57</v>
       </c>
       <c r="Z2">
-        <v>-37.53</v>
+        <v>-29.3</v>
       </c>
       <c r="AA2">
-        <v>-50.22</v>
+        <v>-46.03</v>
       </c>
       <c r="AB2">
-        <v>12.68</v>
+        <v>16.74</v>
       </c>
       <c r="AC2">
-        <v>94.76000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="AD2">
-        <v>86.41</v>
+        <v>91.44</v>
       </c>
       <c r="AE2">
-        <v>63.54</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AF2">
-        <v>95.8</v>
+        <v>63.94</v>
       </c>
       <c r="AG2">
-        <v>2478.74</v>
+        <v>2480.13</v>
       </c>
       <c r="AH2">
-        <v>2206.86</v>
+        <v>2206.56</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1022,7 +1004,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>37.97</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,10 +1015,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>726.85</v>
+        <v>728.85</v>
       </c>
       <c r="D3">
-        <v>2.27</v>
+        <v>0.28</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1045,49 +1027,49 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-28</v>
+        <v>-27.8</v>
       </c>
       <c r="H3">
-        <v>5.79</v>
+        <v>6.08</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="K3">
-        <v>-10.08</v>
+        <v>-11.07</v>
       </c>
       <c r="L3">
-        <v>-25.9</v>
+        <v>-25.4</v>
       </c>
       <c r="M3">
-        <v>-1.77</v>
+        <v>-1.71</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>712.74</v>
+        <v>717.0599999999999</v>
       </c>
       <c r="Q3">
-        <v>718.52</v>
+        <v>719.3099999999999</v>
       </c>
       <c r="R3">
-        <v>718.64</v>
+        <v>718.51</v>
       </c>
       <c r="S3">
-        <v>801.63</v>
+        <v>800.3200000000001</v>
       </c>
       <c r="T3">
-        <v>-9.33</v>
+        <v>-8.93</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3" t="s">
         <v>41</v>
@@ -1096,37 +1078,37 @@
         <v>41</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>54.5</v>
+        <v>55.27</v>
       </c>
       <c r="Z3">
-        <v>-2.72</v>
+        <v>-1.29</v>
       </c>
       <c r="AA3">
-        <v>-3.66</v>
+        <v>-3.19</v>
       </c>
       <c r="AB3">
-        <v>0.9399999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>66.43000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="AD3">
-        <v>51.23</v>
+        <v>64.75</v>
       </c>
       <c r="AE3">
-        <v>14.52</v>
+        <v>14.24</v>
       </c>
       <c r="AF3">
-        <v>19.51</v>
+        <v>-4.79</v>
       </c>
       <c r="AG3">
-        <v>745.83</v>
+        <v>746.87</v>
       </c>
       <c r="AH3">
-        <v>691.22</v>
+        <v>691.76</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1135,7 +1117,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>18.21</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,10 +1128,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>550.55</v>
+        <v>553</v>
       </c>
       <c r="D4">
-        <v>1.19</v>
+        <v>0.45</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1158,46 +1140,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.09</v>
+        <v>-29.78</v>
       </c>
       <c r="H4">
-        <v>7.11</v>
+        <v>7.59</v>
       </c>
       <c r="I4">
-        <v>1.11</v>
+        <v>-0.66</v>
       </c>
       <c r="J4">
-        <v>6.68</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>-3</v>
+        <v>-1.89</v>
       </c>
       <c r="L4">
-        <v>-26.33</v>
+        <v>-25.93</v>
       </c>
       <c r="M4">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>554.1</v>
+        <v>553.37</v>
       </c>
       <c r="Q4">
-        <v>544.63</v>
+        <v>544.4299999999999</v>
       </c>
       <c r="R4">
-        <v>541</v>
+        <v>541.16</v>
       </c>
       <c r="S4">
-        <v>611.23</v>
+        <v>610.26</v>
       </c>
       <c r="T4">
-        <v>-9.93</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1212,34 +1194,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>53.49</v>
+        <v>54.62</v>
       </c>
       <c r="Z4">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="AA4">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="AB4">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AC4">
-        <v>72.17</v>
+        <v>63.3</v>
       </c>
       <c r="AD4">
-        <v>84.61</v>
+        <v>72.88</v>
       </c>
       <c r="AE4">
-        <v>14.79</v>
+        <v>15.32</v>
       </c>
       <c r="AF4">
-        <v>-63.43</v>
+        <v>19.14</v>
       </c>
       <c r="AG4">
-        <v>571.76</v>
+        <v>571.24</v>
       </c>
       <c r="AH4">
-        <v>517.49</v>
+        <v>517.61</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1248,7 +1230,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.72</v>
+        <v>21.76</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1429,7 +1411,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -1441,379 +1423,376 @@
         <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.45</v>
+        <v>1.44</v>
       </c>
       <c r="D8" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4.7</v>
+        <v>1.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.35</v>
+        <v>6.68</v>
       </c>
       <c r="D9" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.09</v>
+        <v>4.3</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>2.65</v>
+        <v>7.57</v>
       </c>
       <c r="D10" s="6">
-        <v>6.68</v>
-      </c>
-      <c r="E10" s="7">
-        <v>4.03</v>
+        <v>6.02</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.77</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6">
-        <v>7.57</v>
-      </c>
-      <c r="E11" s="7">
-        <v>8.34</v>
+        <v>3.05</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="D12" s="6">
-        <v>5</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3.87</v>
+        <v>-0.66</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.37</v>
+        <v>-10.59</v>
       </c>
       <c r="D13" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.48</v>
+        <v>-13.53</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-14.32</v>
+        <v>-25.9</v>
       </c>
       <c r="D14" s="6">
-        <v>-10.59</v>
+        <v>-25.4</v>
       </c>
       <c r="E14" s="7">
-        <v>3.73</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.26</v>
+        <v>-26.33</v>
       </c>
       <c r="D15" s="6">
-        <v>-25.9</v>
+        <v>-25.93</v>
       </c>
       <c r="E15" s="7">
-        <v>1.36</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-27.88</v>
+        <v>-7.19</v>
       </c>
       <c r="D16" s="6">
-        <v>-26.33</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.55</v>
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-15.84</v>
+        <v>-10.08</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.19</v>
-      </c>
-      <c r="E17" s="7">
-        <v>8.65</v>
+        <v>-11.07</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-12.85</v>
+        <v>-3</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.08</v>
+        <v>-1.89</v>
       </c>
       <c r="E18" s="7">
-        <v>2.77</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.34</v>
+        <v>-14.95</v>
       </c>
       <c r="D19" s="6">
-        <v>-3</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.34</v>
+        <v>-15.53</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-19.11</v>
+        <v>-28</v>
       </c>
       <c r="D20" s="6">
-        <v>-14.95</v>
+        <v>-27.8</v>
       </c>
       <c r="E20" s="7">
-        <v>4.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-29.6</v>
+        <v>-30.09</v>
       </c>
       <c r="D21" s="6">
-        <v>-28</v>
+        <v>-29.78</v>
       </c>
       <c r="E21" s="7">
-        <v>1.6</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>-30.92</v>
+        <v>2415</v>
       </c>
       <c r="D22" s="6">
-        <v>-30.09</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.83</v>
+        <v>2398.6</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-16.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>2296.9</v>
+        <v>726.85</v>
       </c>
       <c r="D23" s="6">
-        <v>2415</v>
+        <v>728.85</v>
       </c>
       <c r="E23" s="7">
-        <v>118.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>710.7</v>
+        <v>550.55</v>
       </c>
       <c r="D24" s="6">
-        <v>726.85</v>
+        <v>553</v>
       </c>
       <c r="E24" s="7">
-        <v>16.15</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>544.05</v>
+        <v>54.2</v>
       </c>
       <c r="D25" s="6">
-        <v>550.55</v>
-      </c>
-      <c r="E25" s="7">
-        <v>6.5</v>
+        <v>52.57</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>66</v>
+        <v>54.5</v>
       </c>
       <c r="D26" s="6">
-        <v>99</v>
+        <v>55.27</v>
       </c>
       <c r="E26" s="7">
-        <v>33</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1821,16 +1800,16 @@
         <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>99</v>
+        <v>53.49</v>
       </c>
       <c r="D27" s="6">
-        <v>66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-33</v>
+        <v>54.62</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1838,16 +1817,16 @@
         <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>42.18</v>
+        <v>95.8</v>
       </c>
       <c r="D28" s="6">
-        <v>54.2</v>
-      </c>
-      <c r="E28" s="7">
-        <v>12.02</v>
+        <v>63.94</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-31.86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1855,16 +1834,16 @@
         <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>47.77</v>
+        <v>19.51</v>
       </c>
       <c r="D29" s="6">
-        <v>54.5</v>
-      </c>
-      <c r="E29" s="7">
-        <v>6.73</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-24.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1872,73 +1851,22 @@
         <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>50.45</v>
+        <v>-63.43</v>
       </c>
       <c r="D30" s="6">
-        <v>53.49</v>
+        <v>19.14</v>
       </c>
       <c r="E30" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-14.32</v>
-      </c>
-      <c r="D31" s="6">
-        <v>95.8</v>
-      </c>
-      <c r="E31" s="7">
-        <v>110.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.68</v>
-      </c>
-      <c r="D32" s="6">
-        <v>19.51</v>
-      </c>
-      <c r="E32" s="7">
-        <v>43.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-53.41</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-63.43</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-10.02</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1962,28 +1890,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1997,16 +1925,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.8</v>
+        <v>-7.5</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2125,13 +2053,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1285</v>
+        <v>0.1269</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0177</v>
+        <v>-0.0171</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.04559999999999999</v>
+        <v>-0.0447</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,13 +172,25 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.6 → 47.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>55.3 → 47.9</t>
+  </si>
+  <si>
+    <t>55.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +276,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,7 +781,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -902,10 +915,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2398.6</v>
+        <v>2349.2</v>
       </c>
       <c r="D2">
-        <v>-0.68</v>
+        <v>-2.06</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -914,46 +927,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.53</v>
+        <v>-17.27</v>
       </c>
       <c r="H2">
-        <v>10.59</v>
+        <v>8.31</v>
       </c>
       <c r="I2">
-        <v>6.02</v>
+        <v>2.6</v>
       </c>
       <c r="J2">
-        <v>1.07</v>
+        <v>-1.61</v>
       </c>
       <c r="K2">
-        <v>-9.529999999999999</v>
+        <v>-11.18</v>
       </c>
       <c r="L2">
-        <v>-13.53</v>
+        <v>-14.17</v>
       </c>
       <c r="M2">
-        <v>12.69</v>
+        <v>12.42</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>2346.04</v>
+        <v>2357.94</v>
       </c>
       <c r="Q2">
-        <v>2343.35</v>
+        <v>2339.56</v>
       </c>
       <c r="R2">
-        <v>2448.99</v>
+        <v>2445.22</v>
       </c>
       <c r="S2">
-        <v>2545.74</v>
+        <v>2544.62</v>
       </c>
       <c r="T2">
-        <v>-5.78</v>
+        <v>-7.68</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -968,34 +981,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>52.57</v>
+        <v>47.88</v>
       </c>
       <c r="Z2">
-        <v>-29.3</v>
+        <v>-26.45</v>
       </c>
       <c r="AA2">
-        <v>-46.03</v>
+        <v>-42.11</v>
       </c>
       <c r="AB2">
-        <v>16.74</v>
+        <v>15.67</v>
       </c>
       <c r="AC2">
-        <v>92.84999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="AD2">
-        <v>91.44</v>
+        <v>92.78</v>
       </c>
       <c r="AE2">
-        <v>64.76000000000001</v>
+        <v>65.58</v>
       </c>
       <c r="AF2">
-        <v>63.94</v>
+        <v>-40.5</v>
       </c>
       <c r="AG2">
-        <v>2480.13</v>
+        <v>2470.91</v>
       </c>
       <c r="AH2">
-        <v>2206.56</v>
+        <v>2208.2</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1004,7 +1017,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>37.4</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1028,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>728.85</v>
+        <v>712</v>
       </c>
       <c r="D3">
-        <v>0.28</v>
+        <v>-2.31</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1027,46 +1040,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-27.8</v>
+        <v>-29.47</v>
       </c>
       <c r="H3">
-        <v>6.08</v>
+        <v>3.62</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="J3">
-        <v>1.02</v>
+        <v>-0.14</v>
       </c>
       <c r="K3">
-        <v>-11.07</v>
+        <v>-8.44</v>
       </c>
       <c r="L3">
-        <v>-25.4</v>
+        <v>-27.14</v>
       </c>
       <c r="M3">
-        <v>-1.71</v>
+        <v>-2.38</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>717.0599999999999</v>
+        <v>718.48</v>
       </c>
       <c r="Q3">
-        <v>719.3099999999999</v>
+        <v>718.36</v>
       </c>
       <c r="R3">
-        <v>718.51</v>
+        <v>718.0700000000001</v>
       </c>
       <c r="S3">
-        <v>800.3200000000001</v>
+        <v>798.92</v>
       </c>
       <c r="T3">
-        <v>-8.93</v>
+        <v>-10.88</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1081,34 +1094,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>55.27</v>
+        <v>47.93</v>
       </c>
       <c r="Z3">
-        <v>-1.29</v>
+        <v>-1.49</v>
       </c>
       <c r="AA3">
-        <v>-3.19</v>
+        <v>-2.85</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AC3">
-        <v>81.39</v>
+        <v>82.34</v>
       </c>
       <c r="AD3">
-        <v>64.75</v>
+        <v>76.72</v>
       </c>
       <c r="AE3">
-        <v>14.24</v>
+        <v>15.09</v>
       </c>
       <c r="AF3">
-        <v>-4.79</v>
+        <v>10.08</v>
       </c>
       <c r="AG3">
-        <v>746.87</v>
+        <v>745.53</v>
       </c>
       <c r="AH3">
-        <v>691.76</v>
+        <v>691.2</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1117,7 +1130,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>22.15</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1141,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>553</v>
+        <v>545.5</v>
       </c>
       <c r="D4">
-        <v>0.45</v>
+        <v>-1.36</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1140,46 +1153,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-29.78</v>
+        <v>-30.73</v>
       </c>
       <c r="H4">
-        <v>7.59</v>
+        <v>6.13</v>
       </c>
       <c r="I4">
-        <v>-0.66</v>
+        <v>-2.46</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>-2.06</v>
       </c>
       <c r="K4">
-        <v>-1.89</v>
+        <v>-3.39</v>
       </c>
       <c r="L4">
-        <v>-25.93</v>
+        <v>-26.64</v>
       </c>
       <c r="M4">
-        <v>-4.47</v>
+        <v>-4.71</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>553.37</v>
+        <v>550.62</v>
       </c>
       <c r="Q4">
-        <v>544.4299999999999</v>
+        <v>544.15</v>
       </c>
       <c r="R4">
-        <v>541.16</v>
+        <v>541.22</v>
       </c>
       <c r="S4">
-        <v>610.26</v>
+        <v>609.27</v>
       </c>
       <c r="T4">
-        <v>-9.380000000000001</v>
+        <v>-10.47</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1194,34 +1207,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>54.62</v>
+        <v>50.57</v>
       </c>
       <c r="Z4">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="AA4">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AB4">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="AC4">
-        <v>63.3</v>
+        <v>63.52</v>
       </c>
       <c r="AD4">
-        <v>72.88</v>
+        <v>66.33</v>
       </c>
       <c r="AE4">
-        <v>15.32</v>
+        <v>15.18</v>
       </c>
       <c r="AF4">
-        <v>19.14</v>
+        <v>-66.34</v>
       </c>
       <c r="AG4">
-        <v>571.24</v>
+        <v>570.79</v>
       </c>
       <c r="AH4">
-        <v>517.61</v>
+        <v>517.51</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1230,12 +1243,72 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>21.76</v>
+        <v>20.55</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK4"/>
   <conditionalFormatting sqref="AF2:AF4">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1247,8 +1320,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N4">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1259,72 +1338,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T4">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
@@ -1334,26 +1347,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1371,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1411,7 +1424,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -1423,359 +1436,362 @@
         <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.82</v>
+      <c r="B7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="D8" s="6">
-        <v>1.02</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.42</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>6.68</v>
+        <v>1.02</v>
       </c>
       <c r="D9" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-2.38</v>
+        <v>-0.14</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>7.57</v>
+        <v>4.3</v>
       </c>
       <c r="D10" s="6">
-        <v>6.02</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.55</v>
+        <v>-2.06</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-6.36</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>5</v>
+        <v>6.02</v>
       </c>
       <c r="D11" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.95</v>
+        <v>2.6</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.77</v>
+        <v>1.01</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.59</v>
+        <v>-0.66</v>
       </c>
       <c r="D13" s="6">
-        <v>-13.53</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.94</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-25.9</v>
+        <v>-13.53</v>
       </c>
       <c r="D14" s="6">
-        <v>-25.4</v>
+        <v>-14.17</v>
       </c>
       <c r="E14" s="7">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-26.33</v>
+        <v>-25.4</v>
       </c>
       <c r="D15" s="6">
-        <v>-25.93</v>
+        <v>-27.14</v>
       </c>
       <c r="E15" s="7">
-        <v>0.4</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.19</v>
+        <v>-25.93</v>
       </c>
       <c r="D16" s="6">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.34</v>
+        <v>-26.64</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-10.08</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="D17" s="6">
-        <v>-11.07</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.99</v>
+        <v>-11.18</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-3</v>
+        <v>-11.07</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.11</v>
+        <v>-8.44</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-14.95</v>
+        <v>-1.89</v>
       </c>
       <c r="D19" s="6">
-        <v>-15.53</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.58</v>
+        <v>-3.39</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-28</v>
+        <v>-15.53</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.8</v>
+        <v>-17.27</v>
       </c>
       <c r="E20" s="7">
-        <v>0.2</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-30.09</v>
+        <v>-27.8</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.78</v>
+        <v>-29.47</v>
       </c>
       <c r="E21" s="7">
-        <v>0.31</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>2415</v>
+        <v>-29.78</v>
       </c>
       <c r="D22" s="6">
-        <v>2398.6</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-16.4</v>
+        <v>-30.73</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>726.85</v>
+        <v>2398.6</v>
       </c>
       <c r="D23" s="6">
-        <v>728.85</v>
+        <v>2349.2</v>
       </c>
       <c r="E23" s="7">
-        <v>2</v>
+        <v>-49.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>550.55</v>
+        <v>728.85</v>
       </c>
       <c r="D24" s="6">
-        <v>553</v>
+        <v>712</v>
       </c>
       <c r="E24" s="7">
-        <v>2.45</v>
+        <v>-16.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>54.2</v>
+        <v>553</v>
       </c>
       <c r="D25" s="6">
-        <v>52.57</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.63</v>
+        <v>545.5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1783,90 +1799,124 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="6">
-        <v>54.5</v>
+        <v>34</v>
       </c>
       <c r="D26" s="6">
-        <v>55.27</v>
+        <v>33</v>
       </c>
       <c r="E26" s="7">
-        <v>0.77</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>53.49</v>
+        <v>52.57</v>
       </c>
       <c r="D27" s="6">
-        <v>54.62</v>
+        <v>47.88</v>
       </c>
       <c r="E27" s="7">
-        <v>1.13</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>95.8</v>
+        <v>55.27</v>
       </c>
       <c r="D28" s="6">
-        <v>63.94</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-31.86</v>
+        <v>47.93</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.34</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="6">
-        <v>19.51</v>
+        <v>54.62</v>
       </c>
       <c r="D29" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-24.3</v>
+        <v>50.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-63.43</v>
+        <v>63.94</v>
       </c>
       <c r="D30" s="6">
+        <v>-40.5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-104.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="D31" s="6">
+        <v>10.08</v>
+      </c>
+      <c r="E31" s="8">
+        <v>14.87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="6">
         <v>19.14</v>
       </c>
-      <c r="E30" s="7">
-        <v>82.56999999999999</v>
+      <c r="D32" s="6">
+        <v>-66.34</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-85.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1890,28 +1940,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1919,25 +1969,25 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>36.52</v>
+        <v>36.40000000000001</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>54.2</v>
+        <v>48.8</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="H2" s="11">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="I2" s="11">
         <v>0</v>
@@ -2053,13 +2103,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1269</v>
+        <v>0.1242</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0171</v>
+        <v>-0.0238</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0447</v>
+        <v>-0.0471</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,25 +172,25 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.6 → 47.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>55.3 → 47.9</t>
-  </si>
-  <si>
-    <t>55.3</t>
+    <t>50.6 → 47.6</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>47.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -915,10 +915,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2349.2</v>
+        <v>2311.4</v>
       </c>
       <c r="D2">
-        <v>-2.06</v>
+        <v>-1.61</v>
       </c>
       <c r="E2">
         <v>2839.64</v>
@@ -927,46 +927,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.27</v>
+        <v>-18.6</v>
       </c>
       <c r="H2">
-        <v>8.31</v>
+        <v>6.57</v>
       </c>
       <c r="I2">
-        <v>2.6</v>
+        <v>-0.8</v>
       </c>
       <c r="J2">
-        <v>-1.61</v>
+        <v>-4.68</v>
       </c>
       <c r="K2">
-        <v>-11.18</v>
+        <v>-10.45</v>
       </c>
       <c r="L2">
-        <v>-14.17</v>
+        <v>-18.04</v>
       </c>
       <c r="M2">
-        <v>12.42</v>
+        <v>12.55</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>2357.94</v>
+        <v>2354.22</v>
       </c>
       <c r="Q2">
-        <v>2339.56</v>
+        <v>2333.12</v>
       </c>
       <c r="R2">
-        <v>2445.22</v>
+        <v>2440.54</v>
       </c>
       <c r="S2">
-        <v>2544.62</v>
+        <v>2543.1</v>
       </c>
       <c r="T2">
-        <v>-7.68</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -981,34 +981,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>47.88</v>
+        <v>44.61</v>
       </c>
       <c r="Z2">
-        <v>-26.45</v>
+        <v>-26.93</v>
       </c>
       <c r="AA2">
-        <v>-42.11</v>
+        <v>-39.08</v>
       </c>
       <c r="AB2">
-        <v>15.67</v>
+        <v>12.15</v>
       </c>
       <c r="AC2">
-        <v>90.73</v>
+        <v>74.78</v>
       </c>
       <c r="AD2">
-        <v>92.78</v>
+        <v>86.12</v>
       </c>
       <c r="AE2">
-        <v>65.58</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AF2">
-        <v>-40.5</v>
+        <v>-34.8</v>
       </c>
       <c r="AG2">
-        <v>2470.91</v>
+        <v>2456.1</v>
       </c>
       <c r="AH2">
-        <v>2208.2</v>
+        <v>2210.15</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1017,7 +1017,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>34.32</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1028,10 +1028,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>712</v>
+        <v>706.95</v>
       </c>
       <c r="D3">
-        <v>-2.31</v>
+        <v>-0.71</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1040,22 +1040,22 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.47</v>
+        <v>-29.97</v>
       </c>
       <c r="H3">
-        <v>3.62</v>
+        <v>2.89</v>
       </c>
       <c r="I3">
-        <v>1.01</v>
+        <v>-0.99</v>
       </c>
       <c r="J3">
-        <v>-0.14</v>
+        <v>-3.29</v>
       </c>
       <c r="K3">
-        <v>-8.44</v>
+        <v>-7.16</v>
       </c>
       <c r="L3">
-        <v>-27.14</v>
+        <v>-27.73</v>
       </c>
       <c r="M3">
         <v>-2.38</v>
@@ -1064,25 +1064,25 @@
         <v>33</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>718.48</v>
+        <v>717.0700000000001</v>
       </c>
       <c r="Q3">
-        <v>718.36</v>
+        <v>716.74</v>
       </c>
       <c r="R3">
-        <v>718.0700000000001</v>
+        <v>717.59</v>
       </c>
       <c r="S3">
-        <v>798.92</v>
+        <v>797.5</v>
       </c>
       <c r="T3">
-        <v>-10.88</v>
+        <v>-11.35</v>
       </c>
       <c r="U3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
         <v>41</v>
@@ -1091,37 +1091,37 @@
         <v>41</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.93</v>
+        <v>45.95</v>
       </c>
       <c r="Z3">
-        <v>-1.49</v>
+        <v>-2.04</v>
       </c>
       <c r="AA3">
-        <v>-2.85</v>
+        <v>-2.69</v>
       </c>
       <c r="AB3">
-        <v>1.36</v>
+        <v>0.65</v>
       </c>
       <c r="AC3">
-        <v>82.34</v>
+        <v>66.06</v>
       </c>
       <c r="AD3">
-        <v>76.72</v>
+        <v>76.59</v>
       </c>
       <c r="AE3">
-        <v>15.09</v>
+        <v>15.24</v>
       </c>
       <c r="AF3">
-        <v>10.08</v>
+        <v>-14.36</v>
       </c>
       <c r="AG3">
-        <v>745.53</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="AH3">
-        <v>691.2</v>
+        <v>691.05</v>
       </c>
       <c r="AI3">
         <v>742.71</v>
@@ -1130,7 +1130,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>19.26</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1141,10 +1141,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>545.5</v>
+        <v>539.65</v>
       </c>
       <c r="D4">
-        <v>-1.36</v>
+        <v>-1.07</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1153,46 +1153,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-30.73</v>
+        <v>-31.48</v>
       </c>
       <c r="H4">
-        <v>6.13</v>
+        <v>4.99</v>
       </c>
       <c r="I4">
-        <v>-2.46</v>
+        <v>-3.63</v>
       </c>
       <c r="J4">
-        <v>-2.06</v>
+        <v>-2.05</v>
       </c>
       <c r="K4">
-        <v>-3.39</v>
+        <v>-3.81</v>
       </c>
       <c r="L4">
-        <v>-26.64</v>
+        <v>-29.1</v>
       </c>
       <c r="M4">
-        <v>-4.71</v>
+        <v>-4.69</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>550.62</v>
+        <v>546.55</v>
       </c>
       <c r="Q4">
-        <v>544.15</v>
+        <v>543.17</v>
       </c>
       <c r="R4">
-        <v>541.22</v>
+        <v>541.21</v>
       </c>
       <c r="S4">
-        <v>609.27</v>
+        <v>608.22</v>
       </c>
       <c r="T4">
-        <v>-10.47</v>
+        <v>-11.27</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1207,34 +1207,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.57</v>
+        <v>47.61</v>
       </c>
       <c r="Z4">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="AA4">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>1.01</v>
+        <v>0.14</v>
       </c>
       <c r="AC4">
-        <v>63.52</v>
+        <v>52.31</v>
       </c>
       <c r="AD4">
-        <v>66.33</v>
+        <v>59.71</v>
       </c>
       <c r="AE4">
-        <v>15.18</v>
+        <v>15.24</v>
       </c>
       <c r="AF4">
-        <v>-66.34</v>
+        <v>-67.12</v>
       </c>
       <c r="AG4">
-        <v>570.79</v>
+        <v>568.87</v>
       </c>
       <c r="AH4">
-        <v>517.51</v>
+        <v>517.46</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1243,7 +1243,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.55</v>
+        <v>22.17</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -1436,30 +1436,30 @@
         <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1496,13 +1496,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>1.07</v>
+        <v>-1.61</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.61</v>
+        <v>-4.68</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.68</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1513,13 +1513,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>1.02</v>
+        <v>-0.14</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.14</v>
+        <v>-3.29</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.16</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1530,13 +1530,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>4.3</v>
+        <v>-2.06</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-6.36</v>
+        <v>-2.05</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1547,13 +1547,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>6.02</v>
+        <v>2.6</v>
       </c>
       <c r="D11" s="6">
-        <v>2.6</v>
+        <v>-0.8</v>
       </c>
       <c r="E11" s="7">
-        <v>-3.42</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1564,13 +1564,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="D12" s="6">
-        <v>1.01</v>
+        <v>-0.99</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.04</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1581,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.66</v>
+        <v>-2.46</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.46</v>
+        <v>-3.63</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.8</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1598,13 +1598,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-13.53</v>
+        <v>-14.17</v>
       </c>
       <c r="D14" s="6">
-        <v>-14.17</v>
+        <v>-18.04</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.64</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1615,13 +1615,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-25.4</v>
+        <v>-27.14</v>
       </c>
       <c r="D15" s="6">
-        <v>-27.14</v>
+        <v>-27.73</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.74</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1632,13 +1632,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>-25.93</v>
+        <v>-26.64</v>
       </c>
       <c r="D16" s="6">
-        <v>-26.64</v>
+        <v>-29.1</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.71</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1649,13 +1649,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.529999999999999</v>
+        <v>-11.18</v>
       </c>
       <c r="D17" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.65</v>
+        <v>-10.45</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1666,13 +1666,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-11.07</v>
+        <v>-8.44</v>
       </c>
       <c r="D18" s="6">
-        <v>-8.44</v>
+        <v>-7.16</v>
       </c>
       <c r="E18" s="8">
-        <v>2.63</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1683,13 +1683,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.89</v>
+        <v>-3.39</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.39</v>
+        <v>-3.81</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.5</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1700,13 +1700,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-15.53</v>
+        <v>-17.27</v>
       </c>
       <c r="D20" s="6">
-        <v>-17.27</v>
+        <v>-18.6</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.74</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1717,13 +1717,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-27.8</v>
+        <v>-29.47</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.47</v>
+        <v>-29.97</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.67</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1734,13 +1734,13 @@
         <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>-29.78</v>
+        <v>-30.73</v>
       </c>
       <c r="D22" s="6">
-        <v>-30.73</v>
+        <v>-31.48</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.95</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1751,13 +1751,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>2398.6</v>
+        <v>2349.2</v>
       </c>
       <c r="D23" s="6">
-        <v>2349.2</v>
+        <v>2311.4</v>
       </c>
       <c r="E23" s="7">
-        <v>-49.4</v>
+        <v>-37.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1768,13 +1768,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>728.85</v>
+        <v>712</v>
       </c>
       <c r="D24" s="6">
-        <v>712</v>
+        <v>706.95</v>
       </c>
       <c r="E24" s="7">
-        <v>-16.85</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1785,132 +1785,115 @@
         <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>553</v>
+        <v>545.5</v>
       </c>
       <c r="D25" s="6">
-        <v>545.5</v>
+        <v>539.65</v>
       </c>
       <c r="E25" s="7">
-        <v>-7.5</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>34</v>
+        <v>47.88</v>
       </c>
       <c r="D26" s="6">
-        <v>33</v>
+        <v>44.61</v>
       </c>
       <c r="E26" s="7">
-        <v>-1</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>52.57</v>
+        <v>47.93</v>
       </c>
       <c r="D27" s="6">
-        <v>47.88</v>
+        <v>45.95</v>
       </c>
       <c r="E27" s="7">
-        <v>-4.69</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>55.27</v>
+        <v>50.57</v>
       </c>
       <c r="D28" s="6">
-        <v>47.93</v>
+        <v>47.61</v>
       </c>
       <c r="E28" s="7">
-        <v>-7.34</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>54.62</v>
+        <v>-40.5</v>
       </c>
       <c r="D29" s="6">
-        <v>50.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.05</v>
+        <v>-34.8</v>
+      </c>
+      <c r="E29" s="8">
+        <v>5.7</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>63.94</v>
+        <v>10.08</v>
       </c>
       <c r="D30" s="6">
-        <v>-40.5</v>
+        <v>-14.36</v>
       </c>
       <c r="E30" s="7">
-        <v>-104.44</v>
+        <v>-24.44</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="6">
-        <v>-4.79</v>
+        <v>-66.34</v>
       </c>
       <c r="D31" s="6">
-        <v>10.08</v>
-      </c>
-      <c r="E31" s="8">
-        <v>14.87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>19.14</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-66.34</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-85.48</v>
+        <v>-67.12</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -1975,16 +1958,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>48.8</v>
+        <v>46.1</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.3</v>
+        <v>-3.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.7</v>
+        <v>-7.1</v>
       </c>
       <c r="H2" s="11">
         <v>66</v>
@@ -2103,13 +2086,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1242</v>
+        <v>0.1255</v>
       </c>
       <c r="B2" s="14">
         <v>-0.0238</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0471</v>
+        <v>-0.0469</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,40 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.6 → 47.6</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>47.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -392,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -915,37 +881,37 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2311.4</v>
+        <v>2273.2</v>
       </c>
       <c r="D2">
-        <v>-1.61</v>
+        <v>-1.65</v>
       </c>
       <c r="E2">
-        <v>2839.64</v>
+        <v>2802.31</v>
       </c>
       <c r="F2">
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-18.6</v>
+        <v>-18.88</v>
       </c>
       <c r="H2">
-        <v>6.57</v>
+        <v>4.81</v>
       </c>
       <c r="I2">
-        <v>-0.8</v>
+        <v>-1.03</v>
       </c>
       <c r="J2">
-        <v>-4.68</v>
+        <v>-6.84</v>
       </c>
       <c r="K2">
-        <v>-10.45</v>
+        <v>-10.71</v>
       </c>
       <c r="L2">
-        <v>-18.04</v>
+        <v>-19.95</v>
       </c>
       <c r="M2">
-        <v>12.55</v>
+        <v>12.66</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -954,19 +920,19 @@
         <v>44</v>
       </c>
       <c r="P2">
-        <v>2354.22</v>
+        <v>2349.48</v>
       </c>
       <c r="Q2">
-        <v>2333.12</v>
+        <v>2325.28</v>
       </c>
       <c r="R2">
-        <v>2440.54</v>
+        <v>2434.81</v>
       </c>
       <c r="S2">
-        <v>2543.1</v>
+        <v>2541.51</v>
       </c>
       <c r="T2">
-        <v>-9.109999999999999</v>
+        <v>-10.56</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -981,34 +947,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>44.61</v>
+        <v>41.52</v>
       </c>
       <c r="Z2">
-        <v>-26.93</v>
+        <v>-30.05</v>
       </c>
       <c r="AA2">
-        <v>-39.08</v>
+        <v>-37.27</v>
       </c>
       <c r="AB2">
-        <v>12.15</v>
+        <v>7.22</v>
       </c>
       <c r="AC2">
-        <v>74.78</v>
+        <v>55.34</v>
       </c>
       <c r="AD2">
-        <v>86.12</v>
+        <v>73.62</v>
       </c>
       <c r="AE2">
-        <v>67.29000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AF2">
-        <v>-34.8</v>
+        <v>38.46</v>
       </c>
       <c r="AG2">
-        <v>2456.1</v>
+        <v>2442.09</v>
       </c>
       <c r="AH2">
-        <v>2210.15</v>
+        <v>2208.48</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1017,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.12</v>
+        <v>29.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1028,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>706.95</v>
+        <v>694.05</v>
       </c>
       <c r="D3">
-        <v>-0.71</v>
+        <v>-1.82</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1040,46 +1006,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-29.97</v>
+        <v>-31.25</v>
       </c>
       <c r="H3">
-        <v>2.89</v>
+        <v>1.01</v>
       </c>
       <c r="I3">
-        <v>-0.99</v>
+        <v>-2.34</v>
       </c>
       <c r="J3">
-        <v>-3.29</v>
+        <v>-6.15</v>
       </c>
       <c r="K3">
-        <v>-7.16</v>
+        <v>-7.85</v>
       </c>
       <c r="L3">
-        <v>-27.73</v>
+        <v>-30.2</v>
       </c>
       <c r="M3">
-        <v>-2.38</v>
+        <v>-2.79</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>717.0700000000001</v>
+        <v>713.74</v>
       </c>
       <c r="Q3">
-        <v>716.74</v>
+        <v>714.51</v>
       </c>
       <c r="R3">
-        <v>717.59</v>
+        <v>716.85</v>
       </c>
       <c r="S3">
-        <v>797.5</v>
+        <v>796.02</v>
       </c>
       <c r="T3">
-        <v>-11.35</v>
+        <v>-12.81</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1094,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.95</v>
+        <v>41.28</v>
       </c>
       <c r="Z3">
-        <v>-2.04</v>
+        <v>-3.47</v>
       </c>
       <c r="AA3">
-        <v>-2.69</v>
+        <v>-2.84</v>
       </c>
       <c r="AB3">
-        <v>0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="AC3">
-        <v>66.06</v>
+        <v>37.56</v>
       </c>
       <c r="AD3">
-        <v>76.59</v>
+        <v>61.99</v>
       </c>
       <c r="AE3">
-        <v>15.24</v>
+        <v>15.43</v>
       </c>
       <c r="AF3">
-        <v>-14.36</v>
+        <v>98.12</v>
       </c>
       <c r="AG3">
-        <v>742.4299999999999</v>
+        <v>739.9400000000001</v>
       </c>
       <c r="AH3">
-        <v>691.05</v>
+        <v>689.08</v>
       </c>
       <c r="AI3">
-        <v>742.71</v>
+        <v>742.51</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>18.78</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1141,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>539.65</v>
+        <v>528.35</v>
       </c>
       <c r="D4">
-        <v>-1.07</v>
+        <v>-2.09</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1153,46 +1119,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-31.48</v>
+        <v>-32.91</v>
       </c>
       <c r="H4">
-        <v>4.99</v>
+        <v>2.79</v>
       </c>
       <c r="I4">
-        <v>-3.63</v>
+        <v>-2.89</v>
       </c>
       <c r="J4">
-        <v>-2.05</v>
+        <v>-5.55</v>
       </c>
       <c r="K4">
-        <v>-3.81</v>
+        <v>-4.47</v>
       </c>
       <c r="L4">
-        <v>-29.1</v>
+        <v>-28.88</v>
       </c>
       <c r="M4">
-        <v>-4.69</v>
+        <v>-4.99</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>546.55</v>
+        <v>543.41</v>
       </c>
       <c r="Q4">
-        <v>543.17</v>
+        <v>541.62</v>
       </c>
       <c r="R4">
-        <v>541.21</v>
+        <v>540.98</v>
       </c>
       <c r="S4">
-        <v>608.22</v>
+        <v>607.11</v>
       </c>
       <c r="T4">
-        <v>-11.27</v>
+        <v>-12.97</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1207,34 +1173,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.61</v>
+        <v>42.44</v>
       </c>
       <c r="Z4">
-        <v>2.06</v>
+        <v>0.49</v>
       </c>
       <c r="AA4">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AB4">
-        <v>0.14</v>
+        <v>-1.15</v>
       </c>
       <c r="AC4">
-        <v>52.31</v>
+        <v>27.85</v>
       </c>
       <c r="AD4">
-        <v>59.71</v>
+        <v>47.89</v>
       </c>
       <c r="AE4">
-        <v>15.24</v>
+        <v>15.41</v>
       </c>
       <c r="AF4">
-        <v>-67.12</v>
+        <v>-75.77</v>
       </c>
       <c r="AG4">
-        <v>568.87</v>
+        <v>566.98</v>
       </c>
       <c r="AH4">
-        <v>517.46</v>
+        <v>516.26</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1243,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.17</v>
+        <v>25.28</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1404,502 +1370,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-6.84</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-3.29</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-6.15</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-2.05</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.55</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.68</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-3.29</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.99</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.34</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.63</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-18.04</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-19.95</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.01</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.99</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-27.73</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-30.2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.63</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-29.1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-28.88</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-14.17</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-18.04</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-10.45</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-10.71</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-27.14</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-27.73</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.16</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.85</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-26.64</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-29.1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.81</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.47</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-10.45</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-18.6</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-18.88</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.16</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-29.97</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-31.25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.81</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-31.48</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-32.91</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-17.27</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-18.6</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2311.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2273.2</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-38.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.47</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-29.97</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>706.95</v>
+      </c>
+      <c r="D23" s="5">
+        <v>694.05</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-30.73</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-31.48</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>539.65</v>
+      </c>
+      <c r="D24" s="5">
+        <v>528.35</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-11.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2349.2</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2311.4</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-37.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>44.61</v>
+      </c>
+      <c r="D25" s="5">
+        <v>41.52</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>712</v>
-      </c>
-      <c r="D24" s="6">
-        <v>706.95</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>45.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>41.28</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-4.67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>545.5</v>
-      </c>
-      <c r="D25" s="6">
-        <v>539.65</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>47.61</v>
+      </c>
+      <c r="D27" s="5">
+        <v>42.44</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-5.17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>47.88</v>
-      </c>
-      <c r="D26" s="6">
-        <v>44.61</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-34.8</v>
+      </c>
+      <c r="D28" s="5">
+        <v>38.46</v>
+      </c>
+      <c r="E28" s="7">
+        <v>73.26000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>47.93</v>
-      </c>
-      <c r="D27" s="6">
-        <v>45.95</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-14.36</v>
+      </c>
+      <c r="D29" s="5">
+        <v>98.12</v>
+      </c>
+      <c r="E29" s="7">
+        <v>112.48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>50.57</v>
-      </c>
-      <c r="D28" s="6">
-        <v>47.61</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-40.5</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-34.8</v>
-      </c>
-      <c r="E29" s="8">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>10.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-14.36</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-24.44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-66.34</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>-67.12</v>
       </c>
-      <c r="E31" s="7">
-        <v>-0.78</v>
+      <c r="D30" s="5">
+        <v>-75.77</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-8.65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1919,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>41.7</v>
+      </c>
+      <c r="E2" s="10">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="11">
-        <v>36.40000000000001</v>
-      </c>
-      <c r="C2" s="12">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11">
-        <v>46.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>0</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-3.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.1</v>
-      </c>
-      <c r="H2" s="11">
-        <v>66</v>
-      </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2074,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1255</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0238</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0469</v>
+      <c r="A2" s="13">
+        <v>0.1266</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0279</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0499</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,16 +148,37 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>DOWN</t>
-  </si>
-  <si>
-    <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
-  </si>
-  <si>
-    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +380,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -747,8 +769,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -881,10 +902,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2273.2</v>
+        <v>2250</v>
       </c>
       <c r="D2">
-        <v>-1.65</v>
+        <v>-1.02</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -893,46 +914,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-18.88</v>
+        <v>-19.71</v>
       </c>
       <c r="H2">
-        <v>4.81</v>
+        <v>3.74</v>
       </c>
       <c r="I2">
-        <v>-1.03</v>
+        <v>-6.83</v>
       </c>
       <c r="J2">
-        <v>-6.84</v>
+        <v>-7.41</v>
       </c>
       <c r="K2">
-        <v>-10.71</v>
+        <v>-10.31</v>
       </c>
       <c r="L2">
-        <v>-19.95</v>
+        <v>-19.54</v>
       </c>
       <c r="M2">
-        <v>12.66</v>
+        <v>12.55</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P2">
-        <v>2349.48</v>
+        <v>2316.48</v>
       </c>
       <c r="Q2">
-        <v>2325.28</v>
+        <v>2315.37</v>
       </c>
       <c r="R2">
-        <v>2434.81</v>
+        <v>2429.51</v>
       </c>
       <c r="S2">
-        <v>2541.51</v>
+        <v>2539.75</v>
       </c>
       <c r="T2">
-        <v>-10.56</v>
+        <v>-11.41</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +968,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.52</v>
+        <v>39.72</v>
       </c>
       <c r="Z2">
-        <v>-30.05</v>
+        <v>-34</v>
       </c>
       <c r="AA2">
-        <v>-37.27</v>
+        <v>-36.62</v>
       </c>
       <c r="AB2">
-        <v>7.22</v>
+        <v>2.62</v>
       </c>
       <c r="AC2">
-        <v>55.34</v>
+        <v>38.33</v>
       </c>
       <c r="AD2">
-        <v>73.62</v>
+        <v>56.15</v>
       </c>
       <c r="AE2">
-        <v>66.3</v>
+        <v>67.59</v>
       </c>
       <c r="AF2">
-        <v>38.46</v>
+        <v>29.01</v>
       </c>
       <c r="AG2">
-        <v>2442.09</v>
+        <v>2421.38</v>
       </c>
       <c r="AH2">
-        <v>2208.48</v>
+        <v>2209.36</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
       </c>
       <c r="AJ2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK2">
-        <v>29.57</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1015,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>694.05</v>
+        <v>692.8</v>
       </c>
       <c r="D3">
-        <v>-1.82</v>
+        <v>-0.18</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1027,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-31.25</v>
+        <v>-31.37</v>
       </c>
       <c r="H3">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="I3">
-        <v>-2.34</v>
+        <v>-4.68</v>
       </c>
       <c r="J3">
-        <v>-6.15</v>
+        <v>-6.2</v>
       </c>
       <c r="K3">
-        <v>-7.85</v>
+        <v>-7.29</v>
       </c>
       <c r="L3">
-        <v>-30.2</v>
+        <v>-30.9</v>
       </c>
       <c r="M3">
-        <v>-2.79</v>
+        <v>-2.55</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P3">
-        <v>713.74</v>
+        <v>706.9299999999999</v>
       </c>
       <c r="Q3">
-        <v>714.51</v>
+        <v>712.29</v>
       </c>
       <c r="R3">
-        <v>716.85</v>
+        <v>716.12</v>
       </c>
       <c r="S3">
-        <v>796.02</v>
+        <v>794.47</v>
       </c>
       <c r="T3">
-        <v>-12.81</v>
+        <v>-12.8</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1081,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.28</v>
+        <v>40.85</v>
       </c>
       <c r="Z3">
-        <v>-3.47</v>
+        <v>-4.65</v>
       </c>
       <c r="AA3">
-        <v>-2.84</v>
+        <v>-3.2</v>
       </c>
       <c r="AB3">
-        <v>-0.63</v>
+        <v>-1.45</v>
       </c>
       <c r="AC3">
-        <v>37.56</v>
+        <v>23.15</v>
       </c>
       <c r="AD3">
-        <v>61.99</v>
+        <v>42.26</v>
       </c>
       <c r="AE3">
-        <v>15.43</v>
+        <v>15.04</v>
       </c>
       <c r="AF3">
-        <v>98.12</v>
+        <v>-39.91</v>
       </c>
       <c r="AG3">
-        <v>739.9400000000001</v>
+        <v>737.11</v>
       </c>
       <c r="AH3">
-        <v>689.08</v>
+        <v>687.46</v>
       </c>
       <c r="AI3">
-        <v>742.51</v>
+        <v>736.9299999999999</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>20.17</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1128,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>528.35</v>
+        <v>523.75</v>
       </c>
       <c r="D4">
-        <v>-2.09</v>
+        <v>-0.87</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1119,49 +1140,49 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.91</v>
+        <v>-33.5</v>
       </c>
       <c r="H4">
-        <v>2.79</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>-2.89</v>
+        <v>-4.87</v>
       </c>
       <c r="J4">
-        <v>-5.55</v>
+        <v>-6.34</v>
       </c>
       <c r="K4">
-        <v>-4.47</v>
+        <v>-4.94</v>
       </c>
       <c r="L4">
-        <v>-28.88</v>
+        <v>-29.79</v>
       </c>
       <c r="M4">
-        <v>-4.99</v>
+        <v>-4.95</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>543.41</v>
+        <v>538.05</v>
       </c>
       <c r="Q4">
-        <v>541.62</v>
+        <v>539.74</v>
       </c>
       <c r="R4">
-        <v>540.98</v>
+        <v>540.73</v>
       </c>
       <c r="S4">
-        <v>607.11</v>
+        <v>605.96</v>
       </c>
       <c r="T4">
-        <v>-12.97</v>
+        <v>-13.57</v>
       </c>
       <c r="U4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V4" t="s">
         <v>41</v>
@@ -1170,46 +1191,46 @@
         <v>41</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.44</v>
+        <v>40.51</v>
       </c>
       <c r="Z4">
-        <v>0.49</v>
+        <v>-1.12</v>
       </c>
       <c r="AA4">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="AB4">
-        <v>-1.15</v>
+        <v>-2.2</v>
       </c>
       <c r="AC4">
-        <v>27.85</v>
+        <v>11.1</v>
       </c>
       <c r="AD4">
-        <v>47.89</v>
+        <v>30.42</v>
       </c>
       <c r="AE4">
-        <v>15.41</v>
+        <v>15.51</v>
       </c>
       <c r="AF4">
-        <v>-75.77</v>
+        <v>-62.76</v>
       </c>
       <c r="AG4">
-        <v>566.98</v>
+        <v>564.48</v>
       </c>
       <c r="AH4">
-        <v>516.26</v>
+        <v>514.99</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AK4">
-        <v>25.28</v>
+        <v>29.39</v>
       </c>
     </row>
   </sheetData>
@@ -1360,7 +1381,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1370,12 +1391,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,428 +1439,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.41</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-6.2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.55</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.03</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.83</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.34</v>
+      </c>
+      <c r="D11" s="6">
         <v>-4.68</v>
       </c>
-      <c r="D7" s="5">
-        <v>-6.84</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="E11" s="7">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.89</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-19.95</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-19.54</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-3.29</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-6.15</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-30.2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-30.9</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-2.05</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-5.55</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-28.88</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-29.79</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-1.03</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-10.71</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-10.31</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.34</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-7.85</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-7.29</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.63</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-2.89</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.47</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-18.04</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-19.71</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-27.73</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-30.2</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-31.25</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-31.37</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-29.1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-28.88</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-32.91</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-33.5</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-10.45</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-10.71</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2273.2</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2250</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-23.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-7.16</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-7.85</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>694.05</v>
+      </c>
+      <c r="D23" s="6">
+        <v>692.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-3.81</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-4.47</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>528.35</v>
+      </c>
+      <c r="D24" s="6">
+        <v>523.75</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-18.6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-18.88</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>41.52</v>
+      </c>
+      <c r="D25" s="6">
+        <v>39.72</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-29.97</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-31.25</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>41.28</v>
+      </c>
+      <c r="D26" s="6">
+        <v>40.85</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-31.48</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-32.91</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>42.44</v>
+      </c>
+      <c r="D27" s="6">
+        <v>40.51</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2311.4</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2273.2</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-38.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>38.46</v>
+      </c>
+      <c r="D28" s="6">
+        <v>29.01</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-9.449999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>706.95</v>
-      </c>
-      <c r="D23" s="5">
-        <v>694.05</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-12.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>98.12</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-39.91</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-138.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>539.65</v>
-      </c>
-      <c r="D24" s="5">
-        <v>528.35</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-11.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>44.61</v>
-      </c>
-      <c r="D25" s="5">
-        <v>41.52</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>45.95</v>
-      </c>
-      <c r="D26" s="5">
-        <v>41.28</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>47.61</v>
-      </c>
-      <c r="D27" s="5">
-        <v>42.44</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-5.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-34.8</v>
-      </c>
-      <c r="D28" s="5">
-        <v>38.46</v>
-      </c>
-      <c r="E28" s="7">
-        <v>73.26000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-14.36</v>
-      </c>
-      <c r="D29" s="5">
-        <v>98.12</v>
-      </c>
-      <c r="E29" s="7">
-        <v>112.48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-67.12</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-75.77</v>
       </c>
-      <c r="E30" s="6">
-        <v>-8.65</v>
+      <c r="D30" s="6">
+        <v>-62.76</v>
+      </c>
+      <c r="E30" s="8">
+        <v>13.01</v>
       </c>
     </row>
   </sheetData>
@@ -1830,60 +1886,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.40000000000001</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>41.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>40.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>66</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2041,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1266</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0279</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0499</v>
+      <c r="A2" s="14">
+        <v>0.1255</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0255</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0495</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
   <si>
     <t>Symbol</t>
   </si>
@@ -154,31 +154,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,15 +356,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,7 +744,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -902,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2250</v>
+        <v>2258.4</v>
       </c>
       <c r="D2">
-        <v>-1.02</v>
+        <v>0.37</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -914,46 +890,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.71</v>
+        <v>-19.41</v>
       </c>
       <c r="H2">
-        <v>3.74</v>
+        <v>4.12</v>
       </c>
       <c r="I2">
-        <v>-6.83</v>
+        <v>-5.85</v>
       </c>
       <c r="J2">
-        <v>-7.41</v>
+        <v>-7.76</v>
       </c>
       <c r="K2">
-        <v>-10.31</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L2">
-        <v>-19.54</v>
+        <v>-19.25</v>
       </c>
       <c r="M2">
-        <v>12.55</v>
+        <v>12.88</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P2">
-        <v>2316.48</v>
+        <v>2288.44</v>
       </c>
       <c r="Q2">
-        <v>2315.37</v>
+        <v>2309.27</v>
       </c>
       <c r="R2">
-        <v>2429.51</v>
+        <v>2424.88</v>
       </c>
       <c r="S2">
-        <v>2539.75</v>
+        <v>2538.03</v>
       </c>
       <c r="T2">
-        <v>-11.41</v>
+        <v>-11.02</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -968,34 +944,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.72</v>
+        <v>40.72</v>
       </c>
       <c r="Z2">
-        <v>-34</v>
+        <v>-36.04</v>
       </c>
       <c r="AA2">
-        <v>-36.62</v>
+        <v>-36.5</v>
       </c>
       <c r="AB2">
-        <v>2.62</v>
+        <v>0.46</v>
       </c>
       <c r="AC2">
-        <v>38.33</v>
+        <v>31.59</v>
       </c>
       <c r="AD2">
-        <v>56.15</v>
+        <v>41.75</v>
       </c>
       <c r="AE2">
-        <v>67.59</v>
+        <v>66.86</v>
       </c>
       <c r="AF2">
-        <v>29.01</v>
+        <v>-35.77</v>
       </c>
       <c r="AG2">
-        <v>2421.38</v>
+        <v>2413.57</v>
       </c>
       <c r="AH2">
-        <v>2209.36</v>
+        <v>2204.98</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -1004,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>29.94</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +991,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>692.8</v>
+        <v>688.05</v>
       </c>
       <c r="D3">
-        <v>-0.18</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1027,46 +1003,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-31.37</v>
+        <v>-31.84</v>
       </c>
       <c r="H3">
-        <v>0.83</v>
+        <v>0.14</v>
       </c>
       <c r="I3">
-        <v>-4.68</v>
+        <v>-5.6</v>
       </c>
       <c r="J3">
-        <v>-6.2</v>
+        <v>-6.67</v>
       </c>
       <c r="K3">
-        <v>-7.29</v>
+        <v>-7.37</v>
       </c>
       <c r="L3">
-        <v>-30.9</v>
+        <v>-31.4</v>
       </c>
       <c r="M3">
-        <v>-2.55</v>
+        <v>-2.63</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3">
-        <v>706.9299999999999</v>
+        <v>698.77</v>
       </c>
       <c r="Q3">
-        <v>712.29</v>
+        <v>710.24</v>
       </c>
       <c r="R3">
-        <v>716.12</v>
+        <v>715.3099999999999</v>
       </c>
       <c r="S3">
-        <v>794.47</v>
+        <v>793.02</v>
       </c>
       <c r="T3">
-        <v>-12.8</v>
+        <v>-13.24</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1081,43 +1057,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.85</v>
+        <v>39.17</v>
       </c>
       <c r="Z3">
-        <v>-4.65</v>
+        <v>-5.91</v>
       </c>
       <c r="AA3">
-        <v>-3.2</v>
+        <v>-3.75</v>
       </c>
       <c r="AB3">
-        <v>-1.45</v>
+        <v>-2.16</v>
       </c>
       <c r="AC3">
-        <v>23.15</v>
+        <v>9.32</v>
       </c>
       <c r="AD3">
-        <v>42.26</v>
+        <v>23.34</v>
       </c>
       <c r="AE3">
-        <v>15.04</v>
+        <v>14.66</v>
       </c>
       <c r="AF3">
-        <v>-39.91</v>
+        <v>-23.77</v>
       </c>
       <c r="AG3">
-        <v>737.11</v>
+        <v>736.02</v>
       </c>
       <c r="AH3">
-        <v>687.46</v>
+        <v>684.47</v>
       </c>
       <c r="AI3">
-        <v>736.9299999999999</v>
+        <v>732.89</v>
       </c>
       <c r="AJ3" t="s">
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>21.78</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1104,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>523.75</v>
+        <v>519</v>
       </c>
       <c r="D4">
-        <v>-0.87</v>
+        <v>-0.91</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1140,46 +1116,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-33.5</v>
+        <v>-34.1</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>0.97</v>
       </c>
       <c r="I4">
-        <v>-4.87</v>
+        <v>-6.15</v>
       </c>
       <c r="J4">
-        <v>-6.34</v>
+        <v>-7.57</v>
       </c>
       <c r="K4">
-        <v>-4.94</v>
+        <v>-6.49</v>
       </c>
       <c r="L4">
-        <v>-29.79</v>
+        <v>-30.08</v>
       </c>
       <c r="M4">
-        <v>-4.95</v>
+        <v>-5.31</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>538.05</v>
+        <v>531.25</v>
       </c>
       <c r="Q4">
-        <v>539.74</v>
+        <v>539.34</v>
       </c>
       <c r="R4">
-        <v>540.73</v>
+        <v>540.37</v>
       </c>
       <c r="S4">
-        <v>605.96</v>
+        <v>604.76</v>
       </c>
       <c r="T4">
-        <v>-13.57</v>
+        <v>-14.18</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1194,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.51</v>
+        <v>38.56</v>
       </c>
       <c r="Z4">
-        <v>-1.12</v>
+        <v>-2.75</v>
       </c>
       <c r="AA4">
-        <v>1.08</v>
+        <v>0.32</v>
       </c>
       <c r="AB4">
-        <v>-2.2</v>
+        <v>-3.06</v>
       </c>
       <c r="AC4">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>30.42</v>
+        <v>12.98</v>
       </c>
       <c r="AE4">
-        <v>15.51</v>
+        <v>15.21</v>
       </c>
       <c r="AF4">
-        <v>-62.76</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="AG4">
-        <v>564.48</v>
+        <v>565.17</v>
       </c>
       <c r="AH4">
-        <v>514.99</v>
+        <v>513.51</v>
       </c>
       <c r="AI4">
         <v>561.9299999999999</v>
@@ -1230,7 +1206,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>29.39</v>
+        <v>32.96</v>
       </c>
     </row>
   </sheetData>
@@ -1391,47 +1367,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1439,428 +1380,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>57</v>
+      <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-6.84</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-7.41</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.57</v>
+      <c r="D7" s="5">
+        <v>-7.76</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
+        <v>-6.2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-6.67</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.34</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.57</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-6.83</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.85</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-5.6</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.87</v>
+      </c>
+      <c r="D12" s="5">
         <v>-6.15</v>
       </c>
-      <c r="D8" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="E12" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-19.54</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-19.25</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-30.9</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-31.4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-5.55</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-29.79</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-30.08</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.83</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-10.31</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-4.68</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.29</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.94</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.49</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-19.95</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-19.54</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-19.71</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-19.41</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-30.2</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-30.9</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-31.37</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-31.84</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-28.88</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-29.79</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-33.5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-34.1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-10.71</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-10.31</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2250</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2258.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-7.85</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-7.29</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>692.8</v>
+      </c>
+      <c r="D23" s="5">
+        <v>688.05</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.47</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>523.75</v>
+      </c>
+      <c r="D24" s="5">
+        <v>519</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-19.71</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>39.72</v>
+      </c>
+      <c r="D25" s="5">
+        <v>40.72</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-31.25</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-31.37</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>40.85</v>
+      </c>
+      <c r="D26" s="5">
+        <v>39.17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-32.91</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-33.5</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>40.51</v>
+      </c>
+      <c r="D27" s="5">
+        <v>38.56</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2273.2</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2250</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-23.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>29.01</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-35.77</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-64.78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>694.05</v>
-      </c>
-      <c r="D23" s="6">
-        <v>692.8</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-39.91</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-23.77</v>
+      </c>
+      <c r="E29" s="7">
+        <v>16.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>528.35</v>
-      </c>
-      <c r="D24" s="6">
-        <v>523.75</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>41.52</v>
-      </c>
-      <c r="D25" s="6">
-        <v>39.72</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>41.28</v>
-      </c>
-      <c r="D26" s="6">
-        <v>40.85</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>42.44</v>
-      </c>
-      <c r="D27" s="6">
-        <v>40.51</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>38.46</v>
-      </c>
-      <c r="D28" s="6">
-        <v>29.01</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-9.449999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>98.12</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-39.91</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-138.03</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-75.77</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-62.76</v>
       </c>
-      <c r="E30" s="8">
-        <v>13.01</v>
+      <c r="D30" s="5">
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-7.56</v>
       </c>
     </row>
   </sheetData>
@@ -1886,60 +1827,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>65</v>
+      <c r="B1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.40000000000001</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-7.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2041,25 +1982,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1255</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0255</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0495</v>
+      <c r="A2" s="13">
+        <v>0.1288</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0263</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.05309999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -240,14 +240,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -280,13 +280,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -878,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2258.4</v>
+        <v>2267.7</v>
       </c>
       <c r="D2">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -890,25 +890,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.41</v>
+        <v>-19.08</v>
       </c>
       <c r="H2">
-        <v>4.12</v>
+        <v>4.55</v>
       </c>
       <c r="I2">
-        <v>-5.85</v>
+        <v>-3.47</v>
       </c>
       <c r="J2">
-        <v>-7.76</v>
+        <v>-4.73</v>
       </c>
       <c r="K2">
-        <v>-9.869999999999999</v>
+        <v>-11.15</v>
       </c>
       <c r="L2">
-        <v>-19.25</v>
+        <v>-18.8</v>
       </c>
       <c r="M2">
-        <v>12.88</v>
+        <v>13.27</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -917,19 +917,19 @@
         <v>49</v>
       </c>
       <c r="P2">
-        <v>2288.44</v>
+        <v>2272.14</v>
       </c>
       <c r="Q2">
-        <v>2309.27</v>
+        <v>2303.76</v>
       </c>
       <c r="R2">
-        <v>2424.88</v>
+        <v>2420.24</v>
       </c>
       <c r="S2">
-        <v>2538.03</v>
+        <v>2536.54</v>
       </c>
       <c r="T2">
-        <v>-11.02</v>
+        <v>-10.6</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,34 +944,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.72</v>
+        <v>41.87</v>
       </c>
       <c r="Z2">
-        <v>-36.04</v>
+        <v>-36.48</v>
       </c>
       <c r="AA2">
         <v>-36.5</v>
       </c>
       <c r="AB2">
-        <v>0.46</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>31.59</v>
+        <v>32.18</v>
       </c>
       <c r="AD2">
-        <v>41.75</v>
+        <v>34.03</v>
       </c>
       <c r="AE2">
-        <v>66.86</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AF2">
-        <v>-35.77</v>
+        <v>-12.54</v>
       </c>
       <c r="AG2">
-        <v>2413.57</v>
+        <v>2404.35</v>
       </c>
       <c r="AH2">
-        <v>2204.98</v>
+        <v>2203.17</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>30.25</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -991,58 +991,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>688.05</v>
+        <v>680.2</v>
       </c>
       <c r="D3">
-        <v>-0.6899999999999999</v>
+        <v>-1.14</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>687.1</v>
+        <v>680.2</v>
       </c>
       <c r="G3">
-        <v>-31.84</v>
+        <v>-32.62</v>
       </c>
       <c r="H3">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.6</v>
+        <v>-4.47</v>
       </c>
       <c r="J3">
-        <v>-6.67</v>
+        <v>-6.68</v>
       </c>
       <c r="K3">
-        <v>-7.37</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L3">
-        <v>-31.4</v>
+        <v>-32.5</v>
       </c>
       <c r="M3">
-        <v>-2.63</v>
+        <v>-2.74</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>698.77</v>
+        <v>692.41</v>
       </c>
       <c r="Q3">
-        <v>710.24</v>
+        <v>707.48</v>
       </c>
       <c r="R3">
-        <v>715.3099999999999</v>
+        <v>714.41</v>
       </c>
       <c r="S3">
-        <v>793.02</v>
+        <v>791.61</v>
       </c>
       <c r="T3">
-        <v>-13.24</v>
+        <v>-14.07</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1057,43 +1057,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.17</v>
+        <v>36.5</v>
       </c>
       <c r="Z3">
-        <v>-5.91</v>
+        <v>-7.45</v>
       </c>
       <c r="AA3">
-        <v>-3.75</v>
+        <v>-4.49</v>
       </c>
       <c r="AB3">
-        <v>-2.16</v>
+        <v>-2.96</v>
       </c>
       <c r="AC3">
-        <v>9.32</v>
+        <v>4.48</v>
       </c>
       <c r="AD3">
-        <v>23.34</v>
+        <v>12.32</v>
       </c>
       <c r="AE3">
-        <v>14.66</v>
+        <v>14.44</v>
       </c>
       <c r="AF3">
-        <v>-23.77</v>
+        <v>30.71</v>
       </c>
       <c r="AG3">
-        <v>736.02</v>
+        <v>733.6799999999999</v>
       </c>
       <c r="AH3">
-        <v>684.47</v>
+        <v>681.27</v>
       </c>
       <c r="AI3">
-        <v>732.89</v>
+        <v>727.78</v>
       </c>
       <c r="AJ3" t="s">
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>23.72</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1104,58 +1104,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>519</v>
+        <v>513.6</v>
       </c>
       <c r="D4">
-        <v>-0.91</v>
+        <v>-1.04</v>
       </c>
       <c r="E4">
         <v>787.55</v>
       </c>
       <c r="F4">
-        <v>514</v>
+        <v>513.6</v>
       </c>
       <c r="G4">
-        <v>-34.1</v>
+        <v>-34.79</v>
       </c>
       <c r="H4">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-6.15</v>
+        <v>-5.85</v>
       </c>
       <c r="J4">
-        <v>-7.57</v>
+        <v>-2.52</v>
       </c>
       <c r="K4">
-        <v>-6.49</v>
+        <v>-7.1</v>
       </c>
       <c r="L4">
-        <v>-30.08</v>
+        <v>-30.94</v>
       </c>
       <c r="M4">
-        <v>-5.31</v>
+        <v>-5.61</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>531.25</v>
+        <v>524.87</v>
       </c>
       <c r="Q4">
-        <v>539.34</v>
+        <v>538.47</v>
       </c>
       <c r="R4">
-        <v>540.37</v>
+        <v>539.88</v>
       </c>
       <c r="S4">
-        <v>604.76</v>
+        <v>603.4400000000001</v>
       </c>
       <c r="T4">
-        <v>-14.18</v>
+        <v>-14.89</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1170,43 +1170,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.56</v>
+        <v>36.41</v>
       </c>
       <c r="Z4">
-        <v>-2.75</v>
+        <v>-4.42</v>
       </c>
       <c r="AA4">
-        <v>0.32</v>
+        <v>-0.63</v>
       </c>
       <c r="AB4">
-        <v>-3.06</v>
+        <v>-3.79</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>12.98</v>
+        <v>3.7</v>
       </c>
       <c r="AE4">
-        <v>15.21</v>
+        <v>14.81</v>
       </c>
       <c r="AF4">
-        <v>-70.31999999999999</v>
+        <v>-22.37</v>
       </c>
       <c r="AG4">
-        <v>565.17</v>
+        <v>566.5599999999999</v>
       </c>
       <c r="AH4">
-        <v>513.51</v>
+        <v>510.38</v>
       </c>
       <c r="AI4">
-        <v>561.9299999999999</v>
+        <v>561.29</v>
       </c>
       <c r="AJ4" t="s">
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>32.96</v>
+        <v>36.12</v>
       </c>
     </row>
   </sheetData>
@@ -1404,13 +1404,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.41</v>
+        <v>-7.76</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.76</v>
+        <v>-4.73</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.35</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1421,13 +1421,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.2</v>
+        <v>-6.67</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.67</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.47</v>
+        <v>-6.68</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1438,13 +1438,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.34</v>
+        <v>-7.57</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.57</v>
+        <v>-2.52</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.23</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1455,13 +1455,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.83</v>
+        <v>-5.85</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.85</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.98</v>
+        <v>-3.47</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.38</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1472,13 +1472,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.68</v>
+        <v>-5.6</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.6</v>
+        <v>-4.47</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.92</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1489,13 +1489,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.87</v>
+        <v>-6.15</v>
       </c>
       <c r="D12" s="5">
-        <v>-6.15</v>
+        <v>-5.85</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.28</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1506,13 +1506,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-19.54</v>
+        <v>-19.25</v>
       </c>
       <c r="D13" s="5">
-        <v>-19.25</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.29</v>
+        <v>-18.8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-30.9</v>
+        <v>-31.4</v>
       </c>
       <c r="D14" s="5">
-        <v>-31.4</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.5</v>
+        <v>-32.5</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1540,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-29.79</v>
+        <v>-30.08</v>
       </c>
       <c r="D15" s="5">
-        <v>-30.08</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.29</v>
+        <v>-30.94</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1557,13 +1557,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-10.31</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.869999999999999</v>
+        <v>-11.15</v>
       </c>
       <c r="E16" s="7">
-        <v>0.44</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1574,13 +1574,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-7.29</v>
+        <v>-7.37</v>
       </c>
       <c r="D17" s="5">
-        <v>-7.37</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.08</v>
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1591,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.94</v>
+        <v>-6.49</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.49</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.55</v>
+        <v>-7.1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1608,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-19.71</v>
+        <v>-19.41</v>
       </c>
       <c r="D19" s="5">
-        <v>-19.41</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.3</v>
+        <v>-19.08</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1625,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-31.37</v>
+        <v>-31.84</v>
       </c>
       <c r="D20" s="5">
-        <v>-31.84</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.47</v>
+        <v>-32.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1642,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.5</v>
+        <v>-34.1</v>
       </c>
       <c r="D21" s="5">
-        <v>-34.1</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.6</v>
+        <v>-34.79</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1659,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2250</v>
+        <v>2258.4</v>
       </c>
       <c r="D22" s="5">
-        <v>2258.4</v>
-      </c>
-      <c r="E22" s="7">
-        <v>8.4</v>
+        <v>2267.7</v>
+      </c>
+      <c r="E22" s="6">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1676,13 +1676,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>692.8</v>
+        <v>688.05</v>
       </c>
       <c r="D23" s="5">
-        <v>688.05</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4.75</v>
+        <v>680.2</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1693,13 +1693,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>523.75</v>
+        <v>519</v>
       </c>
       <c r="D24" s="5">
-        <v>519</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-4.75</v>
+        <v>513.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-5.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,13 +1710,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>39.72</v>
+        <v>40.72</v>
       </c>
       <c r="D25" s="5">
-        <v>40.72</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1</v>
+        <v>41.87</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,13 +1727,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>40.85</v>
+        <v>39.17</v>
       </c>
       <c r="D26" s="5">
-        <v>39.17</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.68</v>
+        <v>36.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1744,13 +1744,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>40.51</v>
+        <v>38.56</v>
       </c>
       <c r="D27" s="5">
-        <v>38.56</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.95</v>
+        <v>36.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1761,13 +1761,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>29.01</v>
+        <v>-35.77</v>
       </c>
       <c r="D28" s="5">
-        <v>-35.77</v>
+        <v>-12.54</v>
       </c>
       <c r="E28" s="6">
-        <v>-64.78</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1778,13 +1778,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-39.91</v>
+        <v>-23.77</v>
       </c>
       <c r="D29" s="5">
-        <v>-23.77</v>
-      </c>
-      <c r="E29" s="7">
-        <v>16.14</v>
+        <v>30.71</v>
+      </c>
+      <c r="E29" s="6">
+        <v>54.48</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1795,13 +1795,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-62.76</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="D30" s="5">
-        <v>-70.31999999999999</v>
+        <v>-22.37</v>
       </c>
       <c r="E30" s="6">
-        <v>-7.56</v>
+        <v>47.95</v>
       </c>
     </row>
   </sheetData>
@@ -1866,16 +1866,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>39.5</v>
+        <v>38.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.3</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1288</v>
+        <v>0.1327</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0263</v>
+        <v>-0.0274</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.05309999999999999</v>
+        <v>-0.0561</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -878,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2267.7</v>
+        <v>2300</v>
       </c>
       <c r="D2">
-        <v>0.41</v>
+        <v>1.42</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -890,46 +890,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-19.08</v>
+        <v>-17.92</v>
       </c>
       <c r="H2">
-        <v>4.55</v>
+        <v>6.04</v>
       </c>
       <c r="I2">
-        <v>-3.47</v>
+        <v>-0.49</v>
       </c>
       <c r="J2">
-        <v>-4.73</v>
+        <v>-3.28</v>
       </c>
       <c r="K2">
-        <v>-11.15</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L2">
-        <v>-18.8</v>
+        <v>-16.24</v>
       </c>
       <c r="M2">
-        <v>13.27</v>
+        <v>14.2</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>2272.14</v>
+        <v>2269.86</v>
       </c>
       <c r="Q2">
-        <v>2303.76</v>
+        <v>2303.64</v>
       </c>
       <c r="R2">
-        <v>2420.24</v>
+        <v>2416.54</v>
       </c>
       <c r="S2">
-        <v>2536.54</v>
+        <v>2535.19</v>
       </c>
       <c r="T2">
-        <v>-10.6</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,34 +944,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.87</v>
+        <v>45.81</v>
       </c>
       <c r="Z2">
-        <v>-36.48</v>
+        <v>-33.84</v>
       </c>
       <c r="AA2">
-        <v>-36.5</v>
+        <v>-35.97</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>2.13</v>
       </c>
       <c r="AC2">
-        <v>32.18</v>
+        <v>42.44</v>
       </c>
       <c r="AD2">
-        <v>34.03</v>
+        <v>35.4</v>
       </c>
       <c r="AE2">
-        <v>65.34999999999999</v>
+        <v>64.78</v>
       </c>
       <c r="AF2">
-        <v>-12.54</v>
+        <v>-33.1</v>
       </c>
       <c r="AG2">
-        <v>2404.35</v>
+        <v>2404.25</v>
       </c>
       <c r="AH2">
-        <v>2203.17</v>
+        <v>2203.04</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>29.33</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -991,10 +991,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>680.2</v>
+        <v>685.3</v>
       </c>
       <c r="D3">
-        <v>-1.14</v>
+        <v>0.75</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1003,46 +1003,46 @@
         <v>680.2</v>
       </c>
       <c r="G3">
-        <v>-32.62</v>
+        <v>-32.11</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I3">
-        <v>-4.47</v>
+        <v>-3.06</v>
       </c>
       <c r="J3">
-        <v>-6.68</v>
+        <v>-6.84</v>
       </c>
       <c r="K3">
-        <v>-8.029999999999999</v>
+        <v>-6.81</v>
       </c>
       <c r="L3">
-        <v>-32.5</v>
+        <v>-32.07</v>
       </c>
       <c r="M3">
-        <v>-2.74</v>
+        <v>-2</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>692.41</v>
+        <v>688.08</v>
       </c>
       <c r="Q3">
-        <v>707.48</v>
+        <v>705.79</v>
       </c>
       <c r="R3">
-        <v>714.41</v>
+        <v>713.58</v>
       </c>
       <c r="S3">
-        <v>791.61</v>
+        <v>790.3</v>
       </c>
       <c r="T3">
-        <v>-14.07</v>
+        <v>-13.29</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1057,43 +1057,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.5</v>
+        <v>39.39</v>
       </c>
       <c r="Z3">
-        <v>-7.45</v>
+        <v>-8.16</v>
       </c>
       <c r="AA3">
-        <v>-4.49</v>
+        <v>-5.22</v>
       </c>
       <c r="AB3">
-        <v>-2.96</v>
+        <v>-2.94</v>
       </c>
       <c r="AC3">
-        <v>4.48</v>
+        <v>5.67</v>
       </c>
       <c r="AD3">
-        <v>12.32</v>
+        <v>6.49</v>
       </c>
       <c r="AE3">
-        <v>14.44</v>
+        <v>14.69</v>
       </c>
       <c r="AF3">
-        <v>30.71</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AG3">
-        <v>733.6799999999999</v>
+        <v>733.1799999999999</v>
       </c>
       <c r="AH3">
-        <v>681.27</v>
+        <v>678.4</v>
       </c>
       <c r="AI3">
-        <v>727.78</v>
+        <v>722.22</v>
       </c>
       <c r="AJ3" t="s">
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>26.37</v>
+        <v>30.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1104,10 +1104,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>513.6</v>
+        <v>514.1</v>
       </c>
       <c r="D4">
-        <v>-1.04</v>
+        <v>0.1</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1116,46 +1116,46 @@
         <v>513.6</v>
       </c>
       <c r="G4">
-        <v>-34.79</v>
+        <v>-34.72</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>-5.85</v>
+        <v>-4.73</v>
       </c>
       <c r="J4">
-        <v>-2.52</v>
+        <v>-3.18</v>
       </c>
       <c r="K4">
-        <v>-7.1</v>
+        <v>-7.99</v>
       </c>
       <c r="L4">
-        <v>-30.94</v>
+        <v>-30.87</v>
       </c>
       <c r="M4">
-        <v>-5.61</v>
+        <v>-5.3</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>524.87</v>
+        <v>519.76</v>
       </c>
       <c r="Q4">
-        <v>538.47</v>
+        <v>537.59</v>
       </c>
       <c r="R4">
-        <v>539.88</v>
+        <v>539.45</v>
       </c>
       <c r="S4">
-        <v>603.4400000000001</v>
+        <v>602.15</v>
       </c>
       <c r="T4">
-        <v>-14.89</v>
+        <v>-14.62</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1170,43 +1170,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.41</v>
+        <v>36.76</v>
       </c>
       <c r="Z4">
-        <v>-4.42</v>
+        <v>-5.64</v>
       </c>
       <c r="AA4">
-        <v>-0.63</v>
+        <v>-1.63</v>
       </c>
       <c r="AB4">
-        <v>-3.79</v>
+        <v>-4.01</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AD4">
-        <v>3.7</v>
+        <v>0.17</v>
       </c>
       <c r="AE4">
-        <v>14.81</v>
+        <v>14.55</v>
       </c>
       <c r="AF4">
-        <v>-22.37</v>
+        <v>-19.01</v>
       </c>
       <c r="AG4">
-        <v>566.5599999999999</v>
+        <v>567.61</v>
       </c>
       <c r="AH4">
-        <v>510.38</v>
+        <v>507.58</v>
       </c>
       <c r="AI4">
-        <v>561.29</v>
+        <v>557.24</v>
       </c>
       <c r="AJ4" t="s">
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>36.12</v>
+        <v>39.43</v>
       </c>
     </row>
   </sheetData>
@@ -1404,13 +1404,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.76</v>
+        <v>-4.73</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.73</v>
+        <v>-3.28</v>
       </c>
       <c r="E7" s="6">
-        <v>3.03</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1421,13 +1421,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.67</v>
+        <v>-6.68</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.68</v>
+        <v>-6.84</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1438,13 +1438,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.57</v>
+        <v>-2.52</v>
       </c>
       <c r="D9" s="5">
-        <v>-2.52</v>
-      </c>
-      <c r="E9" s="6">
-        <v>5.05</v>
+        <v>-3.18</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1455,13 +1455,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.85</v>
+        <v>-3.47</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.47</v>
+        <v>-0.49</v>
       </c>
       <c r="E10" s="6">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1472,13 +1472,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.6</v>
+        <v>-4.47</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.47</v>
+        <v>-3.06</v>
       </c>
       <c r="E11" s="6">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1489,13 +1489,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-6.15</v>
+        <v>-5.85</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.85</v>
+        <v>-4.73</v>
       </c>
       <c r="E12" s="6">
-        <v>0.3</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1506,13 +1506,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-19.25</v>
+        <v>-18.8</v>
       </c>
       <c r="D13" s="5">
-        <v>-18.8</v>
+        <v>-16.24</v>
       </c>
       <c r="E13" s="6">
-        <v>0.45</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-31.4</v>
+        <v>-32.5</v>
       </c>
       <c r="D14" s="5">
-        <v>-32.5</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.1</v>
+        <v>-32.07</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1540,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-30.08</v>
+        <v>-30.94</v>
       </c>
       <c r="D15" s="5">
-        <v>-30.94</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.86</v>
+        <v>-30.87</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1557,13 +1557,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-9.869999999999999</v>
+        <v>-11.15</v>
       </c>
       <c r="D16" s="5">
-        <v>-11.15</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.28</v>
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.02</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1574,13 +1574,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-7.37</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.66</v>
+        <v>-6.81</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1591,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-6.49</v>
+        <v>-7.1</v>
       </c>
       <c r="D18" s="5">
-        <v>-7.1</v>
+        <v>-7.99</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.61</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1608,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-19.41</v>
+        <v>-19.08</v>
       </c>
       <c r="D19" s="5">
-        <v>-19.08</v>
+        <v>-17.92</v>
       </c>
       <c r="E19" s="6">
-        <v>0.33</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1625,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-31.84</v>
+        <v>-32.62</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.62</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.78</v>
+        <v>-32.11</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.51</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1642,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-34.1</v>
+        <v>-34.79</v>
       </c>
       <c r="D21" s="5">
-        <v>-34.79</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-34.72</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1659,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2258.4</v>
+        <v>2267.7</v>
       </c>
       <c r="D22" s="5">
-        <v>2267.7</v>
+        <v>2300</v>
       </c>
       <c r="E22" s="6">
-        <v>9.300000000000001</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1676,13 +1676,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>688.05</v>
+        <v>680.2</v>
       </c>
       <c r="D23" s="5">
-        <v>680.2</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-7.85</v>
+        <v>685.3</v>
+      </c>
+      <c r="E23" s="6">
+        <v>5.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1693,13 +1693,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>519</v>
+        <v>513.6</v>
       </c>
       <c r="D24" s="5">
-        <v>513.6</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-5.4</v>
+        <v>514.1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,13 +1710,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>40.72</v>
+        <v>41.87</v>
       </c>
       <c r="D25" s="5">
-        <v>41.87</v>
+        <v>45.81</v>
       </c>
       <c r="E25" s="6">
-        <v>1.15</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,13 +1727,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>39.17</v>
+        <v>36.5</v>
       </c>
       <c r="D26" s="5">
-        <v>36.5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.67</v>
+        <v>39.39</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1744,13 +1744,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>38.56</v>
+        <v>36.41</v>
       </c>
       <c r="D27" s="5">
-        <v>36.41</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.15</v>
+        <v>36.76</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1761,13 +1761,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-35.77</v>
+        <v>-12.54</v>
       </c>
       <c r="D28" s="5">
-        <v>-12.54</v>
-      </c>
-      <c r="E28" s="6">
-        <v>23.23</v>
+        <v>-33.1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-20.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1778,13 +1778,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-23.77</v>
+        <v>30.71</v>
       </c>
       <c r="D29" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="E29" s="6">
-        <v>54.48</v>
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-39.66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1795,13 +1795,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-70.31999999999999</v>
+        <v>-22.37</v>
       </c>
       <c r="D30" s="5">
-        <v>-22.37</v>
+        <v>-19.01</v>
       </c>
       <c r="E30" s="6">
-        <v>47.95</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
@@ -1866,16 +1866,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>38.3</v>
+        <v>40.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.6</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.800000000000001</v>
+        <v>-8</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1327</v>
+        <v>0.142</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0274</v>
+        <v>-0.02</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0561</v>
+        <v>-0.053</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -878,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2300</v>
+        <v>2316.7</v>
       </c>
       <c r="D2">
-        <v>1.42</v>
+        <v>0.73</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -890,46 +890,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.92</v>
+        <v>-17.33</v>
       </c>
       <c r="H2">
-        <v>6.04</v>
+        <v>6.81</v>
       </c>
       <c r="I2">
-        <v>-0.49</v>
+        <v>1.91</v>
       </c>
       <c r="J2">
-        <v>-3.28</v>
+        <v>0.63</v>
       </c>
       <c r="K2">
-        <v>-9.130000000000001</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L2">
-        <v>-16.24</v>
+        <v>-14.59</v>
       </c>
       <c r="M2">
-        <v>14.2</v>
+        <v>14.21</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P2">
-        <v>2269.86</v>
+        <v>2278.56</v>
       </c>
       <c r="Q2">
-        <v>2303.64</v>
+        <v>2308.31</v>
       </c>
       <c r="R2">
-        <v>2416.54</v>
+        <v>2412.41</v>
       </c>
       <c r="S2">
-        <v>2535.19</v>
+        <v>2534.14</v>
       </c>
       <c r="T2">
-        <v>-9.279999999999999</v>
+        <v>-8.58</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,34 +944,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.81</v>
+        <v>47.78</v>
       </c>
       <c r="Z2">
-        <v>-33.84</v>
+        <v>-30.05</v>
       </c>
       <c r="AA2">
-        <v>-35.97</v>
+        <v>-34.78</v>
       </c>
       <c r="AB2">
-        <v>2.13</v>
+        <v>4.73</v>
       </c>
       <c r="AC2">
-        <v>42.44</v>
+        <v>52.87</v>
       </c>
       <c r="AD2">
-        <v>35.4</v>
+        <v>42.5</v>
       </c>
       <c r="AE2">
-        <v>64.78</v>
+        <v>63.51</v>
       </c>
       <c r="AF2">
-        <v>-33.1</v>
+        <v>-58.71</v>
       </c>
       <c r="AG2">
-        <v>2404.25</v>
+        <v>2401.62</v>
       </c>
       <c r="AH2">
-        <v>2203.04</v>
+        <v>2215.01</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>26.23</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -991,10 +991,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>685.3</v>
+        <v>683.3</v>
       </c>
       <c r="D3">
-        <v>0.75</v>
+        <v>-0.29</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1003,46 +1003,46 @@
         <v>680.2</v>
       </c>
       <c r="G3">
-        <v>-32.11</v>
+        <v>-32.31</v>
       </c>
       <c r="H3">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="I3">
-        <v>-3.06</v>
+        <v>-1.55</v>
       </c>
       <c r="J3">
-        <v>-6.84</v>
+        <v>-4.97</v>
       </c>
       <c r="K3">
-        <v>-6.81</v>
+        <v>-8.67</v>
       </c>
       <c r="L3">
-        <v>-32.07</v>
+        <v>-31.31</v>
       </c>
       <c r="M3">
-        <v>-2</v>
+        <v>-1.92</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>688.08</v>
+        <v>685.9299999999999</v>
       </c>
       <c r="Q3">
-        <v>705.79</v>
+        <v>703.8200000000001</v>
       </c>
       <c r="R3">
-        <v>713.58</v>
+        <v>712.66</v>
       </c>
       <c r="S3">
-        <v>790.3</v>
+        <v>788.98</v>
       </c>
       <c r="T3">
-        <v>-13.29</v>
+        <v>-13.39</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1057,34 +1057,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.39</v>
+        <v>38.65</v>
       </c>
       <c r="Z3">
-        <v>-8.16</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AA3">
-        <v>-5.22</v>
+        <v>-5.93</v>
       </c>
       <c r="AB3">
-        <v>-2.94</v>
+        <v>-2.85</v>
       </c>
       <c r="AC3">
-        <v>5.67</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AD3">
-        <v>6.49</v>
+        <v>6.37</v>
       </c>
       <c r="AE3">
-        <v>14.69</v>
+        <v>14.26</v>
       </c>
       <c r="AF3">
-        <v>-8.949999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="AG3">
-        <v>733.1799999999999</v>
+        <v>731.75</v>
       </c>
       <c r="AH3">
-        <v>678.4</v>
+        <v>675.89</v>
       </c>
       <c r="AI3">
         <v>722.22</v>
@@ -1093,7 +1093,7 @@
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>30.09</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1104,10 +1104,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>514.1</v>
+        <v>517</v>
       </c>
       <c r="D4">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1116,46 +1116,46 @@
         <v>513.6</v>
       </c>
       <c r="G4">
-        <v>-34.72</v>
+        <v>-34.35</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="I4">
-        <v>-4.73</v>
+        <v>-2.15</v>
       </c>
       <c r="J4">
-        <v>-3.18</v>
+        <v>-2.75</v>
       </c>
       <c r="K4">
-        <v>-7.99</v>
+        <v>-7.13</v>
       </c>
       <c r="L4">
-        <v>-30.87</v>
+        <v>-29.66</v>
       </c>
       <c r="M4">
-        <v>-5.3</v>
+        <v>-5.11</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>519.76</v>
+        <v>517.49</v>
       </c>
       <c r="Q4">
-        <v>537.59</v>
+        <v>537.27</v>
       </c>
       <c r="R4">
-        <v>539.45</v>
+        <v>538.9299999999999</v>
       </c>
       <c r="S4">
-        <v>602.15</v>
+        <v>600.9400000000001</v>
       </c>
       <c r="T4">
-        <v>-14.62</v>
+        <v>-13.97</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1170,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.76</v>
+        <v>38.87</v>
       </c>
       <c r="Z4">
-        <v>-5.64</v>
+        <v>-6.3</v>
       </c>
       <c r="AA4">
-        <v>-1.63</v>
+        <v>-2.57</v>
       </c>
       <c r="AB4">
-        <v>-4.01</v>
+        <v>-3.74</v>
       </c>
       <c r="AC4">
-        <v>0.51</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
-        <v>0.17</v>
+        <v>1.54</v>
       </c>
       <c r="AE4">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="AF4">
-        <v>-19.01</v>
+        <v>-40.64</v>
       </c>
       <c r="AG4">
-        <v>567.61</v>
+        <v>568.0599999999999</v>
       </c>
       <c r="AH4">
-        <v>507.58</v>
+        <v>506.48</v>
       </c>
       <c r="AI4">
         <v>557.24</v>
@@ -1206,7 +1206,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>39.43</v>
+        <v>40.88</v>
       </c>
     </row>
   </sheetData>
@@ -1404,13 +1404,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.73</v>
+        <v>-3.28</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.28</v>
+        <v>0.63</v>
       </c>
       <c r="E7" s="6">
-        <v>1.45</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1421,13 +1421,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.68</v>
+        <v>-6.84</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.84</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.16</v>
+        <v>-4.97</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1438,13 +1438,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-2.52</v>
+        <v>-3.18</v>
       </c>
       <c r="D9" s="5">
-        <v>-3.18</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.66</v>
+        <v>-2.75</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1455,13 +1455,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.47</v>
+        <v>-0.49</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.49</v>
+        <v>1.91</v>
       </c>
       <c r="E10" s="6">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1472,13 +1472,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.47</v>
+        <v>-3.06</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.06</v>
+        <v>-1.55</v>
       </c>
       <c r="E11" s="6">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1489,13 +1489,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.85</v>
+        <v>-4.73</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.73</v>
+        <v>-2.15</v>
       </c>
       <c r="E12" s="6">
-        <v>1.12</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1506,13 +1506,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-18.8</v>
+        <v>-16.24</v>
       </c>
       <c r="D13" s="5">
-        <v>-16.24</v>
+        <v>-14.59</v>
       </c>
       <c r="E13" s="6">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-32.5</v>
+        <v>-32.07</v>
       </c>
       <c r="D14" s="5">
-        <v>-32.07</v>
+        <v>-31.31</v>
       </c>
       <c r="E14" s="6">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1540,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-30.94</v>
+        <v>-30.87</v>
       </c>
       <c r="D15" s="5">
-        <v>-30.87</v>
+        <v>-29.66</v>
       </c>
       <c r="E15" s="6">
-        <v>0.07000000000000001</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1557,13 +1557,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-11.15</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.130000000000001</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="E16" s="6">
-        <v>2.02</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1574,13 +1574,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-8.029999999999999</v>
+        <v>-6.81</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.81</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.22</v>
+        <v>-8.67</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1591,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-7.1</v>
+        <v>-7.99</v>
       </c>
       <c r="D18" s="5">
-        <v>-7.99</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.89</v>
+        <v>-7.13</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1608,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-19.08</v>
+        <v>-17.92</v>
       </c>
       <c r="D19" s="5">
-        <v>-17.92</v>
+        <v>-17.33</v>
       </c>
       <c r="E19" s="6">
-        <v>1.16</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1625,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.62</v>
+        <v>-32.11</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.11</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.51</v>
+        <v>-32.31</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1642,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-34.79</v>
+        <v>-34.72</v>
       </c>
       <c r="D21" s="5">
-        <v>-34.72</v>
+        <v>-34.35</v>
       </c>
       <c r="E21" s="6">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1659,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2267.7</v>
+        <v>2300</v>
       </c>
       <c r="D22" s="5">
-        <v>2300</v>
+        <v>2316.7</v>
       </c>
       <c r="E22" s="6">
-        <v>32.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1676,13 +1676,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>680.2</v>
+        <v>685.3</v>
       </c>
       <c r="D23" s="5">
-        <v>685.3</v>
-      </c>
-      <c r="E23" s="6">
-        <v>5.1</v>
+        <v>683.3</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1693,13 +1693,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>513.6</v>
+        <v>514.1</v>
       </c>
       <c r="D24" s="5">
-        <v>514.1</v>
+        <v>517</v>
       </c>
       <c r="E24" s="6">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,13 +1710,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>41.87</v>
+        <v>45.81</v>
       </c>
       <c r="D25" s="5">
-        <v>45.81</v>
+        <v>47.78</v>
       </c>
       <c r="E25" s="6">
-        <v>3.94</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,13 +1727,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>36.5</v>
+        <v>39.39</v>
       </c>
       <c r="D26" s="5">
-        <v>39.39</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2.89</v>
+        <v>38.65</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1744,13 +1744,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>36.41</v>
+        <v>36.76</v>
       </c>
       <c r="D27" s="5">
-        <v>36.76</v>
+        <v>38.87</v>
       </c>
       <c r="E27" s="6">
-        <v>0.35</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1761,13 +1761,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-12.54</v>
+        <v>-33.1</v>
       </c>
       <c r="D28" s="5">
-        <v>-33.1</v>
+        <v>-58.71</v>
       </c>
       <c r="E28" s="7">
-        <v>-20.56</v>
+        <v>-25.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1778,13 +1778,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>30.71</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D29" s="5">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-39.66</v>
+        <v>-1.04</v>
+      </c>
+      <c r="E29" s="6">
+        <v>7.91</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1795,13 +1795,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-22.37</v>
+        <v>-19.01</v>
       </c>
       <c r="D30" s="5">
-        <v>-19.01</v>
-      </c>
-      <c r="E30" s="6">
-        <v>3.36</v>
+        <v>-40.64</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-21.63</v>
       </c>
     </row>
   </sheetData>
@@ -1866,16 +1866,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40.7</v>
+        <v>41.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.4</v>
+        <v>-2.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.142</v>
+        <v>0.1421</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.02</v>
+        <v>-0.0192</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.053</v>
+        <v>-0.05110000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -738,7 +738,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -878,10 +880,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2316.7</v>
+        <v>2309.5</v>
       </c>
       <c r="D2">
-        <v>0.73</v>
+        <v>-0.31</v>
       </c>
       <c r="E2">
         <v>2802.31</v>
@@ -890,46 +892,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-17.33</v>
+        <v>-17.59</v>
       </c>
       <c r="H2">
-        <v>6.81</v>
+        <v>6.48</v>
       </c>
       <c r="I2">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
       <c r="J2">
-        <v>0.63</v>
+        <v>3.88</v>
       </c>
       <c r="K2">
-        <v>-8.859999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L2">
-        <v>-14.59</v>
+        <v>-15.09</v>
       </c>
       <c r="M2">
-        <v>14.21</v>
+        <v>14.08</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>2278.56</v>
+        <v>2290.46</v>
       </c>
       <c r="Q2">
-        <v>2308.31</v>
+        <v>2309.75</v>
       </c>
       <c r="R2">
-        <v>2412.41</v>
+        <v>2408.1</v>
       </c>
       <c r="S2">
-        <v>2534.14</v>
+        <v>2533.34</v>
       </c>
       <c r="T2">
-        <v>-8.58</v>
+        <v>-8.84</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,34 +946,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>47.78</v>
+        <v>46.99</v>
       </c>
       <c r="Z2">
-        <v>-30.05</v>
+        <v>-27.31</v>
       </c>
       <c r="AA2">
-        <v>-34.78</v>
+        <v>-33.29</v>
       </c>
       <c r="AB2">
-        <v>4.73</v>
+        <v>5.98</v>
       </c>
       <c r="AC2">
-        <v>52.87</v>
+        <v>57.01</v>
       </c>
       <c r="AD2">
-        <v>42.5</v>
+        <v>50.77</v>
       </c>
       <c r="AE2">
-        <v>63.51</v>
+        <v>63.11</v>
       </c>
       <c r="AF2">
-        <v>-58.71</v>
+        <v>-10.41</v>
       </c>
       <c r="AG2">
-        <v>2401.62</v>
+        <v>2402.15</v>
       </c>
       <c r="AH2">
-        <v>2215.01</v>
+        <v>2217.36</v>
       </c>
       <c r="AI2">
         <v>2426.05</v>
@@ -980,7 +982,7 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>23.51</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -991,10 +993,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>683.3</v>
+        <v>692.8</v>
       </c>
       <c r="D3">
-        <v>-0.29</v>
+        <v>1.39</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1003,46 +1005,46 @@
         <v>680.2</v>
       </c>
       <c r="G3">
-        <v>-32.31</v>
+        <v>-31.37</v>
       </c>
       <c r="H3">
-        <v>0.46</v>
+        <v>1.85</v>
       </c>
       <c r="I3">
-        <v>-1.55</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-4.97</v>
+        <v>-4.14</v>
       </c>
       <c r="K3">
-        <v>-8.67</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L3">
-        <v>-31.31</v>
+        <v>-30.92</v>
       </c>
       <c r="M3">
-        <v>-1.92</v>
+        <v>-1.93</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="P3">
         <v>685.9299999999999</v>
       </c>
       <c r="Q3">
-        <v>703.8200000000001</v>
+        <v>703.02</v>
       </c>
       <c r="R3">
-        <v>712.66</v>
+        <v>712.0599999999999</v>
       </c>
       <c r="S3">
-        <v>788.98</v>
+        <v>787.75</v>
       </c>
       <c r="T3">
-        <v>-13.39</v>
+        <v>-12.05</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1057,34 +1059,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.65</v>
+        <v>44.05</v>
       </c>
       <c r="Z3">
-        <v>-8.789999999999999</v>
+        <v>-8.42</v>
       </c>
       <c r="AA3">
-        <v>-5.93</v>
+        <v>-6.43</v>
       </c>
       <c r="AB3">
-        <v>-2.85</v>
+        <v>-1.99</v>
       </c>
       <c r="AC3">
-        <v>8.960000000000001</v>
+        <v>22.38</v>
       </c>
       <c r="AD3">
-        <v>6.37</v>
+        <v>12.34</v>
       </c>
       <c r="AE3">
-        <v>14.26</v>
+        <v>14.29</v>
       </c>
       <c r="AF3">
-        <v>-1.04</v>
+        <v>-33.9</v>
       </c>
       <c r="AG3">
-        <v>731.75</v>
+        <v>731.27</v>
       </c>
       <c r="AH3">
-        <v>675.89</v>
+        <v>674.78</v>
       </c>
       <c r="AI3">
         <v>722.22</v>
@@ -1093,7 +1095,7 @@
         <v>42</v>
       </c>
       <c r="AK3">
-        <v>33.32</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1104,10 +1106,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>517</v>
+        <v>524.9</v>
       </c>
       <c r="D4">
-        <v>0.5600000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="E4">
         <v>787.55</v>
@@ -1116,46 +1118,46 @@
         <v>513.6</v>
       </c>
       <c r="G4">
-        <v>-34.35</v>
+        <v>-33.35</v>
       </c>
       <c r="H4">
-        <v>0.66</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>-2.15</v>
+        <v>0.22</v>
       </c>
       <c r="J4">
-        <v>-2.75</v>
+        <v>0.26</v>
       </c>
       <c r="K4">
-        <v>-7.13</v>
+        <v>-3.76</v>
       </c>
       <c r="L4">
-        <v>-29.66</v>
+        <v>-28.8</v>
       </c>
       <c r="M4">
-        <v>-5.11</v>
+        <v>-5.09</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>517.49</v>
+        <v>517.72</v>
       </c>
       <c r="Q4">
-        <v>537.27</v>
+        <v>537.45</v>
       </c>
       <c r="R4">
-        <v>538.9299999999999</v>
+        <v>538.66</v>
       </c>
       <c r="S4">
-        <v>600.9400000000001</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="T4">
-        <v>-13.97</v>
+        <v>-12.49</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1170,34 +1172,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.87</v>
+        <v>44.31</v>
       </c>
       <c r="Z4">
-        <v>-6.3</v>
+        <v>-6.12</v>
       </c>
       <c r="AA4">
-        <v>-2.57</v>
+        <v>-3.28</v>
       </c>
       <c r="AB4">
-        <v>-3.74</v>
+        <v>-2.84</v>
       </c>
       <c r="AC4">
-        <v>4.1</v>
+        <v>15.62</v>
       </c>
       <c r="AD4">
-        <v>1.54</v>
+        <v>6.74</v>
       </c>
       <c r="AE4">
-        <v>14.25</v>
+        <v>14.33</v>
       </c>
       <c r="AF4">
-        <v>-40.64</v>
+        <v>-15.08</v>
       </c>
       <c r="AG4">
-        <v>568.0599999999999</v>
+        <v>567.88</v>
       </c>
       <c r="AH4">
-        <v>506.48</v>
+        <v>507.02</v>
       </c>
       <c r="AI4">
         <v>557.24</v>
@@ -1206,7 +1208,7 @@
         <v>42</v>
       </c>
       <c r="AK4">
-        <v>40.88</v>
+        <v>39.79</v>
       </c>
     </row>
   </sheetData>
@@ -1310,27 +1312,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y4">
@@ -1404,13 +1406,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.28</v>
+        <v>0.63</v>
       </c>
       <c r="D7" s="5">
-        <v>0.63</v>
+        <v>3.88</v>
       </c>
       <c r="E7" s="6">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1421,13 +1423,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.84</v>
+        <v>-4.97</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.97</v>
+        <v>-4.14</v>
       </c>
       <c r="E8" s="6">
-        <v>1.87</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1438,13 +1440,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-3.18</v>
+        <v>-2.75</v>
       </c>
       <c r="D9" s="5">
-        <v>-2.75</v>
+        <v>0.26</v>
       </c>
       <c r="E9" s="6">
-        <v>0.43</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1455,13 +1457,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.49</v>
+        <v>1.91</v>
       </c>
       <c r="D10" s="5">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
       <c r="E10" s="6">
-        <v>2.4</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1472,13 +1474,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.06</v>
+        <v>-1.55</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.55</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1489,13 +1491,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.73</v>
+        <v>-2.15</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.15</v>
+        <v>0.22</v>
       </c>
       <c r="E12" s="6">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1506,13 +1508,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-16.24</v>
+        <v>-14.59</v>
       </c>
       <c r="D13" s="5">
-        <v>-14.59</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.65</v>
+        <v>-15.09</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1523,13 +1525,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-32.07</v>
+        <v>-31.31</v>
       </c>
       <c r="D14" s="5">
-        <v>-31.31</v>
+        <v>-30.92</v>
       </c>
       <c r="E14" s="6">
-        <v>0.76</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1540,13 +1542,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-30.87</v>
+        <v>-29.66</v>
       </c>
       <c r="D15" s="5">
-        <v>-29.66</v>
+        <v>-28.8</v>
       </c>
       <c r="E15" s="6">
-        <v>1.21</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1557,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-9.130000000000001</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.27</v>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1574,13 +1576,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-6.81</v>
+        <v>-8.67</v>
       </c>
       <c r="D17" s="5">
-        <v>-8.67</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.86</v>
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1591,13 +1593,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-7.99</v>
+        <v>-7.13</v>
       </c>
       <c r="D18" s="5">
-        <v>-7.13</v>
+        <v>-3.76</v>
       </c>
       <c r="E18" s="6">
-        <v>0.86</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1608,13 +1610,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-17.92</v>
+        <v>-17.33</v>
       </c>
       <c r="D19" s="5">
-        <v>-17.33</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.59</v>
+        <v>-17.59</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1625,13 +1627,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.11</v>
+        <v>-32.31</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.31</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.2</v>
+        <v>-31.37</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1642,13 +1644,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-34.72</v>
+        <v>-34.35</v>
       </c>
       <c r="D21" s="5">
-        <v>-34.35</v>
+        <v>-33.35</v>
       </c>
       <c r="E21" s="6">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1659,13 +1661,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2300</v>
+        <v>2316.7</v>
       </c>
       <c r="D22" s="5">
-        <v>2316.7</v>
-      </c>
-      <c r="E22" s="6">
-        <v>16.7</v>
+        <v>2309.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-7.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1676,13 +1678,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>685.3</v>
+        <v>683.3</v>
       </c>
       <c r="D23" s="5">
-        <v>683.3</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2</v>
+        <v>692.8</v>
+      </c>
+      <c r="E23" s="6">
+        <v>9.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1693,13 +1695,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>514.1</v>
+        <v>517</v>
       </c>
       <c r="D24" s="5">
-        <v>517</v>
+        <v>524.9</v>
       </c>
       <c r="E24" s="6">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,13 +1712,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>45.81</v>
+        <v>47.78</v>
       </c>
       <c r="D25" s="5">
-        <v>47.78</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.97</v>
+        <v>46.99</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,13 +1729,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>39.39</v>
+        <v>38.65</v>
       </c>
       <c r="D26" s="5">
-        <v>38.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.74</v>
+        <v>44.05</v>
+      </c>
+      <c r="E26" s="6">
+        <v>5.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1744,13 +1746,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>36.76</v>
+        <v>38.87</v>
       </c>
       <c r="D27" s="5">
-        <v>38.87</v>
+        <v>44.31</v>
       </c>
       <c r="E27" s="6">
-        <v>2.11</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1761,13 +1763,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-33.1</v>
+        <v>-58.71</v>
       </c>
       <c r="D28" s="5">
-        <v>-58.71</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-25.61</v>
+        <v>-10.41</v>
+      </c>
+      <c r="E28" s="6">
+        <v>48.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1778,13 +1780,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-8.949999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.04</v>
-      </c>
-      <c r="E29" s="6">
-        <v>7.91</v>
+        <v>-33.9</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-32.86</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1795,13 +1797,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-19.01</v>
+        <v>-40.64</v>
       </c>
       <c r="D30" s="5">
-        <v>-40.64</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-21.63</v>
+        <v>-15.08</v>
+      </c>
+      <c r="E30" s="6">
+        <v>25.56</v>
       </c>
     </row>
   </sheetData>
@@ -1860,22 +1862,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>36.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>41.8</v>
+        <v>45.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.199999999999999</v>
+        <v>-7.1</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1994,13 +1996,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1421</v>
+        <v>0.1408</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0192</v>
+        <v>-0.0193</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.05110000000000001</v>
+        <v>-0.0509</v>
       </c>
     </row>
   </sheetData>
